--- a/tests/data/mock_b_and_t_cells_exp.xlsx
+++ b/tests/data/mock_b_and_t_cells_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabewilson/Desktop/worklist_generation/tests/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B022A0-875C-C14E-8E37-79CB7BA39312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{471661DF-9C1C-0641-B062-566A46C4CC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14680" yWindow="700" windowWidth="14720" windowHeight="16940" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="User" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="104">
   <si>
     <t>Name:</t>
   </si>
@@ -312,9 +312,6 @@
     <t>tb</t>
   </si>
   <si>
-    <t>RA1</t>
-  </si>
-  <si>
     <t>Notes (not used):</t>
   </si>
   <si>
@@ -337,6 +334,18 @@
   </si>
   <si>
     <t>Vanquish Neo</t>
+  </si>
+  <si>
+    <t>tbmethod</t>
+  </si>
+  <si>
+    <t>tbmethodfile</t>
+  </si>
+  <si>
+    <t>wet</t>
+  </si>
+  <si>
+    <t>wetfile</t>
   </si>
 </sst>
 </file>
@@ -857,6 +866,21 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -872,21 +896,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1280,7 +1289,7 @@
         <v>4</v>
       </c>
       <c r="AH1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AM1" s="29"/>
       <c r="AO1" s="28"/>
@@ -1386,10 +1395,10 @@
       <c r="AJ4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AK4" s="81" t="s">
+      <c r="AK4" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="AL4" s="82"/>
+      <c r="AL4" s="87"/>
       <c r="AM4" s="9"/>
       <c r="AN4" s="9"/>
       <c r="AO4" s="28"/>
@@ -1489,15 +1498,13 @@
         <v>1</v>
       </c>
       <c r="AI5" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ5" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="AK5" s="81" t="s">
         <v>96</v>
       </c>
-      <c r="AL5" s="86"/>
+      <c r="AJ5" s="6"/>
+      <c r="AK5" s="86" t="s">
+        <v>95</v>
+      </c>
+      <c r="AL5" s="91"/>
       <c r="AM5" s="9"/>
       <c r="AN5" s="9"/>
       <c r="AO5" s="28"/>
@@ -1671,10 +1678,10 @@
       <c r="Z7" s="42">
         <v>4</v>
       </c>
-      <c r="AA7" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB7" s="89">
+      <c r="AA7" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB7" s="79">
         <v>14</v>
       </c>
       <c r="AD7" s="11">
@@ -1763,10 +1770,10 @@
       <c r="Z8" s="42">
         <v>4</v>
       </c>
-      <c r="AA8" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB8" s="89">
+      <c r="AA8" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB8" s="79">
         <v>14</v>
       </c>
       <c r="AD8" s="11">
@@ -1782,15 +1789,15 @@
         <v>1</v>
       </c>
       <c r="AI8" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ8" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="AK8" s="81" t="s">
+      <c r="AK8" s="86" t="s">
         <v>34</v>
       </c>
-      <c r="AL8" s="82"/>
+      <c r="AL8" s="87"/>
       <c r="AM8" s="9"/>
       <c r="AN8" s="9"/>
       <c r="AO8" s="28"/>
@@ -1865,10 +1872,10 @@
       <c r="Z9" s="42">
         <v>4</v>
       </c>
-      <c r="AA9" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB9" s="89">
+      <c r="AA9" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB9" s="79">
         <v>14</v>
       </c>
       <c r="AD9" s="11">
@@ -1884,11 +1891,11 @@
         <v>1</v>
       </c>
       <c r="AI9" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AJ9" s="6"/>
-      <c r="AK9" s="85"/>
-      <c r="AL9" s="82"/>
+      <c r="AK9" s="90"/>
+      <c r="AL9" s="87"/>
       <c r="AM9" s="9"/>
       <c r="AN9" s="9"/>
       <c r="AO9" s="28"/>
@@ -1963,10 +1970,10 @@
       <c r="Z10" s="42">
         <v>4</v>
       </c>
-      <c r="AA10" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB10" s="89">
+      <c r="AA10" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB10" s="79">
         <v>14</v>
       </c>
       <c r="AD10" s="11">
@@ -1981,14 +1988,14 @@
       <c r="AG10" s="26">
         <v>1</v>
       </c>
-      <c r="AI10" s="83" t="s">
+      <c r="AI10" s="88" t="s">
         <v>35</v>
       </c>
-      <c r="AJ10" s="79" t="s">
+      <c r="AJ10" s="84" t="s">
         <v>31</v>
       </c>
-      <c r="AK10" s="85"/>
-      <c r="AL10" s="82"/>
+      <c r="AK10" s="90"/>
+      <c r="AL10" s="87"/>
       <c r="AM10" s="9"/>
       <c r="AN10" s="9"/>
       <c r="AO10" s="28"/>
@@ -2063,10 +2070,10 @@
       <c r="Z11" s="42">
         <v>4</v>
       </c>
-      <c r="AA11" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB11" s="89">
+      <c r="AA11" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB11" s="79">
         <v>14</v>
       </c>
       <c r="AD11" s="11">
@@ -2081,8 +2088,8 @@
       <c r="AG11" s="26">
         <v>1</v>
       </c>
-      <c r="AI11" s="84"/>
-      <c r="AJ11" s="80"/>
+      <c r="AI11" s="89"/>
+      <c r="AJ11" s="85"/>
       <c r="AK11" s="30"/>
       <c r="AL11" s="30"/>
       <c r="AM11" s="9"/>
@@ -2159,10 +2166,10 @@
       <c r="Z12" s="42">
         <v>4</v>
       </c>
-      <c r="AA12" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB12" s="89">
+      <c r="AA12" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB12" s="79">
         <v>14</v>
       </c>
       <c r="AD12" s="11">
@@ -2255,10 +2262,10 @@
       <c r="Z13" s="42">
         <v>4</v>
       </c>
-      <c r="AA13" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB13" s="89">
+      <c r="AA13" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB13" s="79">
         <v>14</v>
       </c>
       <c r="AD13" s="11">
@@ -2351,10 +2358,10 @@
       <c r="Z14" s="42">
         <v>4</v>
       </c>
-      <c r="AA14" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB14" s="89">
+      <c r="AA14" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB14" s="79">
         <v>14</v>
       </c>
       <c r="AD14" s="11">
@@ -2367,7 +2374,7 @@
         <v>71</v>
       </c>
       <c r="AG14" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI14" s="31"/>
       <c r="AJ14" s="31"/>
@@ -2447,10 +2454,10 @@
       <c r="Z15" s="42">
         <v>4</v>
       </c>
-      <c r="AA15" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB15" s="89">
+      <c r="AA15" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB15" s="79">
         <v>14</v>
       </c>
       <c r="AD15" s="11">
@@ -2459,11 +2466,11 @@
       <c r="AE15" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AF15" s="91" t="s">
+      <c r="AF15" s="81" t="s">
         <v>72</v>
       </c>
       <c r="AG15" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI15" s="31"/>
       <c r="AJ15" s="31"/>
@@ -2543,10 +2550,10 @@
       <c r="Z16" s="42">
         <v>4</v>
       </c>
-      <c r="AA16" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB16" s="89">
+      <c r="AA16" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB16" s="79">
         <v>14</v>
       </c>
       <c r="AD16" s="11">
@@ -2639,10 +2646,10 @@
       <c r="Z17" s="42">
         <v>4</v>
       </c>
-      <c r="AA17" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB17" s="89">
+      <c r="AA17" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB17" s="79">
         <v>14</v>
       </c>
       <c r="AD17" s="11">
@@ -2734,10 +2741,10 @@
       <c r="Z18" s="42">
         <v>4</v>
       </c>
-      <c r="AA18" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB18" s="89">
+      <c r="AA18" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB18" s="79">
         <v>14</v>
       </c>
       <c r="AD18" s="11">
@@ -2823,10 +2830,10 @@
       <c r="Z19" s="42">
         <v>4</v>
       </c>
-      <c r="AA19" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB19" s="89">
+      <c r="AA19" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB19" s="79">
         <v>14</v>
       </c>
       <c r="AD19" s="11">
@@ -2909,10 +2916,10 @@
       <c r="Z20" s="42">
         <v>4</v>
       </c>
-      <c r="AA20" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB20" s="89">
+      <c r="AA20" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB20" s="79">
         <v>14</v>
       </c>
       <c r="AD20" s="11">
@@ -3311,10 +3318,10 @@
       <c r="Z25" s="62">
         <v>8</v>
       </c>
-      <c r="AA25" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB25" s="90">
+      <c r="AA25" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB25" s="80">
         <v>14</v>
       </c>
       <c r="AD25" s="11">
@@ -3401,10 +3408,10 @@
       <c r="Z26" s="62">
         <v>8</v>
       </c>
-      <c r="AA26" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB26" s="90">
+      <c r="AA26" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB26" s="80">
         <v>14</v>
       </c>
       <c r="AD26" s="11">
@@ -3491,10 +3498,10 @@
       <c r="Z27" s="62">
         <v>8</v>
       </c>
-      <c r="AA27" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB27" s="90">
+      <c r="AA27" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB27" s="80">
         <v>14</v>
       </c>
       <c r="AD27" s="11">
@@ -3581,10 +3588,10 @@
       <c r="Z28" s="62">
         <v>8</v>
       </c>
-      <c r="AA28" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB28" s="90">
+      <c r="AA28" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB28" s="80">
         <v>14</v>
       </c>
       <c r="AD28" s="11">
@@ -3671,10 +3678,10 @@
       <c r="Z29" s="62">
         <v>8</v>
       </c>
-      <c r="AA29" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB29" s="90">
+      <c r="AA29" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB29" s="80">
         <v>14</v>
       </c>
       <c r="AD29" s="11">
@@ -3761,10 +3768,10 @@
       <c r="Z30" s="62">
         <v>8</v>
       </c>
-      <c r="AA30" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB30" s="90">
+      <c r="AA30" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB30" s="80">
         <v>14</v>
       </c>
       <c r="AD30" s="11">
@@ -3851,10 +3858,10 @@
       <c r="Z31" s="62">
         <v>8</v>
       </c>
-      <c r="AA31" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB31" s="90">
+      <c r="AA31" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB31" s="80">
         <v>14</v>
       </c>
       <c r="AD31" s="11">
@@ -3941,10 +3948,10 @@
       <c r="Z32" s="62">
         <v>8</v>
       </c>
-      <c r="AA32" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB32" s="90">
+      <c r="AA32" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB32" s="80">
         <v>14</v>
       </c>
       <c r="AD32" s="11">
@@ -4031,10 +4038,10 @@
       <c r="Z33" s="62">
         <v>8</v>
       </c>
-      <c r="AA33" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB33" s="90">
+      <c r="AA33" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB33" s="80">
         <v>14</v>
       </c>
       <c r="AD33" s="11">
@@ -4117,10 +4124,10 @@
       <c r="Z34" s="62">
         <v>8</v>
       </c>
-      <c r="AA34" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB34" s="90">
+      <c r="AA34" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB34" s="80">
         <v>14</v>
       </c>
       <c r="AD34" s="11">
@@ -4200,10 +4207,10 @@
       <c r="Z35" s="62">
         <v>8</v>
       </c>
-      <c r="AA35" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB35" s="90">
+      <c r="AA35" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB35" s="80">
         <v>14</v>
       </c>
       <c r="AD35" s="11">
@@ -4283,10 +4290,10 @@
       <c r="Z36" s="62">
         <v>8</v>
       </c>
-      <c r="AA36" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB36" s="90">
+      <c r="AA36" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB36" s="80">
         <v>14</v>
       </c>
       <c r="AD36" s="11">
@@ -4366,10 +4373,10 @@
       <c r="Z37" s="62">
         <v>8</v>
       </c>
-      <c r="AA37" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB37" s="90">
+      <c r="AA37" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB37" s="80">
         <v>14</v>
       </c>
       <c r="AD37" s="11">
@@ -4449,10 +4456,10 @@
       <c r="Z38" s="62">
         <v>8</v>
       </c>
-      <c r="AA38" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB38" s="90">
+      <c r="AA38" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB38" s="80">
         <v>14</v>
       </c>
       <c r="AD38" s="11">
@@ -4832,10 +4839,10 @@
       <c r="Z43" s="50">
         <v>12</v>
       </c>
-      <c r="AA43" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB43" s="89">
+      <c r="AA43" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB43" s="79">
         <v>14</v>
       </c>
       <c r="AD43" s="11">
@@ -4915,10 +4922,10 @@
       <c r="Z44" s="50">
         <v>12</v>
       </c>
-      <c r="AA44" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB44" s="89">
+      <c r="AA44" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB44" s="79">
         <v>14</v>
       </c>
       <c r="AD44" s="11">
@@ -4998,10 +5005,10 @@
       <c r="Z45" s="50">
         <v>12</v>
       </c>
-      <c r="AA45" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB45" s="89">
+      <c r="AA45" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB45" s="79">
         <v>14</v>
       </c>
       <c r="AD45" s="11">
@@ -5081,10 +5088,10 @@
       <c r="Z46" s="50">
         <v>12</v>
       </c>
-      <c r="AA46" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB46" s="89">
+      <c r="AA46" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB46" s="79">
         <v>14</v>
       </c>
       <c r="AD46" s="11">
@@ -5164,10 +5171,10 @@
       <c r="Z47" s="50">
         <v>12</v>
       </c>
-      <c r="AA47" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB47" s="89">
+      <c r="AA47" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB47" s="79">
         <v>14</v>
       </c>
       <c r="AD47" s="11">
@@ -5247,10 +5254,10 @@
       <c r="Z48" s="50">
         <v>12</v>
       </c>
-      <c r="AA48" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB48" s="89">
+      <c r="AA48" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB48" s="79">
         <v>14</v>
       </c>
       <c r="AD48" s="11">
@@ -5330,10 +5337,10 @@
       <c r="Z49" s="50">
         <v>12</v>
       </c>
-      <c r="AA49" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB49" s="89">
+      <c r="AA49" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB49" s="79">
         <v>14</v>
       </c>
       <c r="AD49" s="11">
@@ -5413,10 +5420,10 @@
       <c r="Z50" s="50">
         <v>12</v>
       </c>
-      <c r="AA50" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB50" s="89">
+      <c r="AA50" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB50" s="79">
         <v>14</v>
       </c>
       <c r="AD50" s="11">
@@ -5496,10 +5503,10 @@
       <c r="Z51" s="50">
         <v>12</v>
       </c>
-      <c r="AA51" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB51" s="89">
+      <c r="AA51" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB51" s="79">
         <v>14</v>
       </c>
       <c r="AD51" s="17">
@@ -5579,10 +5586,10 @@
       <c r="Z52" s="50">
         <v>12</v>
       </c>
-      <c r="AA52" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB52" s="89">
+      <c r="AA52" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB52" s="79">
         <v>14</v>
       </c>
     </row>
@@ -5656,10 +5663,10 @@
       <c r="Z53" s="50">
         <v>12</v>
       </c>
-      <c r="AA53" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB53" s="89">
+      <c r="AA53" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB53" s="79">
         <v>14</v>
       </c>
       <c r="AE53" s="20"/>
@@ -5737,10 +5744,10 @@
       <c r="Z54" s="50">
         <v>12</v>
       </c>
-      <c r="AA54" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB54" s="89">
+      <c r="AA54" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB54" s="79">
         <v>14</v>
       </c>
       <c r="AE54" s="20"/>
@@ -5818,10 +5825,10 @@
       <c r="Z55" s="50">
         <v>12</v>
       </c>
-      <c r="AA55" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB55" s="89">
+      <c r="AA55" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB55" s="79">
         <v>14</v>
       </c>
       <c r="AE55" s="20"/>
@@ -5899,10 +5906,10 @@
       <c r="Z56" s="50">
         <v>12</v>
       </c>
-      <c r="AA56" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB56" s="89">
+      <c r="AA56" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB56" s="79">
         <v>14</v>
       </c>
       <c r="AE56" s="9"/>
@@ -6648,10 +6655,10 @@
       <c r="O12" s="10"/>
       <c r="P12" s="10"/>
       <c r="Q12" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
@@ -6698,10 +6705,10 @@
       <c r="N13" s="11"/>
       <c r="O13" s="10"/>
       <c r="P13" s="10"/>
-      <c r="Q13" s="87" t="s">
-        <v>94</v>
-      </c>
-      <c r="R13" s="88"/>
+      <c r="Q13" s="82" t="s">
+        <v>93</v>
+      </c>
+      <c r="R13" s="83"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="11">
@@ -6734,14 +6741,14 @@
         <v>57</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="L14" s="26">
         <f>IF(LEN(User!AG14)=0,"",User!AG14)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14" s="11"/>
       <c r="N14" s="11"/>
@@ -6779,14 +6786,14 @@
         <v>57</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="L15" s="26">
         <f>IF(LEN(User!AG15)=0,"",User!AG15)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" s="11"/>
       <c r="N15" s="11"/>
@@ -6824,10 +6831,10 @@
         <v>57</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="L16" s="26">
         <f>IF(LEN(User!AG16)=0,"",User!AG16)</f>

--- a/tests/data/mock_b_and_t_cells_exp.xlsx
+++ b/tests/data/mock_b_and_t_cells_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabewilson/Desktop/worklist_generation/tests/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{471661DF-9C1C-0641-B062-566A46C4CC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D90A10F-E59C-B54A-932A-41D8AEEC6ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16860" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="User" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="106">
   <si>
     <t>Name:</t>
   </si>
@@ -312,6 +312,9 @@
     <t>tb</t>
   </si>
   <si>
+    <t>RA1</t>
+  </si>
+  <si>
     <t>Notes (not used):</t>
   </si>
   <si>
@@ -346,6 +349,9 @@
   </si>
   <si>
     <t>wetfile</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -1289,7 +1295,7 @@
         <v>4</v>
       </c>
       <c r="AH1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AM1" s="29"/>
       <c r="AO1" s="28"/>
@@ -1393,7 +1399,7 @@
         <v>30</v>
       </c>
       <c r="AJ4" s="6" t="s">
-        <v>31</v>
+        <v>105</v>
       </c>
       <c r="AK4" s="86" t="s">
         <v>32</v>
@@ -1498,11 +1504,13 @@
         <v>1</v>
       </c>
       <c r="AI5" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ5" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK5" s="86" t="s">
         <v>96</v>
-      </c>
-      <c r="AJ5" s="6"/>
-      <c r="AK5" s="86" t="s">
-        <v>95</v>
       </c>
       <c r="AL5" s="91"/>
       <c r="AM5" s="9"/>
@@ -1789,7 +1797,7 @@
         <v>1</v>
       </c>
       <c r="AI8" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AJ8" s="19" t="s">
         <v>33</v>
@@ -1891,7 +1899,7 @@
         <v>1</v>
       </c>
       <c r="AI9" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AJ9" s="6"/>
       <c r="AK9" s="90"/>
@@ -6655,10 +6663,10 @@
       <c r="O12" s="10"/>
       <c r="P12" s="10"/>
       <c r="Q12" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
@@ -6706,7 +6714,7 @@
       <c r="O13" s="10"/>
       <c r="P13" s="10"/>
       <c r="Q13" s="82" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="R13" s="83"/>
     </row>
@@ -6741,10 +6749,10 @@
         <v>57</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L14" s="26">
         <f>IF(LEN(User!AG14)=0,"",User!AG14)</f>
@@ -6786,10 +6794,10 @@
         <v>57</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L15" s="26">
         <f>IF(LEN(User!AG15)=0,"",User!AG15)</f>
@@ -6831,10 +6839,10 @@
         <v>57</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L16" s="26">
         <f>IF(LEN(User!AG16)=0,"",User!AG16)</f>

--- a/tests/data/mock_b_and_t_cells_exp.xlsx
+++ b/tests/data/mock_b_and_t_cells_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabewilson/Desktop/worklist_generation/tests/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D90A10F-E59C-B54A-932A-41D8AEEC6ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08775FB9-5446-8B40-B544-03095727BCB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16860" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="User" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="105">
   <si>
     <t>Name:</t>
   </si>
@@ -349,9 +349,6 @@
   </si>
   <si>
     <t>wetfile</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
 </sst>
 </file>
@@ -1399,7 +1396,7 @@
         <v>30</v>
       </c>
       <c r="AJ4" s="6" t="s">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="AK4" s="86" t="s">
         <v>32</v>

--- a/tests/data/mock_b_and_t_cells_exp.xlsx
+++ b/tests/data/mock_b_and_t_cells_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabewilson/Desktop/worklist_generation/tests/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08775FB9-5446-8B40-B544-03095727BCB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD253007-A02B-8D4B-A7B2-4EF984686F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16860" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="User" sheetId="1" r:id="rId1"/>

--- a/tests/data/mock_b_and_t_cells_exp.xlsx
+++ b/tests/data/mock_b_and_t_cells_exp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabewilson/Desktop/worklist_generation/tests/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/01c1829094dbd390/Desktop/Kelly_Lab/.venv/worklist_git/tests/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B022A0-875C-C14E-8E37-79CB7BA39312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14680" yWindow="700" windowWidth="14720" windowHeight="16940" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="User" sheetId="1" r:id="rId1"/>
@@ -857,6 +857,21 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -872,21 +887,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1237,7 +1237,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AU63"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="15.6640625" customWidth="1"/>
@@ -1260,7 +1260,7 @@
     <col min="43" max="45" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1285,7 +1285,7 @@
       <c r="AM1" s="29"/>
       <c r="AO1" s="28"/>
     </row>
-    <row r="2" spans="1:47" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:47" ht="16" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1312,7 +1312,7 @@
       <c r="AN2" s="9"/>
       <c r="AO2" s="28"/>
     </row>
-    <row r="3" spans="1:47" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:47" ht="16" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1340,7 +1340,7 @@
       <c r="AO3" s="28"/>
       <c r="AU3" s="21"/>
     </row>
-    <row r="4" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:47" x14ac:dyDescent="0.4">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="D4" s="3"/>
@@ -1386,15 +1386,15 @@
       <c r="AJ4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AK4" s="81" t="s">
+      <c r="AK4" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="AL4" s="82"/>
+      <c r="AL4" s="87"/>
       <c r="AM4" s="9"/>
       <c r="AN4" s="9"/>
       <c r="AO4" s="28"/>
     </row>
-    <row r="5" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:47" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
@@ -1494,15 +1494,15 @@
       <c r="AJ5" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="AK5" s="81" t="s">
+      <c r="AK5" s="86" t="s">
         <v>96</v>
       </c>
-      <c r="AL5" s="86"/>
+      <c r="AL5" s="91"/>
       <c r="AM5" s="9"/>
       <c r="AN5" s="9"/>
       <c r="AO5" s="28"/>
     </row>
-    <row r="6" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:47" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
@@ -1601,7 +1601,7 @@
       <c r="AN6" s="9"/>
       <c r="AO6" s="28"/>
     </row>
-    <row r="7" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:47" x14ac:dyDescent="0.4">
       <c r="D7" t="s">
         <v>14</v>
       </c>
@@ -1671,10 +1671,10 @@
       <c r="Z7" s="42">
         <v>4</v>
       </c>
-      <c r="AA7" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB7" s="89">
+      <c r="AA7" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB7" s="79">
         <v>14</v>
       </c>
       <c r="AD7" s="11">
@@ -1693,7 +1693,7 @@
       <c r="AN7" s="9"/>
       <c r="AO7" s="28"/>
     </row>
-    <row r="8" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:47" x14ac:dyDescent="0.4">
       <c r="D8" t="s">
         <v>15</v>
       </c>
@@ -1763,10 +1763,10 @@
       <c r="Z8" s="42">
         <v>4</v>
       </c>
-      <c r="AA8" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB8" s="89">
+      <c r="AA8" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB8" s="79">
         <v>14</v>
       </c>
       <c r="AD8" s="11">
@@ -1787,15 +1787,15 @@
       <c r="AJ8" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="AK8" s="81" t="s">
+      <c r="AK8" s="86" t="s">
         <v>34</v>
       </c>
-      <c r="AL8" s="82"/>
+      <c r="AL8" s="87"/>
       <c r="AM8" s="9"/>
       <c r="AN8" s="9"/>
       <c r="AO8" s="28"/>
     </row>
-    <row r="9" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:47" x14ac:dyDescent="0.4">
       <c r="D9" t="s">
         <v>16</v>
       </c>
@@ -1865,10 +1865,10 @@
       <c r="Z9" s="42">
         <v>4</v>
       </c>
-      <c r="AA9" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB9" s="89">
+      <c r="AA9" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB9" s="79">
         <v>14</v>
       </c>
       <c r="AD9" s="11">
@@ -1887,13 +1887,13 @@
         <v>99</v>
       </c>
       <c r="AJ9" s="6"/>
-      <c r="AK9" s="85"/>
-      <c r="AL9" s="82"/>
+      <c r="AK9" s="90"/>
+      <c r="AL9" s="87"/>
       <c r="AM9" s="9"/>
       <c r="AN9" s="9"/>
       <c r="AO9" s="28"/>
     </row>
-    <row r="10" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:47" x14ac:dyDescent="0.4">
       <c r="D10" t="s">
         <v>17</v>
       </c>
@@ -1963,10 +1963,10 @@
       <c r="Z10" s="42">
         <v>4</v>
       </c>
-      <c r="AA10" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB10" s="89">
+      <c r="AA10" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB10" s="79">
         <v>14</v>
       </c>
       <c r="AD10" s="11">
@@ -1981,19 +1981,19 @@
       <c r="AG10" s="26">
         <v>1</v>
       </c>
-      <c r="AI10" s="83" t="s">
+      <c r="AI10" s="88" t="s">
         <v>35</v>
       </c>
-      <c r="AJ10" s="79" t="s">
+      <c r="AJ10" s="84" t="s">
         <v>31</v>
       </c>
-      <c r="AK10" s="85"/>
-      <c r="AL10" s="82"/>
+      <c r="AK10" s="90"/>
+      <c r="AL10" s="87"/>
       <c r="AM10" s="9"/>
       <c r="AN10" s="9"/>
       <c r="AO10" s="28"/>
     </row>
-    <row r="11" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:47" x14ac:dyDescent="0.4">
       <c r="D11" t="s">
         <v>18</v>
       </c>
@@ -2063,10 +2063,10 @@
       <c r="Z11" s="42">
         <v>4</v>
       </c>
-      <c r="AA11" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB11" s="89">
+      <c r="AA11" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB11" s="79">
         <v>14</v>
       </c>
       <c r="AD11" s="11">
@@ -2081,15 +2081,15 @@
       <c r="AG11" s="26">
         <v>1</v>
       </c>
-      <c r="AI11" s="84"/>
-      <c r="AJ11" s="80"/>
+      <c r="AI11" s="89"/>
+      <c r="AJ11" s="85"/>
       <c r="AK11" s="30"/>
       <c r="AL11" s="30"/>
       <c r="AM11" s="9"/>
       <c r="AN11" s="9"/>
       <c r="AO11" s="28"/>
     </row>
-    <row r="12" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:47" x14ac:dyDescent="0.4">
       <c r="D12" t="s">
         <v>19</v>
       </c>
@@ -2159,10 +2159,10 @@
       <c r="Z12" s="42">
         <v>4</v>
       </c>
-      <c r="AA12" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB12" s="89">
+      <c r="AA12" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB12" s="79">
         <v>14</v>
       </c>
       <c r="AD12" s="11">
@@ -2185,7 +2185,7 @@
       <c r="AN12" s="9"/>
       <c r="AO12" s="28"/>
     </row>
-    <row r="13" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:47" x14ac:dyDescent="0.4">
       <c r="D13" t="s">
         <v>20</v>
       </c>
@@ -2255,10 +2255,10 @@
       <c r="Z13" s="42">
         <v>4</v>
       </c>
-      <c r="AA13" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB13" s="89">
+      <c r="AA13" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB13" s="79">
         <v>14</v>
       </c>
       <c r="AD13" s="11">
@@ -2281,7 +2281,7 @@
       <c r="AN13" s="9"/>
       <c r="AO13" s="28"/>
     </row>
-    <row r="14" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:47" x14ac:dyDescent="0.4">
       <c r="D14" t="s">
         <v>21</v>
       </c>
@@ -2351,10 +2351,10 @@
       <c r="Z14" s="42">
         <v>4</v>
       </c>
-      <c r="AA14" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB14" s="89">
+      <c r="AA14" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB14" s="79">
         <v>14</v>
       </c>
       <c r="AD14" s="11">
@@ -2377,7 +2377,7 @@
       <c r="AN14" s="9"/>
       <c r="AO14" s="28"/>
     </row>
-    <row r="15" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:47" x14ac:dyDescent="0.4">
       <c r="D15" t="s">
         <v>22</v>
       </c>
@@ -2447,10 +2447,10 @@
       <c r="Z15" s="42">
         <v>4</v>
       </c>
-      <c r="AA15" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB15" s="89">
+      <c r="AA15" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB15" s="79">
         <v>14</v>
       </c>
       <c r="AD15" s="11">
@@ -2459,7 +2459,7 @@
       <c r="AE15" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AF15" s="91" t="s">
+      <c r="AF15" s="81" t="s">
         <v>72</v>
       </c>
       <c r="AG15" s="26">
@@ -2473,7 +2473,7 @@
       <c r="AN15" s="9"/>
       <c r="AO15" s="28"/>
     </row>
-    <row r="16" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:47" x14ac:dyDescent="0.4">
       <c r="D16" t="s">
         <v>23</v>
       </c>
@@ -2543,10 +2543,10 @@
       <c r="Z16" s="42">
         <v>4</v>
       </c>
-      <c r="AA16" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB16" s="89">
+      <c r="AA16" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB16" s="79">
         <v>14</v>
       </c>
       <c r="AD16" s="11">
@@ -2569,7 +2569,7 @@
       <c r="AN16" s="9"/>
       <c r="AO16" s="28"/>
     </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D17" t="s">
         <v>24</v>
       </c>
@@ -2639,10 +2639,10 @@
       <c r="Z17" s="42">
         <v>4</v>
       </c>
-      <c r="AA17" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB17" s="89">
+      <c r="AA17" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB17" s="79">
         <v>14</v>
       </c>
       <c r="AD17" s="11">
@@ -2664,7 +2664,7 @@
       <c r="AN17" s="9"/>
       <c r="AO17" s="28"/>
     </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D18" t="s">
         <v>25</v>
       </c>
@@ -2734,10 +2734,10 @@
       <c r="Z18" s="42">
         <v>4</v>
       </c>
-      <c r="AA18" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB18" s="89">
+      <c r="AA18" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB18" s="79">
         <v>14</v>
       </c>
       <c r="AD18" s="11">
@@ -2753,7 +2753,7 @@
       <c r="AN18" s="9"/>
       <c r="AO18" s="28"/>
     </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D19" t="s">
         <v>26</v>
       </c>
@@ -2823,10 +2823,10 @@
       <c r="Z19" s="42">
         <v>4</v>
       </c>
-      <c r="AA19" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB19" s="89">
+      <c r="AA19" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB19" s="79">
         <v>14</v>
       </c>
       <c r="AD19" s="11">
@@ -2839,7 +2839,7 @@
       <c r="AN19" s="9"/>
       <c r="AO19" s="28"/>
     </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D20" t="s">
         <v>27</v>
       </c>
@@ -2909,10 +2909,10 @@
       <c r="Z20" s="42">
         <v>4</v>
       </c>
-      <c r="AA20" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB20" s="89">
+      <c r="AA20" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB20" s="79">
         <v>14</v>
       </c>
       <c r="AD20" s="11">
@@ -2925,7 +2925,7 @@
       <c r="AN20" s="9"/>
       <c r="AO20" s="28"/>
     </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D21" t="s">
         <v>28</v>
       </c>
@@ -3011,7 +3011,7 @@
       <c r="AN21" s="9"/>
       <c r="AO21" s="28"/>
     </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="D22" s="3"/>
@@ -3049,7 +3049,7 @@
       <c r="AN22" s="9"/>
       <c r="AO22" s="28"/>
     </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A23" s="4" t="s">
         <v>9</v>
       </c>
@@ -3145,7 +3145,7 @@
       <c r="AN23" s="9"/>
       <c r="AO23" s="28"/>
     </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A24" s="12" t="s">
         <v>19</v>
       </c>
@@ -3241,7 +3241,7 @@
       <c r="AN24" s="9"/>
       <c r="AO24" s="28"/>
     </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D25" t="s">
         <v>14</v>
       </c>
@@ -3311,10 +3311,10 @@
       <c r="Z25" s="62">
         <v>8</v>
       </c>
-      <c r="AA25" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB25" s="90">
+      <c r="AA25" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB25" s="80">
         <v>14</v>
       </c>
       <c r="AD25" s="11">
@@ -3331,7 +3331,7 @@
       <c r="AN25" s="9"/>
       <c r="AO25" s="28"/>
     </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D26" t="s">
         <v>15</v>
       </c>
@@ -3401,10 +3401,10 @@
       <c r="Z26" s="62">
         <v>8</v>
       </c>
-      <c r="AA26" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB26" s="90">
+      <c r="AA26" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB26" s="80">
         <v>14</v>
       </c>
       <c r="AD26" s="11">
@@ -3421,7 +3421,7 @@
       <c r="AN26" s="9"/>
       <c r="AO26" s="28"/>
     </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D27" t="s">
         <v>16</v>
       </c>
@@ -3491,10 +3491,10 @@
       <c r="Z27" s="62">
         <v>8</v>
       </c>
-      <c r="AA27" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB27" s="90">
+      <c r="AA27" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB27" s="80">
         <v>14</v>
       </c>
       <c r="AD27" s="11">
@@ -3511,7 +3511,7 @@
       <c r="AN27" s="9"/>
       <c r="AO27" s="28"/>
     </row>
-    <row r="28" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D28" t="s">
         <v>17</v>
       </c>
@@ -3581,10 +3581,10 @@
       <c r="Z28" s="62">
         <v>8</v>
       </c>
-      <c r="AA28" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB28" s="90">
+      <c r="AA28" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB28" s="80">
         <v>14</v>
       </c>
       <c r="AD28" s="11">
@@ -3601,7 +3601,7 @@
       <c r="AN28" s="9"/>
       <c r="AO28" s="28"/>
     </row>
-    <row r="29" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D29" t="s">
         <v>18</v>
       </c>
@@ -3671,10 +3671,10 @@
       <c r="Z29" s="62">
         <v>8</v>
       </c>
-      <c r="AA29" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB29" s="90">
+      <c r="AA29" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB29" s="80">
         <v>14</v>
       </c>
       <c r="AD29" s="11">
@@ -3691,7 +3691,7 @@
       <c r="AN29" s="9"/>
       <c r="AO29" s="28"/>
     </row>
-    <row r="30" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D30" t="s">
         <v>19</v>
       </c>
@@ -3761,10 +3761,10 @@
       <c r="Z30" s="62">
         <v>8</v>
       </c>
-      <c r="AA30" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB30" s="90">
+      <c r="AA30" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB30" s="80">
         <v>14</v>
       </c>
       <c r="AD30" s="11">
@@ -3781,7 +3781,7 @@
       <c r="AN30" s="9"/>
       <c r="AO30" s="28"/>
     </row>
-    <row r="31" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D31" t="s">
         <v>20</v>
       </c>
@@ -3851,10 +3851,10 @@
       <c r="Z31" s="62">
         <v>8</v>
       </c>
-      <c r="AA31" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB31" s="90">
+      <c r="AA31" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB31" s="80">
         <v>14</v>
       </c>
       <c r="AD31" s="11">
@@ -3871,7 +3871,7 @@
       <c r="AN31" s="9"/>
       <c r="AO31" s="28"/>
     </row>
-    <row r="32" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D32" t="s">
         <v>21</v>
       </c>
@@ -3941,10 +3941,10 @@
       <c r="Z32" s="62">
         <v>8</v>
       </c>
-      <c r="AA32" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB32" s="90">
+      <c r="AA32" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB32" s="80">
         <v>14</v>
       </c>
       <c r="AD32" s="11">
@@ -3961,7 +3961,7 @@
       <c r="AN32" s="9"/>
       <c r="AO32" s="28"/>
     </row>
-    <row r="33" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D33" t="s">
         <v>22</v>
       </c>
@@ -4031,10 +4031,10 @@
       <c r="Z33" s="62">
         <v>8</v>
       </c>
-      <c r="AA33" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB33" s="90">
+      <c r="AA33" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB33" s="80">
         <v>14</v>
       </c>
       <c r="AD33" s="11">
@@ -4047,7 +4047,7 @@
       <c r="AN33" s="9"/>
       <c r="AO33" s="28"/>
     </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D34" t="s">
         <v>23</v>
       </c>
@@ -4117,10 +4117,10 @@
       <c r="Z34" s="62">
         <v>8</v>
       </c>
-      <c r="AA34" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB34" s="90">
+      <c r="AA34" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB34" s="80">
         <v>14</v>
       </c>
       <c r="AD34" s="11">
@@ -4130,7 +4130,7 @@
       <c r="AF34" s="10"/>
       <c r="AG34" s="10"/>
     </row>
-    <row r="35" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D35" t="s">
         <v>24</v>
       </c>
@@ -4200,10 +4200,10 @@
       <c r="Z35" s="62">
         <v>8</v>
       </c>
-      <c r="AA35" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB35" s="90">
+      <c r="AA35" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB35" s="80">
         <v>14</v>
       </c>
       <c r="AD35" s="11">
@@ -4213,7 +4213,7 @@
       <c r="AF35" s="10"/>
       <c r="AG35" s="10"/>
     </row>
-    <row r="36" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D36" t="s">
         <v>25</v>
       </c>
@@ -4283,10 +4283,10 @@
       <c r="Z36" s="62">
         <v>8</v>
       </c>
-      <c r="AA36" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB36" s="90">
+      <c r="AA36" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB36" s="80">
         <v>14</v>
       </c>
       <c r="AD36" s="11">
@@ -4296,7 +4296,7 @@
       <c r="AF36" s="10"/>
       <c r="AG36" s="10"/>
     </row>
-    <row r="37" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D37" t="s">
         <v>26</v>
       </c>
@@ -4366,10 +4366,10 @@
       <c r="Z37" s="62">
         <v>8</v>
       </c>
-      <c r="AA37" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB37" s="90">
+      <c r="AA37" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB37" s="80">
         <v>14</v>
       </c>
       <c r="AD37" s="11">
@@ -4379,7 +4379,7 @@
       <c r="AF37" s="10"/>
       <c r="AG37" s="10"/>
     </row>
-    <row r="38" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D38" t="s">
         <v>27</v>
       </c>
@@ -4449,10 +4449,10 @@
       <c r="Z38" s="62">
         <v>8</v>
       </c>
-      <c r="AA38" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB38" s="90">
+      <c r="AA38" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB38" s="80">
         <v>14</v>
       </c>
       <c r="AD38" s="11">
@@ -4462,7 +4462,7 @@
       <c r="AF38" s="10"/>
       <c r="AG38" s="10"/>
     </row>
-    <row r="39" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D39" t="s">
         <v>28</v>
       </c>
@@ -4545,7 +4545,7 @@
       <c r="AF39" s="10"/>
       <c r="AG39" s="10"/>
     </row>
-    <row r="40" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="D40" s="3"/>
@@ -4582,7 +4582,7 @@
       <c r="AJ40" s="30"/>
       <c r="AK40" s="30"/>
     </row>
-    <row r="41" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A41" s="4" t="s">
         <v>9</v>
       </c>
@@ -4673,7 +4673,7 @@
       <c r="AJ41" s="30"/>
       <c r="AK41" s="30"/>
     </row>
-    <row r="42" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A42" s="12" t="s">
         <v>14</v>
       </c>
@@ -4762,7 +4762,7 @@
       <c r="AF42" s="10"/>
       <c r="AG42" s="10"/>
     </row>
-    <row r="43" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D43" t="s">
         <v>14</v>
       </c>
@@ -4832,10 +4832,10 @@
       <c r="Z43" s="50">
         <v>12</v>
       </c>
-      <c r="AA43" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB43" s="89">
+      <c r="AA43" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB43" s="79">
         <v>14</v>
       </c>
       <c r="AD43" s="11">
@@ -4845,7 +4845,7 @@
       <c r="AF43" s="10"/>
       <c r="AG43" s="10"/>
     </row>
-    <row r="44" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D44" t="s">
         <v>15</v>
       </c>
@@ -4915,10 +4915,10 @@
       <c r="Z44" s="50">
         <v>12</v>
       </c>
-      <c r="AA44" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB44" s="89">
+      <c r="AA44" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB44" s="79">
         <v>14</v>
       </c>
       <c r="AD44" s="11">
@@ -4928,7 +4928,7 @@
       <c r="AF44" s="10"/>
       <c r="AG44" s="10"/>
     </row>
-    <row r="45" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D45" t="s">
         <v>16</v>
       </c>
@@ -4998,10 +4998,10 @@
       <c r="Z45" s="50">
         <v>12</v>
       </c>
-      <c r="AA45" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB45" s="89">
+      <c r="AA45" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB45" s="79">
         <v>14</v>
       </c>
       <c r="AD45" s="11">
@@ -5011,7 +5011,7 @@
       <c r="AF45" s="10"/>
       <c r="AG45" s="10"/>
     </row>
-    <row r="46" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D46" t="s">
         <v>17</v>
       </c>
@@ -5081,10 +5081,10 @@
       <c r="Z46" s="50">
         <v>12</v>
       </c>
-      <c r="AA46" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB46" s="89">
+      <c r="AA46" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB46" s="79">
         <v>14</v>
       </c>
       <c r="AD46" s="11">
@@ -5094,7 +5094,7 @@
       <c r="AF46" s="10"/>
       <c r="AG46" s="10"/>
     </row>
-    <row r="47" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D47" t="s">
         <v>18</v>
       </c>
@@ -5164,10 +5164,10 @@
       <c r="Z47" s="50">
         <v>12</v>
       </c>
-      <c r="AA47" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB47" s="89">
+      <c r="AA47" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB47" s="79">
         <v>14</v>
       </c>
       <c r="AD47" s="11">
@@ -5177,7 +5177,7 @@
       <c r="AF47" s="10"/>
       <c r="AG47" s="10"/>
     </row>
-    <row r="48" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:41" x14ac:dyDescent="0.4">
       <c r="D48" t="s">
         <v>19</v>
       </c>
@@ -5247,10 +5247,10 @@
       <c r="Z48" s="50">
         <v>12</v>
       </c>
-      <c r="AA48" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB48" s="89">
+      <c r="AA48" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB48" s="79">
         <v>14</v>
       </c>
       <c r="AD48" s="11">
@@ -5260,7 +5260,7 @@
       <c r="AF48" s="24"/>
       <c r="AG48" s="10"/>
     </row>
-    <row r="49" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:40" x14ac:dyDescent="0.4">
       <c r="D49" t="s">
         <v>20</v>
       </c>
@@ -5330,10 +5330,10 @@
       <c r="Z49" s="50">
         <v>12</v>
       </c>
-      <c r="AA49" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB49" s="89">
+      <c r="AA49" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB49" s="79">
         <v>14</v>
       </c>
       <c r="AD49" s="11">
@@ -5343,7 +5343,7 @@
       <c r="AF49" s="24"/>
       <c r="AG49" s="10"/>
     </row>
-    <row r="50" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:40" x14ac:dyDescent="0.4">
       <c r="D50" t="s">
         <v>21</v>
       </c>
@@ -5413,10 +5413,10 @@
       <c r="Z50" s="50">
         <v>12</v>
       </c>
-      <c r="AA50" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB50" s="89">
+      <c r="AA50" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB50" s="79">
         <v>14</v>
       </c>
       <c r="AD50" s="11">
@@ -5426,7 +5426,7 @@
       <c r="AF50" s="24"/>
       <c r="AG50" s="10"/>
     </row>
-    <row r="51" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:40" x14ac:dyDescent="0.4">
       <c r="D51" t="s">
         <v>22</v>
       </c>
@@ -5496,10 +5496,10 @@
       <c r="Z51" s="50">
         <v>12</v>
       </c>
-      <c r="AA51" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB51" s="89">
+      <c r="AA51" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB51" s="79">
         <v>14</v>
       </c>
       <c r="AD51" s="17">
@@ -5509,7 +5509,7 @@
       <c r="AF51" s="18"/>
       <c r="AG51" s="18"/>
     </row>
-    <row r="52" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:40" x14ac:dyDescent="0.4">
       <c r="D52" t="s">
         <v>23</v>
       </c>
@@ -5579,14 +5579,14 @@
       <c r="Z52" s="50">
         <v>12</v>
       </c>
-      <c r="AA52" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB52" s="89">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="AA52" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB52" s="79">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:40" x14ac:dyDescent="0.4">
       <c r="D53" t="s">
         <v>24</v>
       </c>
@@ -5656,10 +5656,10 @@
       <c r="Z53" s="50">
         <v>12</v>
       </c>
-      <c r="AA53" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB53" s="89">
+      <c r="AA53" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB53" s="79">
         <v>14</v>
       </c>
       <c r="AE53" s="20"/>
@@ -5667,7 +5667,7 @@
       <c r="AM53" s="20"/>
       <c r="AN53" s="20"/>
     </row>
-    <row r="54" spans="1:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:40" ht="16" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D54" t="s">
         <v>25</v>
       </c>
@@ -5737,10 +5737,10 @@
       <c r="Z54" s="50">
         <v>12</v>
       </c>
-      <c r="AA54" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB54" s="89">
+      <c r="AA54" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB54" s="79">
         <v>14</v>
       </c>
       <c r="AE54" s="20"/>
@@ -5748,7 +5748,7 @@
       <c r="AM54" s="20"/>
       <c r="AN54" s="20"/>
     </row>
-    <row r="55" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:40" x14ac:dyDescent="0.4">
       <c r="D55" t="s">
         <v>26</v>
       </c>
@@ -5818,10 +5818,10 @@
       <c r="Z55" s="50">
         <v>12</v>
       </c>
-      <c r="AA55" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB55" s="89">
+      <c r="AA55" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB55" s="79">
         <v>14</v>
       </c>
       <c r="AE55" s="20"/>
@@ -5829,7 +5829,7 @@
       <c r="AM55" s="20"/>
       <c r="AN55" s="20"/>
     </row>
-    <row r="56" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:40" x14ac:dyDescent="0.4">
       <c r="D56" t="s">
         <v>27</v>
       </c>
@@ -5899,15 +5899,15 @@
       <c r="Z56" s="50">
         <v>12</v>
       </c>
-      <c r="AA56" s="89">
-        <v>14</v>
-      </c>
-      <c r="AB56" s="89">
+      <c r="AA56" s="79">
+        <v>14</v>
+      </c>
+      <c r="AB56" s="79">
         <v>14</v>
       </c>
       <c r="AE56" s="9"/>
     </row>
-    <row r="57" spans="1:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:40" ht="16" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D57" t="s">
         <v>28</v>
       </c>
@@ -5989,7 +5989,7 @@
       <c r="AM57" s="20"/>
       <c r="AN57" s="20"/>
     </row>
-    <row r="58" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:40" x14ac:dyDescent="0.4">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="D58" s="3"/>
@@ -6023,23 +6023,23 @@
       <c r="AM58" s="20"/>
       <c r="AN58" s="20"/>
     </row>
-    <row r="59" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:40" x14ac:dyDescent="0.4">
       <c r="AE59" s="9"/>
       <c r="AK59" s="20"/>
       <c r="AL59" s="21"/>
       <c r="AM59" s="20"/>
       <c r="AN59" s="20"/>
     </row>
-    <row r="60" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:40" x14ac:dyDescent="0.4">
       <c r="AE60" s="9"/>
     </row>
-    <row r="61" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:40" x14ac:dyDescent="0.4">
       <c r="AE61" s="9"/>
     </row>
-    <row r="62" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:40" x14ac:dyDescent="0.4">
       <c r="AE62" s="9"/>
     </row>
-    <row r="63" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:40" x14ac:dyDescent="0.4">
       <c r="AE63" s="9"/>
     </row>
   </sheetData>
@@ -6069,7 +6069,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="14" max="16" width="10.6640625" customWidth="1"/>
     <col min="17" max="17" width="30.83203125" customWidth="1"/>
@@ -6077,7 +6077,7 @@
     <col min="19" max="19" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -6127,7 +6127,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A2" s="11">
         <v>1</v>
       </c>
@@ -6178,7 +6178,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A3" s="11">
         <v>2</v>
       </c>
@@ -6223,7 +6223,7 @@
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A4" s="11">
         <v>3</v>
       </c>
@@ -6270,7 +6270,7 @@
       <c r="Q4" s="20"/>
       <c r="R4" s="21"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A5" s="11">
         <v>4</v>
       </c>
@@ -6321,7 +6321,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A6" s="11">
         <v>5</v>
       </c>
@@ -6366,7 +6366,7 @@
       <c r="O6" s="10"/>
       <c r="P6" s="10"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A7" s="11">
         <v>6</v>
       </c>
@@ -6411,7 +6411,7 @@
       <c r="O7" s="10"/>
       <c r="P7" s="10"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A8" s="11">
         <v>7</v>
       </c>
@@ -6462,7 +6462,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A9" s="11">
         <v>8</v>
       </c>
@@ -6513,7 +6513,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A10" s="11">
         <v>9</v>
       </c>
@@ -6558,7 +6558,7 @@
       <c r="O10" s="10"/>
       <c r="P10" s="10"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A11" s="11">
         <v>10</v>
       </c>
@@ -6603,7 +6603,7 @@
       <c r="O11" s="10"/>
       <c r="P11" s="10"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A12" s="11">
         <v>11</v>
       </c>
@@ -6654,7 +6654,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A13" s="11">
         <v>12</v>
       </c>
@@ -6698,12 +6698,12 @@
       <c r="N13" s="11"/>
       <c r="O13" s="10"/>
       <c r="P13" s="10"/>
-      <c r="Q13" s="87" t="s">
+      <c r="Q13" s="82" t="s">
         <v>94</v>
       </c>
-      <c r="R13" s="88"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="83"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A14" s="11">
         <v>13</v>
       </c>
@@ -6748,7 +6748,7 @@
       <c r="O14" s="10"/>
       <c r="P14" s="10"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A15" s="11">
         <v>14</v>
       </c>
@@ -6793,7 +6793,7 @@
       <c r="O15" s="10"/>
       <c r="P15" s="10"/>
     </row>
-    <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="11">
         <v>15</v>
       </c>
@@ -6838,7 +6838,7 @@
       <c r="O16" s="10"/>
       <c r="P16" s="10"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A17" s="11">
         <v>16</v>
       </c>
@@ -6883,7 +6883,7 @@
       <c r="O17" s="10"/>
       <c r="P17" s="10"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A18" s="11">
         <v>17</v>
       </c>
@@ -6909,7 +6909,7 @@
       <c r="O18" s="10"/>
       <c r="P18" s="10"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A19" s="11">
         <v>18</v>
       </c>
@@ -6938,7 +6938,7 @@
       <c r="O19" s="10"/>
       <c r="P19" s="10"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A20" s="11">
         <v>19</v>
       </c>
@@ -6967,7 +6967,7 @@
       <c r="O20" s="10"/>
       <c r="P20" s="10"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A21" s="11">
         <v>20</v>
       </c>
@@ -6996,7 +6996,7 @@
       <c r="O21" s="10"/>
       <c r="P21" s="10"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A22" s="11">
         <v>21</v>
       </c>
@@ -7025,7 +7025,7 @@
       <c r="O22" s="10"/>
       <c r="P22" s="10"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A23" s="11">
         <v>22</v>
       </c>
@@ -7054,7 +7054,7 @@
       <c r="O23" s="10"/>
       <c r="P23" s="10"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A24" s="11">
         <v>23</v>
       </c>
@@ -7083,7 +7083,7 @@
       <c r="O24" s="10"/>
       <c r="P24" s="10"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A25" s="11">
         <v>24</v>
       </c>
@@ -7112,7 +7112,7 @@
       <c r="O25" s="10"/>
       <c r="P25" s="10"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A26" s="11">
         <v>25</v>
       </c>
@@ -7141,7 +7141,7 @@
       <c r="O26" s="10"/>
       <c r="P26" s="10"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A27" s="11">
         <v>26</v>
       </c>
@@ -7170,7 +7170,7 @@
       <c r="O27" s="10"/>
       <c r="P27" s="10"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A28" s="11">
         <v>27</v>
       </c>
@@ -7199,7 +7199,7 @@
       <c r="O28" s="10"/>
       <c r="P28" s="10"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A29" s="11">
         <v>28</v>
       </c>
@@ -7228,7 +7228,7 @@
       <c r="O29" s="10"/>
       <c r="P29" s="10"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A30" s="11">
         <v>29</v>
       </c>
@@ -7257,7 +7257,7 @@
       <c r="O30" s="10"/>
       <c r="P30" s="10"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A31" s="11">
         <v>30</v>
       </c>
@@ -7286,7 +7286,7 @@
       <c r="O31" s="10"/>
       <c r="P31" s="10"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A32" s="11">
         <v>31</v>
       </c>
@@ -7315,7 +7315,7 @@
       <c r="O32" s="10"/>
       <c r="P32" s="10"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A33" s="11">
         <v>32</v>
       </c>
@@ -7344,7 +7344,7 @@
       <c r="O33" s="10"/>
       <c r="P33" s="10"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A34" s="11">
         <v>33</v>
       </c>
@@ -7373,7 +7373,7 @@
       <c r="O34" s="10"/>
       <c r="P34" s="10"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A35" s="11">
         <v>34</v>
       </c>
@@ -7402,7 +7402,7 @@
       <c r="O35" s="10"/>
       <c r="P35" s="10"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A36" s="11">
         <v>35</v>
       </c>
@@ -7430,7 +7430,7 @@
       <c r="O36" s="10"/>
       <c r="P36" s="10"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A37" s="11">
         <v>36</v>
       </c>
@@ -7459,7 +7459,7 @@
       <c r="O37" s="10"/>
       <c r="P37" s="10"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A38" s="11">
         <v>37</v>
       </c>
@@ -7488,7 +7488,7 @@
       <c r="O38" s="10"/>
       <c r="P38" s="10"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A39" s="11">
         <v>38</v>
       </c>
@@ -7517,7 +7517,7 @@
       <c r="O39" s="10"/>
       <c r="P39" s="10"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A40" s="11">
         <v>39</v>
       </c>
@@ -7546,7 +7546,7 @@
       <c r="O40" s="10"/>
       <c r="P40" s="10"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A41" s="11">
         <v>40</v>
       </c>
@@ -7575,7 +7575,7 @@
       <c r="O41" s="10"/>
       <c r="P41" s="10"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A42" s="11">
         <v>41</v>
       </c>
@@ -7604,7 +7604,7 @@
       <c r="O42" s="10"/>
       <c r="P42" s="10"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A43" s="11">
         <v>42</v>
       </c>
@@ -7633,7 +7633,7 @@
       <c r="O43" s="10"/>
       <c r="P43" s="10"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A44" s="11">
         <v>43</v>
       </c>
@@ -7662,7 +7662,7 @@
       <c r="O44" s="10"/>
       <c r="P44" s="10"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A45" s="11">
         <v>44</v>
       </c>
@@ -7691,7 +7691,7 @@
       <c r="O45" s="10"/>
       <c r="P45" s="10"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A46" s="11">
         <v>45</v>
       </c>
@@ -7720,7 +7720,7 @@
       <c r="O46" s="10"/>
       <c r="P46" s="10"/>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A47" s="11">
         <v>46</v>
       </c>
@@ -7749,7 +7749,7 @@
       <c r="O47" s="10"/>
       <c r="P47" s="10"/>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A48" s="11">
         <v>47</v>
       </c>
@@ -7778,7 +7778,7 @@
       <c r="O48" s="10"/>
       <c r="P48" s="10"/>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A49" s="11">
         <v>48</v>
       </c>
@@ -7807,7 +7807,7 @@
       <c r="O49" s="10"/>
       <c r="P49" s="10"/>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A50" s="11">
         <v>49</v>
       </c>
@@ -7836,7 +7836,7 @@
       <c r="O50" s="10"/>
       <c r="P50" s="10"/>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A51" s="17">
         <v>50</v>
       </c>

--- a/tests/data/mock_b_and_t_cells_exp.xlsx
+++ b/tests/data/mock_b_and_t_cells_exp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/01c1829094dbd390/Desktop/Kelly_Lab/.venv/worklist_git/tests/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B022A0-875C-C14E-8E37-79CB7BA39312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{C1B022A0-875C-C14E-8E37-79CB7BA39312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3C593DA-1A19-45D9-9B43-F23588EF2473}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="190" windowWidth="19420" windowHeight="11920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="User" sheetId="1" r:id="rId1"/>
@@ -255,15 +255,6 @@
     <t>hyeb</t>
   </si>
   <si>
-    <t>Nonsample before:</t>
-  </si>
-  <si>
-    <t>Nonsample after:</t>
-  </si>
-  <si>
-    <t>Nonsample between:</t>
-  </si>
-  <si>
     <t>Frequency of system validation (#):</t>
   </si>
   <si>
@@ -337,6 +328,15 @@
   </si>
   <si>
     <t>Vanquish Neo</t>
+  </si>
+  <si>
+    <t>Before (nonsample):</t>
+  </si>
+  <si>
+    <t>After (nonsample):</t>
+  </si>
+  <si>
+    <t>Between (nonsample):</t>
   </si>
 </sst>
 </file>
@@ -1280,7 +1280,7 @@
         <v>4</v>
       </c>
       <c r="AH1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="AM1" s="29"/>
       <c r="AO1" s="28"/>
@@ -1299,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="AF2" s="58" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AG2" s="26">
         <v>1</v>
@@ -1326,7 +1326,7 @@
         <v>6</v>
       </c>
       <c r="AF3" s="57" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AG3" s="26">
         <v>1</v>
@@ -1375,7 +1375,7 @@
         <v>6</v>
       </c>
       <c r="AF4" s="56" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="AG4" s="26">
         <v>1</v>
@@ -1483,19 +1483,19 @@
         <v>6</v>
       </c>
       <c r="AF5" s="55" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AG5" s="26">
         <v>1</v>
       </c>
       <c r="AI5" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AJ5" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="AK5" s="86" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="AL5" s="91"/>
       <c r="AM5" s="9"/>
@@ -1591,7 +1591,7 @@
         <v>6</v>
       </c>
       <c r="AF6" s="72" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="AG6" s="26">
         <v>1</v>
@@ -1684,7 +1684,7 @@
         <v>6</v>
       </c>
       <c r="AF7" s="73" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="AG7" s="26">
         <v>1</v>
@@ -1776,13 +1776,13 @@
         <v>6</v>
       </c>
       <c r="AF8" s="59" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AG8" s="26">
         <v>1</v>
       </c>
       <c r="AI8" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AJ8" s="19" t="s">
         <v>33</v>
@@ -1878,13 +1878,13 @@
         <v>6</v>
       </c>
       <c r="AF9" s="60" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AG9" s="26">
         <v>1</v>
       </c>
       <c r="AI9" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="AJ9" s="6"/>
       <c r="AK9" s="90"/>
@@ -1976,7 +1976,7 @@
         <v>6</v>
       </c>
       <c r="AF10" s="54" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="AG10" s="26">
         <v>1</v>
@@ -2076,7 +2076,7 @@
         <v>6</v>
       </c>
       <c r="AF11" s="53" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AG11" s="26">
         <v>1</v>
@@ -2172,7 +2172,7 @@
         <v>6</v>
       </c>
       <c r="AF12" s="52" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="AG12" s="26">
         <v>1</v>
@@ -2268,7 +2268,7 @@
         <v>6</v>
       </c>
       <c r="AF13" s="51" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AG13" s="26">
         <v>1</v>
@@ -2556,7 +2556,7 @@
         <v>49</v>
       </c>
       <c r="AF16" s="75" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AG16" s="26">
         <v>1</v>
@@ -6118,13 +6118,13 @@
         <v>45</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.4">
@@ -6315,7 +6315,7 @@
       <c r="O5" s="10"/>
       <c r="P5" s="10"/>
       <c r="Q5" s="32" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="R5" s="6" t="s">
         <v>61</v>
@@ -6456,7 +6456,7 @@
       <c r="O8" s="10"/>
       <c r="P8" s="10"/>
       <c r="Q8" s="33" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="R8" s="27">
         <v>20</v>
@@ -6507,7 +6507,7 @@
       <c r="O9" s="10"/>
       <c r="P9" s="10"/>
       <c r="Q9" s="32" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="R9" s="6">
         <v>20</v>
@@ -6648,10 +6648,10 @@
       <c r="O12" s="10"/>
       <c r="P12" s="10"/>
       <c r="Q12" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.4">
@@ -6699,7 +6699,7 @@
       <c r="O13" s="10"/>
       <c r="P13" s="10"/>
       <c r="Q13" s="82" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="R13" s="83"/>
     </row>

--- a/tests/data/mock_b_and_t_cells_exp.xlsx
+++ b/tests/data/mock_b_and_t_cells_exp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabewilson/Desktop/worklist_generation/tests/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD253007-A02B-8D4B-A7B2-4EF984686F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F2A4A1-5333-5744-96B6-23A489E84432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16860" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -255,15 +255,6 @@
     <t>hyeb</t>
   </si>
   <si>
-    <t>Nonsample before:</t>
-  </si>
-  <si>
-    <t>Nonsample after:</t>
-  </si>
-  <si>
-    <t>Nonsample between:</t>
-  </si>
-  <si>
     <t>Frequency of system validation (#):</t>
   </si>
   <si>
@@ -336,9 +327,6 @@
     <t>Experiment Two Range:</t>
   </si>
   <si>
-    <t>Vanquish Neo</t>
-  </si>
-  <si>
     <t>tbmethod</t>
   </si>
   <si>
@@ -349,6 +337,18 @@
   </si>
   <si>
     <t>wetfile</t>
+  </si>
+  <si>
+    <t>Between NonCondition:</t>
+  </si>
+  <si>
+    <t>Beginning NonCondition:</t>
+  </si>
+  <si>
+    <t>Ending NonCondition</t>
+  </si>
+  <si>
+    <t>UltiMate3000</t>
   </si>
 </sst>
 </file>
@@ -672,7 +672,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyProtection="1">
@@ -899,6 +899,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1292,13 +1296,13 @@
         <v>4</v>
       </c>
       <c r="AH1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="AM1" s="29"/>
       <c r="AO1" s="28"/>
     </row>
     <row r="2" spans="1:47" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="92" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1311,7 +1315,7 @@
         <v>6</v>
       </c>
       <c r="AF2" s="58" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AG2" s="26">
         <v>1</v>
@@ -1338,7 +1342,7 @@
         <v>6</v>
       </c>
       <c r="AF3" s="57" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AG3" s="26">
         <v>1</v>
@@ -1387,7 +1391,7 @@
         <v>6</v>
       </c>
       <c r="AF4" s="56" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="AG4" s="26">
         <v>1</v>
@@ -1495,19 +1499,19 @@
         <v>6</v>
       </c>
       <c r="AF5" s="55" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AG5" s="26">
         <v>1</v>
       </c>
       <c r="AI5" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AJ5" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="AK5" s="86" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="AL5" s="91"/>
       <c r="AM5" s="9"/>
@@ -1515,7 +1519,7 @@
       <c r="AO5" s="28"/>
     </row>
     <row r="6" spans="1:47" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="93" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="12" t="s">
@@ -1603,7 +1607,7 @@
         <v>6</v>
       </c>
       <c r="AF6" s="72" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="AG6" s="26">
         <v>1</v>
@@ -1696,7 +1700,7 @@
         <v>6</v>
       </c>
       <c r="AF7" s="73" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="AG7" s="26">
         <v>1</v>
@@ -1788,13 +1792,13 @@
         <v>6</v>
       </c>
       <c r="AF8" s="59" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AG8" s="26">
         <v>1</v>
       </c>
       <c r="AI8" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AJ8" s="19" t="s">
         <v>33</v>
@@ -1890,13 +1894,13 @@
         <v>6</v>
       </c>
       <c r="AF9" s="60" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AG9" s="26">
         <v>1</v>
       </c>
       <c r="AI9" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="AJ9" s="6"/>
       <c r="AK9" s="90"/>
@@ -1988,7 +1992,7 @@
         <v>6</v>
       </c>
       <c r="AF10" s="54" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="AG10" s="26">
         <v>1</v>
@@ -2088,7 +2092,7 @@
         <v>6</v>
       </c>
       <c r="AF11" s="53" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AG11" s="26">
         <v>1</v>
@@ -2184,7 +2188,7 @@
         <v>6</v>
       </c>
       <c r="AF12" s="52" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="AG12" s="26">
         <v>1</v>
@@ -2280,7 +2284,7 @@
         <v>6</v>
       </c>
       <c r="AF13" s="51" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AG13" s="26">
         <v>1</v>
@@ -2568,7 +2572,7 @@
         <v>49</v>
       </c>
       <c r="AF16" s="75" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AG16" s="26">
         <v>1</v>
@@ -3158,7 +3162,7 @@
       <c r="AO23" s="28"/>
     </row>
     <row r="24" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="93" t="s">
         <v>19</v>
       </c>
       <c r="B24" s="12" t="s">
@@ -4686,7 +4690,7 @@
       <c r="AK41" s="30"/>
     </row>
     <row r="42" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A42" s="12" t="s">
+      <c r="A42" s="93" t="s">
         <v>14</v>
       </c>
       <c r="B42" s="12" t="s">
@@ -6130,13 +6134,13 @@
         <v>45</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
@@ -6327,7 +6331,7 @@
       <c r="O5" s="10"/>
       <c r="P5" s="10"/>
       <c r="Q5" s="32" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="R5" s="6" t="s">
         <v>61</v>
@@ -6468,7 +6472,7 @@
       <c r="O8" s="10"/>
       <c r="P8" s="10"/>
       <c r="Q8" s="33" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="R8" s="27">
         <v>20</v>
@@ -6519,7 +6523,7 @@
       <c r="O9" s="10"/>
       <c r="P9" s="10"/>
       <c r="Q9" s="32" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="R9" s="6">
         <v>20</v>
@@ -6660,10 +6664,10 @@
       <c r="O12" s="10"/>
       <c r="P12" s="10"/>
       <c r="Q12" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
@@ -6711,7 +6715,7 @@
       <c r="O13" s="10"/>
       <c r="P13" s="10"/>
       <c r="Q13" s="82" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="R13" s="83"/>
     </row>
@@ -6746,10 +6750,10 @@
         <v>57</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L14" s="26">
         <f>IF(LEN(User!AG14)=0,"",User!AG14)</f>
@@ -6791,10 +6795,10 @@
         <v>57</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L15" s="26">
         <f>IF(LEN(User!AG15)=0,"",User!AG15)</f>
@@ -6836,10 +6840,10 @@
         <v>57</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="L16" s="26">
         <f>IF(LEN(User!AG16)=0,"",User!AG16)</f>

--- a/tests/data/mock_b_and_t_cells_exp.xlsx
+++ b/tests/data/mock_b_and_t_cells_exp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabewilson/Desktop/worklist_generation/tests/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F2A4A1-5333-5744-96B6-23A489E84432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA0CA795-1086-5649-8886-684377A2B441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16860" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="14680" windowHeight="16920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="User" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="116">
   <si>
     <t>Name:</t>
   </si>
@@ -174,9 +174,6 @@
     <t>Number of sample to run:</t>
   </si>
   <si>
-    <t>Columns:</t>
-  </si>
-  <si>
     <t>Library</t>
   </si>
   <si>
@@ -216,146 +213,182 @@
     <t>lcmethodfile</t>
   </si>
   <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>BandT</t>
+  </si>
+  <si>
+    <t>Patients 1 and 2</t>
+  </si>
+  <si>
+    <t>Patients 3 and 4</t>
+  </si>
+  <si>
+    <t>Patients 5 and 6</t>
+  </si>
+  <si>
+    <t>lc_condition</t>
+  </si>
+  <si>
+    <t>lc_lib</t>
+  </si>
+  <si>
+    <t>lc_sys</t>
+  </si>
+  <si>
+    <t>lc_tb</t>
+  </si>
+  <si>
+    <t>hyea</t>
+  </si>
+  <si>
+    <t>hyeb</t>
+  </si>
+  <si>
+    <t>Frequency of system validation (#):</t>
+  </si>
+  <si>
+    <t>H1B</t>
+  </si>
+  <si>
+    <t>H1T</t>
+  </si>
+  <si>
+    <t>D2B</t>
+  </si>
+  <si>
+    <t>D2T</t>
+  </si>
+  <si>
+    <t>D6B</t>
+  </si>
+  <si>
+    <t>H5T</t>
+  </si>
+  <si>
+    <t>D6T</t>
+  </si>
+  <si>
+    <t>H5B</t>
+  </si>
+  <si>
+    <t>D4T</t>
+  </si>
+  <si>
+    <t>D4B</t>
+  </si>
+  <si>
+    <t>H3T</t>
+  </si>
+  <si>
+    <t>H3B</t>
+  </si>
+  <si>
+    <t>tb</t>
+  </si>
+  <si>
+    <t>RA1</t>
+  </si>
+  <si>
+    <t>Notes (not used):</t>
+  </si>
+  <si>
+    <t>This determines how the well location is denoted (RA1 vs R:A1)</t>
+  </si>
+  <si>
+    <t>What LC system are you using?</t>
+  </si>
+  <si>
+    <t>Provide one location of an empty well on any plate (e.g. RA1)</t>
+  </si>
+  <si>
+    <t>TrueBlank Well Location:</t>
+  </si>
+  <si>
+    <t>Experiment One Range:</t>
+  </si>
+  <si>
+    <t>Experiment Two Range:</t>
+  </si>
+  <si>
+    <t>tbmethod</t>
+  </si>
+  <si>
+    <t>tbmethodfile</t>
+  </si>
+  <si>
+    <t>wet</t>
+  </si>
+  <si>
+    <t>wetfile</t>
+  </si>
+  <si>
+    <t>Between NonCondition:</t>
+  </si>
+  <si>
+    <t>Beginning NonCondition:</t>
+  </si>
+  <si>
+    <t>Ending NonCondition</t>
+  </si>
+  <si>
+    <t>Solvent Vials</t>
+  </si>
+  <si>
+    <t>Plate 4</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Injection volume:</t>
+  </si>
+  <si>
+    <t>System configuration:</t>
+  </si>
+  <si>
+    <t>Analytical Columns:</t>
+  </si>
+  <si>
+    <t>For 2 column, "ChannelA_" or "ChannelB_" is added before column K (LC method file name)</t>
+  </si>
+  <si>
+    <t>Library runs placement:</t>
+  </si>
+  <si>
+    <t>Do Library runs come before or after the experiment?</t>
+  </si>
+  <si>
+    <t>Frequency of QC (#):</t>
+  </si>
+  <si>
+    <t>NonCondition Ordering: QC-&gt;Blank-&gt;Trueblank</t>
+  </si>
+  <si>
+    <t>What MS system are you using?</t>
+  </si>
+  <si>
+    <t>This determines if the run number is included at the end of each file name</t>
+  </si>
+  <si>
     <t>1 column</t>
   </si>
   <si>
-    <t>After</t>
-  </si>
-  <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t>BandT</t>
-  </si>
-  <si>
-    <t>Patients 1 and 2</t>
-  </si>
-  <si>
-    <t>Patients 3 and 4</t>
-  </si>
-  <si>
-    <t>Patients 5 and 6</t>
-  </si>
-  <si>
-    <t>lc_condition</t>
-  </si>
-  <si>
-    <t>lc_lib</t>
-  </si>
-  <si>
-    <t>lc_sys</t>
-  </si>
-  <si>
-    <t>lc_tb</t>
-  </si>
-  <si>
-    <t>hyea</t>
-  </si>
-  <si>
-    <t>hyeb</t>
-  </si>
-  <si>
-    <t>Frequency of system validation (#):</t>
-  </si>
-  <si>
-    <t>Frequency of QC:</t>
-  </si>
-  <si>
-    <t>Library value placement:</t>
-  </si>
-  <si>
-    <t>H1B</t>
-  </si>
-  <si>
-    <t>H1T</t>
-  </si>
-  <si>
-    <t>D2B</t>
-  </si>
-  <si>
-    <t>D2T</t>
-  </si>
-  <si>
-    <t>D6B</t>
-  </si>
-  <si>
-    <t>H5T</t>
-  </si>
-  <si>
-    <t>D6T</t>
-  </si>
-  <si>
-    <t>H5B</t>
-  </si>
-  <si>
-    <t>D4T</t>
-  </si>
-  <si>
-    <t>D4B</t>
-  </si>
-  <si>
-    <t>H3T</t>
-  </si>
-  <si>
-    <t>H3B</t>
-  </si>
-  <si>
-    <t>tb</t>
-  </si>
-  <si>
-    <t>RA1</t>
-  </si>
-  <si>
-    <t>Notes (not used):</t>
-  </si>
-  <si>
-    <t>This determines how the well location is denoted (RA1 vs R:A1)</t>
-  </si>
-  <si>
-    <t>What LC system are you using?</t>
-  </si>
-  <si>
-    <t>Provide one location of an empty well on any plate (e.g. RA1)</t>
-  </si>
-  <si>
-    <t>TrueBlank Well Location:</t>
-  </si>
-  <si>
-    <t>Experiment One Range:</t>
-  </si>
-  <si>
-    <t>Experiment Two Range:</t>
-  </si>
-  <si>
-    <t>tbmethod</t>
-  </si>
-  <si>
-    <t>tbmethodfile</t>
-  </si>
-  <si>
-    <t>wet</t>
-  </si>
-  <si>
-    <t>wetfile</t>
-  </si>
-  <si>
-    <t>Between NonCondition:</t>
-  </si>
-  <si>
-    <t>Beginning NonCondition:</t>
-  </si>
-  <si>
-    <t>Ending NonCondition</t>
+    <t>Before</t>
   </si>
   <si>
     <t>UltiMate3000</t>
+  </si>
+  <si>
+    <t>Thermo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -383,8 +416,20 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow (Body)"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -499,8 +544,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF44B3E1"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -668,11 +725,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyProtection="1">
@@ -724,7 +790,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -878,7 +943,53 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -899,10 +1010,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1252,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AU63"/>
+  <dimension ref="A1:AU76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1281,7 +1388,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="AD1" s="5" t="s">
         <v>1</v>
@@ -1296,17 +1403,17 @@
         <v>4</v>
       </c>
       <c r="AH1" t="s">
-        <v>90</v>
-      </c>
-      <c r="AM1" s="29"/>
-      <c r="AO1" s="28"/>
+        <v>85</v>
+      </c>
+      <c r="AM1" s="28"/>
+      <c r="AO1" s="27"/>
     </row>
     <row r="2" spans="1:47" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="92" t="s">
+      <c r="A2" s="81" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="AD2" s="11">
         <v>1</v>
@@ -1314,19 +1421,19 @@
       <c r="AE2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AF2" s="58" t="s">
-        <v>76</v>
+      <c r="AF2" s="57" t="s">
+        <v>71</v>
       </c>
       <c r="AG2" s="26">
         <v>1</v>
       </c>
-      <c r="AI2" s="31"/>
-      <c r="AJ2" s="31"/>
-      <c r="AK2" s="31"/>
+      <c r="AI2" s="30"/>
+      <c r="AJ2" s="30"/>
+      <c r="AK2" s="30"/>
       <c r="AL2" s="9"/>
       <c r="AM2" s="9"/>
       <c r="AN2" s="9"/>
-      <c r="AO2" s="28"/>
+      <c r="AO2" s="27"/>
     </row>
     <row r="3" spans="1:47" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -1341,19 +1448,19 @@
       <c r="AE3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AF3" s="57" t="s">
-        <v>77</v>
+      <c r="AF3" s="56" t="s">
+        <v>72</v>
       </c>
       <c r="AG3" s="26">
         <v>1</v>
       </c>
-      <c r="AI3" s="31"/>
-      <c r="AJ3" s="31"/>
-      <c r="AK3" s="31"/>
+      <c r="AI3" s="30"/>
+      <c r="AJ3" s="30"/>
+      <c r="AK3" s="30"/>
       <c r="AL3" s="9"/>
       <c r="AM3" s="9"/>
       <c r="AN3" s="9"/>
-      <c r="AO3" s="28"/>
+      <c r="AO3" s="27"/>
       <c r="AU3" s="21"/>
     </row>
     <row r="4" spans="1:47" x14ac:dyDescent="0.2">
@@ -1390,8 +1497,8 @@
       <c r="AE4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AF4" s="56" t="s">
-        <v>78</v>
+      <c r="AF4" s="55" t="s">
+        <v>73</v>
       </c>
       <c r="AG4" s="26">
         <v>1</v>
@@ -1402,13 +1509,13 @@
       <c r="AJ4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AK4" s="86" t="s">
+      <c r="AK4" s="105" t="s">
         <v>32</v>
       </c>
-      <c r="AL4" s="87"/>
+      <c r="AL4" s="106"/>
       <c r="AM4" s="9"/>
       <c r="AN4" s="9"/>
-      <c r="AO4" s="28"/>
+      <c r="AO4" s="27"/>
     </row>
     <row r="5" spans="1:47" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
@@ -1498,32 +1605,32 @@
       <c r="AE5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AF5" s="55" t="s">
-        <v>79</v>
+      <c r="AF5" s="54" t="s">
+        <v>74</v>
       </c>
       <c r="AG5" s="26">
         <v>1</v>
       </c>
       <c r="AI5" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="AJ5" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="AK5" s="86" t="s">
-        <v>93</v>
-      </c>
-      <c r="AL5" s="91"/>
+        <v>84</v>
+      </c>
+      <c r="AK5" s="105" t="s">
+        <v>88</v>
+      </c>
+      <c r="AL5" s="110"/>
       <c r="AM5" s="9"/>
       <c r="AN5" s="9"/>
-      <c r="AO5" s="28"/>
+      <c r="AO5" s="27"/>
     </row>
     <row r="6" spans="1:47" x14ac:dyDescent="0.2">
-      <c r="A6" s="93" t="s">
+      <c r="A6" s="82" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
@@ -1534,64 +1641,64 @@
       <c r="F6" s="14">
         <v>15</v>
       </c>
-      <c r="G6" s="37">
-        <v>1</v>
-      </c>
-      <c r="H6" s="37">
-        <v>1</v>
-      </c>
-      <c r="I6" s="37">
-        <v>1</v>
-      </c>
-      <c r="J6" s="37">
-        <v>1</v>
-      </c>
-      <c r="K6" s="37">
-        <v>1</v>
-      </c>
-      <c r="L6" s="35">
-        <v>2</v>
-      </c>
-      <c r="M6" s="35">
-        <v>2</v>
-      </c>
-      <c r="N6" s="35">
-        <v>2</v>
-      </c>
-      <c r="O6" s="35">
-        <v>2</v>
-      </c>
-      <c r="P6" s="35">
-        <v>2</v>
-      </c>
-      <c r="Q6" s="39">
-        <v>3</v>
-      </c>
-      <c r="R6" s="39">
-        <v>3</v>
-      </c>
-      <c r="S6" s="39">
-        <v>3</v>
-      </c>
-      <c r="T6" s="39">
-        <v>3</v>
-      </c>
-      <c r="U6" s="39">
-        <v>3</v>
-      </c>
-      <c r="V6" s="41">
-        <v>4</v>
-      </c>
-      <c r="W6" s="41">
-        <v>4</v>
-      </c>
-      <c r="X6" s="41">
-        <v>4</v>
-      </c>
-      <c r="Y6" s="41">
-        <v>4</v>
-      </c>
-      <c r="Z6" s="41">
+      <c r="G6" s="36">
+        <v>1</v>
+      </c>
+      <c r="H6" s="36">
+        <v>1</v>
+      </c>
+      <c r="I6" s="36">
+        <v>1</v>
+      </c>
+      <c r="J6" s="36">
+        <v>1</v>
+      </c>
+      <c r="K6" s="36">
+        <v>1</v>
+      </c>
+      <c r="L6" s="34">
+        <v>2</v>
+      </c>
+      <c r="M6" s="34">
+        <v>2</v>
+      </c>
+      <c r="N6" s="34">
+        <v>2</v>
+      </c>
+      <c r="O6" s="34">
+        <v>2</v>
+      </c>
+      <c r="P6" s="34">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="38">
+        <v>3</v>
+      </c>
+      <c r="R6" s="38">
+        <v>3</v>
+      </c>
+      <c r="S6" s="38">
+        <v>3</v>
+      </c>
+      <c r="T6" s="38">
+        <v>3</v>
+      </c>
+      <c r="U6" s="38">
+        <v>3</v>
+      </c>
+      <c r="V6" s="40">
+        <v>4</v>
+      </c>
+      <c r="W6" s="40">
+        <v>4</v>
+      </c>
+      <c r="X6" s="40">
+        <v>4</v>
+      </c>
+      <c r="Y6" s="40">
+        <v>4</v>
+      </c>
+      <c r="Z6" s="40">
         <v>4</v>
       </c>
       <c r="AA6" s="14">
@@ -1606,8 +1713,8 @@
       <c r="AE6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AF6" s="72" t="s">
-        <v>87</v>
+      <c r="AF6" s="71" t="s">
+        <v>82</v>
       </c>
       <c r="AG6" s="26">
         <v>1</v>
@@ -1615,82 +1722,82 @@
       <c r="AK6" s="20"/>
       <c r="AM6" s="9"/>
       <c r="AN6" s="9"/>
-      <c r="AO6" s="28"/>
+      <c r="AO6" s="27"/>
     </row>
     <row r="7" spans="1:47" x14ac:dyDescent="0.2">
       <c r="D7" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="76">
-        <v>13</v>
-      </c>
-      <c r="F7" s="66">
-        <v>13</v>
-      </c>
-      <c r="G7" s="38">
-        <v>1</v>
-      </c>
-      <c r="H7" s="38">
-        <v>1</v>
-      </c>
-      <c r="I7" s="38">
-        <v>1</v>
-      </c>
-      <c r="J7" s="38">
-        <v>1</v>
-      </c>
-      <c r="K7" s="38">
-        <v>1</v>
-      </c>
-      <c r="L7" s="36">
-        <v>2</v>
-      </c>
-      <c r="M7" s="36">
-        <v>2</v>
-      </c>
-      <c r="N7" s="36">
-        <v>2</v>
-      </c>
-      <c r="O7" s="36">
-        <v>2</v>
-      </c>
-      <c r="P7" s="36">
-        <v>2</v>
-      </c>
-      <c r="Q7" s="40">
-        <v>3</v>
-      </c>
-      <c r="R7" s="40">
-        <v>3</v>
-      </c>
-      <c r="S7" s="40">
-        <v>3</v>
-      </c>
-      <c r="T7" s="40">
-        <v>3</v>
-      </c>
-      <c r="U7" s="40">
-        <v>3</v>
-      </c>
-      <c r="V7" s="42">
-        <v>4</v>
-      </c>
-      <c r="W7" s="42">
-        <v>4</v>
-      </c>
-      <c r="X7" s="42">
-        <v>4</v>
-      </c>
-      <c r="Y7" s="42">
-        <v>4</v>
-      </c>
-      <c r="Z7" s="42">
-        <v>4</v>
-      </c>
-      <c r="AA7" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB7" s="79">
+      <c r="E7" s="75">
+        <v>13</v>
+      </c>
+      <c r="F7" s="65">
+        <v>13</v>
+      </c>
+      <c r="G7" s="37">
+        <v>1</v>
+      </c>
+      <c r="H7" s="37">
+        <v>1</v>
+      </c>
+      <c r="I7" s="37">
+        <v>1</v>
+      </c>
+      <c r="J7" s="37">
+        <v>1</v>
+      </c>
+      <c r="K7" s="37">
+        <v>1</v>
+      </c>
+      <c r="L7" s="35">
+        <v>2</v>
+      </c>
+      <c r="M7" s="35">
+        <v>2</v>
+      </c>
+      <c r="N7" s="35">
+        <v>2</v>
+      </c>
+      <c r="O7" s="35">
+        <v>2</v>
+      </c>
+      <c r="P7" s="35">
+        <v>2</v>
+      </c>
+      <c r="Q7" s="39">
+        <v>3</v>
+      </c>
+      <c r="R7" s="39">
+        <v>3</v>
+      </c>
+      <c r="S7" s="39">
+        <v>3</v>
+      </c>
+      <c r="T7" s="39">
+        <v>3</v>
+      </c>
+      <c r="U7" s="39">
+        <v>3</v>
+      </c>
+      <c r="V7" s="41">
+        <v>4</v>
+      </c>
+      <c r="W7" s="41">
+        <v>4</v>
+      </c>
+      <c r="X7" s="41">
+        <v>4</v>
+      </c>
+      <c r="Y7" s="41">
+        <v>4</v>
+      </c>
+      <c r="Z7" s="41">
+        <v>4</v>
+      </c>
+      <c r="AA7" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB7" s="78">
         <v>14</v>
       </c>
       <c r="AD7" s="11">
@@ -1699,90 +1806,90 @@
       <c r="AE7" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AF7" s="73" t="s">
-        <v>86</v>
+      <c r="AF7" s="72" t="s">
+        <v>81</v>
       </c>
       <c r="AG7" s="26">
         <v>1</v>
       </c>
       <c r="AM7" s="9"/>
       <c r="AN7" s="9"/>
-      <c r="AO7" s="28"/>
+      <c r="AO7" s="27"/>
     </row>
     <row r="8" spans="1:47" x14ac:dyDescent="0.2">
       <c r="D8" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="76">
-        <v>13</v>
-      </c>
-      <c r="F8" s="66">
-        <v>13</v>
-      </c>
-      <c r="G8" s="38">
-        <v>1</v>
-      </c>
-      <c r="H8" s="38">
-        <v>1</v>
-      </c>
-      <c r="I8" s="38">
-        <v>1</v>
-      </c>
-      <c r="J8" s="38">
-        <v>1</v>
-      </c>
-      <c r="K8" s="38">
-        <v>1</v>
-      </c>
-      <c r="L8" s="36">
-        <v>2</v>
-      </c>
-      <c r="M8" s="36">
-        <v>2</v>
-      </c>
-      <c r="N8" s="36">
-        <v>2</v>
-      </c>
-      <c r="O8" s="36">
-        <v>2</v>
-      </c>
-      <c r="P8" s="36">
-        <v>2</v>
-      </c>
-      <c r="Q8" s="40">
-        <v>3</v>
-      </c>
-      <c r="R8" s="40">
-        <v>3</v>
-      </c>
-      <c r="S8" s="40">
-        <v>3</v>
-      </c>
-      <c r="T8" s="40">
-        <v>3</v>
-      </c>
-      <c r="U8" s="40">
-        <v>3</v>
-      </c>
-      <c r="V8" s="42">
-        <v>4</v>
-      </c>
-      <c r="W8" s="42">
-        <v>4</v>
-      </c>
-      <c r="X8" s="42">
-        <v>4</v>
-      </c>
-      <c r="Y8" s="42">
-        <v>4</v>
-      </c>
-      <c r="Z8" s="42">
-        <v>4</v>
-      </c>
-      <c r="AA8" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB8" s="79">
+      <c r="E8" s="75">
+        <v>13</v>
+      </c>
+      <c r="F8" s="65">
+        <v>13</v>
+      </c>
+      <c r="G8" s="37">
+        <v>1</v>
+      </c>
+      <c r="H8" s="37">
+        <v>1</v>
+      </c>
+      <c r="I8" s="37">
+        <v>1</v>
+      </c>
+      <c r="J8" s="37">
+        <v>1</v>
+      </c>
+      <c r="K8" s="37">
+        <v>1</v>
+      </c>
+      <c r="L8" s="35">
+        <v>2</v>
+      </c>
+      <c r="M8" s="35">
+        <v>2</v>
+      </c>
+      <c r="N8" s="35">
+        <v>2</v>
+      </c>
+      <c r="O8" s="35">
+        <v>2</v>
+      </c>
+      <c r="P8" s="35">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="39">
+        <v>3</v>
+      </c>
+      <c r="R8" s="39">
+        <v>3</v>
+      </c>
+      <c r="S8" s="39">
+        <v>3</v>
+      </c>
+      <c r="T8" s="39">
+        <v>3</v>
+      </c>
+      <c r="U8" s="39">
+        <v>3</v>
+      </c>
+      <c r="V8" s="41">
+        <v>4</v>
+      </c>
+      <c r="W8" s="41">
+        <v>4</v>
+      </c>
+      <c r="X8" s="41">
+        <v>4</v>
+      </c>
+      <c r="Y8" s="41">
+        <v>4</v>
+      </c>
+      <c r="Z8" s="41">
+        <v>4</v>
+      </c>
+      <c r="AA8" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB8" s="78">
         <v>14</v>
       </c>
       <c r="AD8" s="11">
@@ -1791,100 +1898,103 @@
       <c r="AE8" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AF8" s="59" t="s">
-        <v>85</v>
+      <c r="AF8" s="58" t="s">
+        <v>80</v>
       </c>
       <c r="AG8" s="26">
         <v>1</v>
       </c>
       <c r="AI8" s="1" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ8" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="AK8" s="86" t="s">
+      <c r="AK8" s="105" t="s">
         <v>34</v>
       </c>
-      <c r="AL8" s="87"/>
+      <c r="AL8" s="106"/>
       <c r="AM8" s="9"/>
       <c r="AN8" s="9"/>
-      <c r="AO8" s="28"/>
+      <c r="AO8" s="27"/>
     </row>
     <row r="9" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="B9" s="28" t="s">
+        <v>99</v>
+      </c>
       <c r="D9" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="76">
-        <v>13</v>
-      </c>
-      <c r="F9" s="66">
-        <v>13</v>
-      </c>
-      <c r="G9" s="38">
-        <v>1</v>
-      </c>
-      <c r="H9" s="38">
-        <v>1</v>
-      </c>
-      <c r="I9" s="38">
-        <v>1</v>
-      </c>
-      <c r="J9" s="38">
-        <v>1</v>
-      </c>
-      <c r="K9" s="38">
-        <v>1</v>
-      </c>
-      <c r="L9" s="36">
-        <v>2</v>
-      </c>
-      <c r="M9" s="36">
-        <v>2</v>
-      </c>
-      <c r="N9" s="36">
-        <v>2</v>
-      </c>
-      <c r="O9" s="36">
-        <v>2</v>
-      </c>
-      <c r="P9" s="36">
-        <v>2</v>
-      </c>
-      <c r="Q9" s="40">
-        <v>3</v>
-      </c>
-      <c r="R9" s="40">
-        <v>3</v>
-      </c>
-      <c r="S9" s="40">
-        <v>3</v>
-      </c>
-      <c r="T9" s="40">
-        <v>3</v>
-      </c>
-      <c r="U9" s="40">
-        <v>3</v>
-      </c>
-      <c r="V9" s="42">
-        <v>4</v>
-      </c>
-      <c r="W9" s="42">
-        <v>4</v>
-      </c>
-      <c r="X9" s="42">
-        <v>4</v>
-      </c>
-      <c r="Y9" s="42">
-        <v>4</v>
-      </c>
-      <c r="Z9" s="42">
-        <v>4</v>
-      </c>
-      <c r="AA9" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB9" s="79">
+      <c r="E9" s="75">
+        <v>13</v>
+      </c>
+      <c r="F9" s="65">
+        <v>13</v>
+      </c>
+      <c r="G9" s="37">
+        <v>1</v>
+      </c>
+      <c r="H9" s="37">
+        <v>1</v>
+      </c>
+      <c r="I9" s="37">
+        <v>1</v>
+      </c>
+      <c r="J9" s="37">
+        <v>1</v>
+      </c>
+      <c r="K9" s="37">
+        <v>1</v>
+      </c>
+      <c r="L9" s="35">
+        <v>2</v>
+      </c>
+      <c r="M9" s="35">
+        <v>2</v>
+      </c>
+      <c r="N9" s="35">
+        <v>2</v>
+      </c>
+      <c r="O9" s="35">
+        <v>2</v>
+      </c>
+      <c r="P9" s="35">
+        <v>2</v>
+      </c>
+      <c r="Q9" s="39">
+        <v>3</v>
+      </c>
+      <c r="R9" s="39">
+        <v>3</v>
+      </c>
+      <c r="S9" s="39">
+        <v>3</v>
+      </c>
+      <c r="T9" s="39">
+        <v>3</v>
+      </c>
+      <c r="U9" s="39">
+        <v>3</v>
+      </c>
+      <c r="V9" s="41">
+        <v>4</v>
+      </c>
+      <c r="W9" s="41">
+        <v>4</v>
+      </c>
+      <c r="X9" s="41">
+        <v>4</v>
+      </c>
+      <c r="Y9" s="41">
+        <v>4</v>
+      </c>
+      <c r="Z9" s="41">
+        <v>4</v>
+      </c>
+      <c r="AA9" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB9" s="78">
         <v>14</v>
       </c>
       <c r="AD9" s="11">
@@ -1893,96 +2003,100 @@
       <c r="AE9" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AF9" s="60" t="s">
-        <v>84</v>
+      <c r="AF9" s="59" t="s">
+        <v>79</v>
       </c>
       <c r="AG9" s="26">
         <v>1</v>
       </c>
       <c r="AI9" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ9" s="6"/>
-      <c r="AK9" s="90"/>
-      <c r="AL9" s="87"/>
+      <c r="AK9" s="109"/>
+      <c r="AL9" s="106"/>
       <c r="AM9" s="9"/>
       <c r="AN9" s="9"/>
-      <c r="AO9" s="28"/>
+      <c r="AO9" s="27"/>
     </row>
     <row r="10" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10" s="10"/>
       <c r="D10" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="76">
-        <v>13</v>
-      </c>
-      <c r="F10" s="66">
-        <v>13</v>
-      </c>
-      <c r="G10" s="38">
-        <v>1</v>
-      </c>
-      <c r="H10" s="38">
-        <v>1</v>
-      </c>
-      <c r="I10" s="38">
-        <v>1</v>
-      </c>
-      <c r="J10" s="38">
-        <v>1</v>
-      </c>
-      <c r="K10" s="38">
-        <v>1</v>
-      </c>
-      <c r="L10" s="36">
-        <v>2</v>
-      </c>
-      <c r="M10" s="36">
-        <v>2</v>
-      </c>
-      <c r="N10" s="36">
-        <v>2</v>
-      </c>
-      <c r="O10" s="36">
-        <v>2</v>
-      </c>
-      <c r="P10" s="36">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="40">
-        <v>3</v>
-      </c>
-      <c r="R10" s="40">
-        <v>3</v>
-      </c>
-      <c r="S10" s="40">
-        <v>3</v>
-      </c>
-      <c r="T10" s="40">
-        <v>3</v>
-      </c>
-      <c r="U10" s="40">
-        <v>3</v>
-      </c>
-      <c r="V10" s="42">
-        <v>4</v>
-      </c>
-      <c r="W10" s="42">
-        <v>4</v>
-      </c>
-      <c r="X10" s="42">
-        <v>4</v>
-      </c>
-      <c r="Y10" s="42">
-        <v>4</v>
-      </c>
-      <c r="Z10" s="42">
-        <v>4</v>
-      </c>
-      <c r="AA10" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB10" s="79">
+      <c r="E10" s="75">
+        <v>13</v>
+      </c>
+      <c r="F10" s="65">
+        <v>13</v>
+      </c>
+      <c r="G10" s="37">
+        <v>1</v>
+      </c>
+      <c r="H10" s="37">
+        <v>1</v>
+      </c>
+      <c r="I10" s="37">
+        <v>1</v>
+      </c>
+      <c r="J10" s="37">
+        <v>1</v>
+      </c>
+      <c r="K10" s="37">
+        <v>1</v>
+      </c>
+      <c r="L10" s="35">
+        <v>2</v>
+      </c>
+      <c r="M10" s="35">
+        <v>2</v>
+      </c>
+      <c r="N10" s="35">
+        <v>2</v>
+      </c>
+      <c r="O10" s="35">
+        <v>2</v>
+      </c>
+      <c r="P10" s="35">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="39">
+        <v>3</v>
+      </c>
+      <c r="R10" s="39">
+        <v>3</v>
+      </c>
+      <c r="S10" s="39">
+        <v>3</v>
+      </c>
+      <c r="T10" s="39">
+        <v>3</v>
+      </c>
+      <c r="U10" s="39">
+        <v>3</v>
+      </c>
+      <c r="V10" s="41">
+        <v>4</v>
+      </c>
+      <c r="W10" s="41">
+        <v>4</v>
+      </c>
+      <c r="X10" s="41">
+        <v>4</v>
+      </c>
+      <c r="Y10" s="41">
+        <v>4</v>
+      </c>
+      <c r="Z10" s="41">
+        <v>4</v>
+      </c>
+      <c r="AA10" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB10" s="78">
         <v>14</v>
       </c>
       <c r="AD10" s="11">
@@ -1991,98 +2105,102 @@
       <c r="AE10" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AF10" s="54" t="s">
-        <v>83</v>
+      <c r="AF10" s="53" t="s">
+        <v>78</v>
       </c>
       <c r="AG10" s="26">
         <v>1</v>
       </c>
-      <c r="AI10" s="88" t="s">
+      <c r="AI10" s="107" t="s">
         <v>35</v>
       </c>
-      <c r="AJ10" s="84" t="s">
+      <c r="AJ10" s="103" t="s">
         <v>31</v>
       </c>
-      <c r="AK10" s="90"/>
-      <c r="AL10" s="87"/>
+      <c r="AK10" s="109"/>
+      <c r="AL10" s="106"/>
       <c r="AM10" s="9"/>
       <c r="AN10" s="9"/>
-      <c r="AO10" s="28"/>
+      <c r="AO10" s="27"/>
     </row>
     <row r="11" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11" s="10"/>
       <c r="D11" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="76">
-        <v>13</v>
-      </c>
-      <c r="F11" s="66">
-        <v>13</v>
-      </c>
-      <c r="G11" s="38">
-        <v>1</v>
-      </c>
-      <c r="H11" s="38">
-        <v>1</v>
-      </c>
-      <c r="I11" s="38">
-        <v>1</v>
-      </c>
-      <c r="J11" s="38">
-        <v>1</v>
-      </c>
-      <c r="K11" s="38">
-        <v>1</v>
-      </c>
-      <c r="L11" s="36">
-        <v>2</v>
-      </c>
-      <c r="M11" s="36">
-        <v>2</v>
-      </c>
-      <c r="N11" s="36">
-        <v>2</v>
-      </c>
-      <c r="O11" s="36">
-        <v>2</v>
-      </c>
-      <c r="P11" s="36">
-        <v>2</v>
-      </c>
-      <c r="Q11" s="40">
-        <v>3</v>
-      </c>
-      <c r="R11" s="40">
-        <v>3</v>
-      </c>
-      <c r="S11" s="40">
-        <v>3</v>
-      </c>
-      <c r="T11" s="40">
-        <v>3</v>
-      </c>
-      <c r="U11" s="40">
-        <v>3</v>
-      </c>
-      <c r="V11" s="42">
-        <v>4</v>
-      </c>
-      <c r="W11" s="42">
-        <v>4</v>
-      </c>
-      <c r="X11" s="42">
-        <v>4</v>
-      </c>
-      <c r="Y11" s="42">
-        <v>4</v>
-      </c>
-      <c r="Z11" s="42">
-        <v>4</v>
-      </c>
-      <c r="AA11" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB11" s="79">
+      <c r="E11" s="75">
+        <v>13</v>
+      </c>
+      <c r="F11" s="65">
+        <v>13</v>
+      </c>
+      <c r="G11" s="37">
+        <v>1</v>
+      </c>
+      <c r="H11" s="37">
+        <v>1</v>
+      </c>
+      <c r="I11" s="37">
+        <v>1</v>
+      </c>
+      <c r="J11" s="37">
+        <v>1</v>
+      </c>
+      <c r="K11" s="37">
+        <v>1</v>
+      </c>
+      <c r="L11" s="35">
+        <v>2</v>
+      </c>
+      <c r="M11" s="35">
+        <v>2</v>
+      </c>
+      <c r="N11" s="35">
+        <v>2</v>
+      </c>
+      <c r="O11" s="35">
+        <v>2</v>
+      </c>
+      <c r="P11" s="35">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="39">
+        <v>3</v>
+      </c>
+      <c r="R11" s="39">
+        <v>3</v>
+      </c>
+      <c r="S11" s="39">
+        <v>3</v>
+      </c>
+      <c r="T11" s="39">
+        <v>3</v>
+      </c>
+      <c r="U11" s="39">
+        <v>3</v>
+      </c>
+      <c r="V11" s="41">
+        <v>4</v>
+      </c>
+      <c r="W11" s="41">
+        <v>4</v>
+      </c>
+      <c r="X11" s="41">
+        <v>4</v>
+      </c>
+      <c r="Y11" s="41">
+        <v>4</v>
+      </c>
+      <c r="Z11" s="41">
+        <v>4</v>
+      </c>
+      <c r="AA11" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB11" s="78">
         <v>14</v>
       </c>
       <c r="AD11" s="11">
@@ -2091,94 +2209,98 @@
       <c r="AE11" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AF11" s="53" t="s">
-        <v>81</v>
+      <c r="AF11" s="52" t="s">
+        <v>76</v>
       </c>
       <c r="AG11" s="26">
         <v>1</v>
       </c>
-      <c r="AI11" s="89"/>
-      <c r="AJ11" s="85"/>
-      <c r="AK11" s="30"/>
-      <c r="AL11" s="30"/>
+      <c r="AI11" s="108"/>
+      <c r="AJ11" s="104"/>
+      <c r="AK11" s="29"/>
+      <c r="AL11" s="29"/>
       <c r="AM11" s="9"/>
       <c r="AN11" s="9"/>
-      <c r="AO11" s="28"/>
+      <c r="AO11" s="27"/>
     </row>
     <row r="12" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>3</v>
+      </c>
+      <c r="B12" s="10"/>
       <c r="D12" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="76">
-        <v>13</v>
-      </c>
-      <c r="F12" s="66">
-        <v>13</v>
-      </c>
-      <c r="G12" s="38">
-        <v>1</v>
-      </c>
-      <c r="H12" s="38">
-        <v>1</v>
-      </c>
-      <c r="I12" s="38">
-        <v>1</v>
-      </c>
-      <c r="J12" s="38">
-        <v>1</v>
-      </c>
-      <c r="K12" s="38">
-        <v>1</v>
-      </c>
-      <c r="L12" s="36">
-        <v>2</v>
-      </c>
-      <c r="M12" s="36">
-        <v>2</v>
-      </c>
-      <c r="N12" s="36">
-        <v>2</v>
-      </c>
-      <c r="O12" s="36">
-        <v>2</v>
-      </c>
-      <c r="P12" s="36">
-        <v>2</v>
-      </c>
-      <c r="Q12" s="40">
-        <v>3</v>
-      </c>
-      <c r="R12" s="40">
-        <v>3</v>
-      </c>
-      <c r="S12" s="40">
-        <v>3</v>
-      </c>
-      <c r="T12" s="40">
-        <v>3</v>
-      </c>
-      <c r="U12" s="40">
-        <v>3</v>
-      </c>
-      <c r="V12" s="42">
-        <v>4</v>
-      </c>
-      <c r="W12" s="42">
-        <v>4</v>
-      </c>
-      <c r="X12" s="42">
-        <v>4</v>
-      </c>
-      <c r="Y12" s="42">
-        <v>4</v>
-      </c>
-      <c r="Z12" s="42">
-        <v>4</v>
-      </c>
-      <c r="AA12" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB12" s="79">
+      <c r="E12" s="75">
+        <v>13</v>
+      </c>
+      <c r="F12" s="65">
+        <v>13</v>
+      </c>
+      <c r="G12" s="37">
+        <v>1</v>
+      </c>
+      <c r="H12" s="37">
+        <v>1</v>
+      </c>
+      <c r="I12" s="37">
+        <v>1</v>
+      </c>
+      <c r="J12" s="37">
+        <v>1</v>
+      </c>
+      <c r="K12" s="37">
+        <v>1</v>
+      </c>
+      <c r="L12" s="35">
+        <v>2</v>
+      </c>
+      <c r="M12" s="35">
+        <v>2</v>
+      </c>
+      <c r="N12" s="35">
+        <v>2</v>
+      </c>
+      <c r="O12" s="35">
+        <v>2</v>
+      </c>
+      <c r="P12" s="35">
+        <v>2</v>
+      </c>
+      <c r="Q12" s="39">
+        <v>3</v>
+      </c>
+      <c r="R12" s="39">
+        <v>3</v>
+      </c>
+      <c r="S12" s="39">
+        <v>3</v>
+      </c>
+      <c r="T12" s="39">
+        <v>3</v>
+      </c>
+      <c r="U12" s="39">
+        <v>3</v>
+      </c>
+      <c r="V12" s="41">
+        <v>4</v>
+      </c>
+      <c r="W12" s="41">
+        <v>4</v>
+      </c>
+      <c r="X12" s="41">
+        <v>4</v>
+      </c>
+      <c r="Y12" s="41">
+        <v>4</v>
+      </c>
+      <c r="Z12" s="41">
+        <v>4</v>
+      </c>
+      <c r="AA12" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB12" s="78">
         <v>14</v>
       </c>
       <c r="AD12" s="11">
@@ -2187,94 +2309,98 @@
       <c r="AE12" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AF12" s="52" t="s">
-        <v>80</v>
+      <c r="AF12" s="51" t="s">
+        <v>75</v>
       </c>
       <c r="AG12" s="26">
         <v>1</v>
       </c>
-      <c r="AI12" s="31"/>
-      <c r="AJ12" s="31"/>
-      <c r="AK12" s="31"/>
+      <c r="AI12" s="30"/>
+      <c r="AJ12" s="30"/>
+      <c r="AK12" s="30"/>
       <c r="AL12" s="9"/>
       <c r="AM12" s="9"/>
       <c r="AN12" s="9"/>
-      <c r="AO12" s="28"/>
+      <c r="AO12" s="27"/>
     </row>
     <row r="13" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>4</v>
+      </c>
+      <c r="B13" s="10"/>
       <c r="D13" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="76">
-        <v>13</v>
-      </c>
-      <c r="F13" s="66">
-        <v>13</v>
-      </c>
-      <c r="G13" s="38">
-        <v>1</v>
-      </c>
-      <c r="H13" s="38">
-        <v>1</v>
-      </c>
-      <c r="I13" s="38">
-        <v>1</v>
-      </c>
-      <c r="J13" s="38">
-        <v>1</v>
-      </c>
-      <c r="K13" s="38">
-        <v>1</v>
-      </c>
-      <c r="L13" s="36">
-        <v>2</v>
-      </c>
-      <c r="M13" s="36">
-        <v>2</v>
-      </c>
-      <c r="N13" s="36">
-        <v>2</v>
-      </c>
-      <c r="O13" s="36">
-        <v>2</v>
-      </c>
-      <c r="P13" s="36">
-        <v>2</v>
-      </c>
-      <c r="Q13" s="40">
-        <v>3</v>
-      </c>
-      <c r="R13" s="40">
-        <v>3</v>
-      </c>
-      <c r="S13" s="40">
-        <v>3</v>
-      </c>
-      <c r="T13" s="40">
-        <v>3</v>
-      </c>
-      <c r="U13" s="40">
-        <v>3</v>
-      </c>
-      <c r="V13" s="42">
-        <v>4</v>
-      </c>
-      <c r="W13" s="42">
-        <v>4</v>
-      </c>
-      <c r="X13" s="42">
-        <v>4</v>
-      </c>
-      <c r="Y13" s="42">
-        <v>4</v>
-      </c>
-      <c r="Z13" s="42">
-        <v>4</v>
-      </c>
-      <c r="AA13" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB13" s="79">
+      <c r="E13" s="75">
+        <v>13</v>
+      </c>
+      <c r="F13" s="65">
+        <v>13</v>
+      </c>
+      <c r="G13" s="37">
+        <v>1</v>
+      </c>
+      <c r="H13" s="37">
+        <v>1</v>
+      </c>
+      <c r="I13" s="37">
+        <v>1</v>
+      </c>
+      <c r="J13" s="37">
+        <v>1</v>
+      </c>
+      <c r="K13" s="37">
+        <v>1</v>
+      </c>
+      <c r="L13" s="35">
+        <v>2</v>
+      </c>
+      <c r="M13" s="35">
+        <v>2</v>
+      </c>
+      <c r="N13" s="35">
+        <v>2</v>
+      </c>
+      <c r="O13" s="35">
+        <v>2</v>
+      </c>
+      <c r="P13" s="35">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="39">
+        <v>3</v>
+      </c>
+      <c r="R13" s="39">
+        <v>3</v>
+      </c>
+      <c r="S13" s="39">
+        <v>3</v>
+      </c>
+      <c r="T13" s="39">
+        <v>3</v>
+      </c>
+      <c r="U13" s="39">
+        <v>3</v>
+      </c>
+      <c r="V13" s="41">
+        <v>4</v>
+      </c>
+      <c r="W13" s="41">
+        <v>4</v>
+      </c>
+      <c r="X13" s="41">
+        <v>4</v>
+      </c>
+      <c r="Y13" s="41">
+        <v>4</v>
+      </c>
+      <c r="Z13" s="41">
+        <v>4</v>
+      </c>
+      <c r="AA13" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB13" s="78">
         <v>14</v>
       </c>
       <c r="AD13" s="11">
@@ -2283,477 +2409,481 @@
       <c r="AE13" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AF13" s="51" t="s">
-        <v>82</v>
+      <c r="AF13" s="50" t="s">
+        <v>77</v>
       </c>
       <c r="AG13" s="26">
         <v>1</v>
       </c>
-      <c r="AI13" s="31"/>
-      <c r="AJ13" s="31"/>
-      <c r="AK13" s="31"/>
+      <c r="AI13" s="30"/>
+      <c r="AJ13" s="30"/>
+      <c r="AK13" s="30"/>
       <c r="AL13" s="9"/>
       <c r="AM13" s="9"/>
       <c r="AN13" s="9"/>
-      <c r="AO13" s="28"/>
+      <c r="AO13" s="27"/>
     </row>
     <row r="14" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>5</v>
+      </c>
+      <c r="B14" s="18"/>
       <c r="D14" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="76">
-        <v>13</v>
-      </c>
-      <c r="F14" s="66">
-        <v>13</v>
-      </c>
-      <c r="G14" s="38">
-        <v>1</v>
-      </c>
-      <c r="H14" s="38">
-        <v>1</v>
-      </c>
-      <c r="I14" s="38">
-        <v>1</v>
-      </c>
-      <c r="J14" s="38">
-        <v>1</v>
-      </c>
-      <c r="K14" s="38">
-        <v>1</v>
-      </c>
-      <c r="L14" s="36">
-        <v>2</v>
-      </c>
-      <c r="M14" s="36">
-        <v>2</v>
-      </c>
-      <c r="N14" s="36">
-        <v>2</v>
-      </c>
-      <c r="O14" s="36">
-        <v>2</v>
-      </c>
-      <c r="P14" s="36">
-        <v>2</v>
-      </c>
-      <c r="Q14" s="40">
-        <v>3</v>
-      </c>
-      <c r="R14" s="40">
-        <v>3</v>
-      </c>
-      <c r="S14" s="40">
-        <v>3</v>
-      </c>
-      <c r="T14" s="40">
-        <v>3</v>
-      </c>
-      <c r="U14" s="40">
-        <v>3</v>
-      </c>
-      <c r="V14" s="42">
-        <v>4</v>
-      </c>
-      <c r="W14" s="42">
-        <v>4</v>
-      </c>
-      <c r="X14" s="42">
-        <v>4</v>
-      </c>
-      <c r="Y14" s="42">
-        <v>4</v>
-      </c>
-      <c r="Z14" s="42">
-        <v>4</v>
-      </c>
-      <c r="AA14" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB14" s="79">
+      <c r="E14" s="75">
+        <v>13</v>
+      </c>
+      <c r="F14" s="65">
+        <v>13</v>
+      </c>
+      <c r="G14" s="37">
+        <v>1</v>
+      </c>
+      <c r="H14" s="37">
+        <v>1</v>
+      </c>
+      <c r="I14" s="37">
+        <v>1</v>
+      </c>
+      <c r="J14" s="37">
+        <v>1</v>
+      </c>
+      <c r="K14" s="37">
+        <v>1</v>
+      </c>
+      <c r="L14" s="35">
+        <v>2</v>
+      </c>
+      <c r="M14" s="35">
+        <v>2</v>
+      </c>
+      <c r="N14" s="35">
+        <v>2</v>
+      </c>
+      <c r="O14" s="35">
+        <v>2</v>
+      </c>
+      <c r="P14" s="35">
+        <v>2</v>
+      </c>
+      <c r="Q14" s="39">
+        <v>3</v>
+      </c>
+      <c r="R14" s="39">
+        <v>3</v>
+      </c>
+      <c r="S14" s="39">
+        <v>3</v>
+      </c>
+      <c r="T14" s="39">
+        <v>3</v>
+      </c>
+      <c r="U14" s="39">
+        <v>3</v>
+      </c>
+      <c r="V14" s="41">
+        <v>4</v>
+      </c>
+      <c r="W14" s="41">
+        <v>4</v>
+      </c>
+      <c r="X14" s="41">
+        <v>4</v>
+      </c>
+      <c r="Y14" s="41">
+        <v>4</v>
+      </c>
+      <c r="Z14" s="41">
+        <v>4</v>
+      </c>
+      <c r="AA14" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB14" s="78">
         <v>14</v>
       </c>
       <c r="AD14" s="11">
         <v>13</v>
       </c>
       <c r="AE14" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF14" s="65" t="s">
-        <v>71</v>
+        <v>47</v>
+      </c>
+      <c r="AF14" s="64" t="s">
+        <v>68</v>
       </c>
       <c r="AG14" s="26">
         <v>2</v>
       </c>
-      <c r="AI14" s="31"/>
-      <c r="AJ14" s="31"/>
-      <c r="AK14" s="31"/>
+      <c r="AI14" s="30"/>
+      <c r="AJ14" s="30"/>
+      <c r="AK14" s="30"/>
       <c r="AL14" s="9"/>
       <c r="AM14" s="9"/>
       <c r="AN14" s="9"/>
-      <c r="AO14" s="28"/>
+      <c r="AO14" s="27"/>
     </row>
     <row r="15" spans="1:47" x14ac:dyDescent="0.2">
       <c r="D15" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="76">
-        <v>13</v>
-      </c>
-      <c r="F15" s="66">
-        <v>13</v>
-      </c>
-      <c r="G15" s="38">
-        <v>1</v>
-      </c>
-      <c r="H15" s="38">
-        <v>1</v>
-      </c>
-      <c r="I15" s="38">
-        <v>1</v>
-      </c>
-      <c r="J15" s="38">
-        <v>1</v>
-      </c>
-      <c r="K15" s="38">
-        <v>1</v>
-      </c>
-      <c r="L15" s="36">
-        <v>2</v>
-      </c>
-      <c r="M15" s="36">
-        <v>2</v>
-      </c>
-      <c r="N15" s="36">
-        <v>2</v>
-      </c>
-      <c r="O15" s="36">
-        <v>2</v>
-      </c>
-      <c r="P15" s="36">
-        <v>2</v>
-      </c>
-      <c r="Q15" s="40">
-        <v>3</v>
-      </c>
-      <c r="R15" s="40">
-        <v>3</v>
-      </c>
-      <c r="S15" s="40">
-        <v>3</v>
-      </c>
-      <c r="T15" s="40">
-        <v>3</v>
-      </c>
-      <c r="U15" s="40">
-        <v>3</v>
-      </c>
-      <c r="V15" s="42">
-        <v>4</v>
-      </c>
-      <c r="W15" s="42">
-        <v>4</v>
-      </c>
-      <c r="X15" s="42">
-        <v>4</v>
-      </c>
-      <c r="Y15" s="42">
-        <v>4</v>
-      </c>
-      <c r="Z15" s="42">
-        <v>4</v>
-      </c>
-      <c r="AA15" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB15" s="79">
+      <c r="E15" s="75">
+        <v>13</v>
+      </c>
+      <c r="F15" s="65">
+        <v>13</v>
+      </c>
+      <c r="G15" s="37">
+        <v>1</v>
+      </c>
+      <c r="H15" s="37">
+        <v>1</v>
+      </c>
+      <c r="I15" s="37">
+        <v>1</v>
+      </c>
+      <c r="J15" s="37">
+        <v>1</v>
+      </c>
+      <c r="K15" s="37">
+        <v>1</v>
+      </c>
+      <c r="L15" s="35">
+        <v>2</v>
+      </c>
+      <c r="M15" s="35">
+        <v>2</v>
+      </c>
+      <c r="N15" s="35">
+        <v>2</v>
+      </c>
+      <c r="O15" s="35">
+        <v>2</v>
+      </c>
+      <c r="P15" s="35">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="39">
+        <v>3</v>
+      </c>
+      <c r="R15" s="39">
+        <v>3</v>
+      </c>
+      <c r="S15" s="39">
+        <v>3</v>
+      </c>
+      <c r="T15" s="39">
+        <v>3</v>
+      </c>
+      <c r="U15" s="39">
+        <v>3</v>
+      </c>
+      <c r="V15" s="41">
+        <v>4</v>
+      </c>
+      <c r="W15" s="41">
+        <v>4</v>
+      </c>
+      <c r="X15" s="41">
+        <v>4</v>
+      </c>
+      <c r="Y15" s="41">
+        <v>4</v>
+      </c>
+      <c r="Z15" s="41">
+        <v>4</v>
+      </c>
+      <c r="AA15" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB15" s="78">
         <v>14</v>
       </c>
       <c r="AD15" s="11">
         <v>14</v>
       </c>
       <c r="AE15" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF15" s="81" t="s">
-        <v>72</v>
+        <v>47</v>
+      </c>
+      <c r="AF15" s="80" t="s">
+        <v>69</v>
       </c>
       <c r="AG15" s="26">
         <v>2</v>
       </c>
-      <c r="AI15" s="31"/>
-      <c r="AJ15" s="31"/>
-      <c r="AK15" s="31"/>
+      <c r="AI15" s="30"/>
+      <c r="AJ15" s="30"/>
+      <c r="AK15" s="30"/>
       <c r="AL15" s="9"/>
       <c r="AM15" s="9"/>
       <c r="AN15" s="9"/>
-      <c r="AO15" s="28"/>
+      <c r="AO15" s="27"/>
     </row>
     <row r="16" spans="1:47" x14ac:dyDescent="0.2">
       <c r="D16" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="76">
-        <v>13</v>
-      </c>
-      <c r="F16" s="66">
-        <v>13</v>
-      </c>
-      <c r="G16" s="38">
-        <v>1</v>
-      </c>
-      <c r="H16" s="38">
-        <v>1</v>
-      </c>
-      <c r="I16" s="38">
-        <v>1</v>
-      </c>
-      <c r="J16" s="38">
-        <v>1</v>
-      </c>
-      <c r="K16" s="38">
-        <v>1</v>
-      </c>
-      <c r="L16" s="36">
-        <v>2</v>
-      </c>
-      <c r="M16" s="36">
-        <v>2</v>
-      </c>
-      <c r="N16" s="36">
-        <v>2</v>
-      </c>
-      <c r="O16" s="36">
-        <v>2</v>
-      </c>
-      <c r="P16" s="36">
-        <v>2</v>
-      </c>
-      <c r="Q16" s="40">
-        <v>3</v>
-      </c>
-      <c r="R16" s="40">
-        <v>3</v>
-      </c>
-      <c r="S16" s="40">
-        <v>3</v>
-      </c>
-      <c r="T16" s="40">
-        <v>3</v>
-      </c>
-      <c r="U16" s="40">
-        <v>3</v>
-      </c>
-      <c r="V16" s="42">
-        <v>4</v>
-      </c>
-      <c r="W16" s="42">
-        <v>4</v>
-      </c>
-      <c r="X16" s="42">
-        <v>4</v>
-      </c>
-      <c r="Y16" s="42">
-        <v>4</v>
-      </c>
-      <c r="Z16" s="42">
-        <v>4</v>
-      </c>
-      <c r="AA16" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB16" s="79">
+      <c r="E16" s="75">
+        <v>13</v>
+      </c>
+      <c r="F16" s="65">
+        <v>13</v>
+      </c>
+      <c r="G16" s="37">
+        <v>1</v>
+      </c>
+      <c r="H16" s="37">
+        <v>1</v>
+      </c>
+      <c r="I16" s="37">
+        <v>1</v>
+      </c>
+      <c r="J16" s="37">
+        <v>1</v>
+      </c>
+      <c r="K16" s="37">
+        <v>1</v>
+      </c>
+      <c r="L16" s="35">
+        <v>2</v>
+      </c>
+      <c r="M16" s="35">
+        <v>2</v>
+      </c>
+      <c r="N16" s="35">
+        <v>2</v>
+      </c>
+      <c r="O16" s="35">
+        <v>2</v>
+      </c>
+      <c r="P16" s="35">
+        <v>2</v>
+      </c>
+      <c r="Q16" s="39">
+        <v>3</v>
+      </c>
+      <c r="R16" s="39">
+        <v>3</v>
+      </c>
+      <c r="S16" s="39">
+        <v>3</v>
+      </c>
+      <c r="T16" s="39">
+        <v>3</v>
+      </c>
+      <c r="U16" s="39">
+        <v>3</v>
+      </c>
+      <c r="V16" s="41">
+        <v>4</v>
+      </c>
+      <c r="W16" s="41">
+        <v>4</v>
+      </c>
+      <c r="X16" s="41">
+        <v>4</v>
+      </c>
+      <c r="Y16" s="41">
+        <v>4</v>
+      </c>
+      <c r="Z16" s="41">
+        <v>4</v>
+      </c>
+      <c r="AA16" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB16" s="78">
         <v>14</v>
       </c>
       <c r="AD16" s="11">
         <v>15</v>
       </c>
       <c r="AE16" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF16" s="75" t="s">
-        <v>88</v>
+        <v>48</v>
+      </c>
+      <c r="AF16" s="74" t="s">
+        <v>83</v>
       </c>
       <c r="AG16" s="26">
         <v>1</v>
       </c>
-      <c r="AI16" s="31"/>
-      <c r="AJ16" s="31"/>
-      <c r="AK16" s="31"/>
+      <c r="AI16" s="30"/>
+      <c r="AJ16" s="30"/>
+      <c r="AK16" s="30"/>
       <c r="AL16" s="9"/>
       <c r="AM16" s="9"/>
       <c r="AN16" s="9"/>
-      <c r="AO16" s="28"/>
+      <c r="AO16" s="27"/>
     </row>
     <row r="17" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D17" t="s">
         <v>24</v>
       </c>
-      <c r="E17" s="76">
-        <v>13</v>
-      </c>
-      <c r="F17" s="66">
-        <v>13</v>
-      </c>
-      <c r="G17" s="38">
-        <v>1</v>
-      </c>
-      <c r="H17" s="38">
-        <v>1</v>
-      </c>
-      <c r="I17" s="38">
-        <v>1</v>
-      </c>
-      <c r="J17" s="38">
-        <v>1</v>
-      </c>
-      <c r="K17" s="38">
-        <v>1</v>
-      </c>
-      <c r="L17" s="36">
-        <v>2</v>
-      </c>
-      <c r="M17" s="36">
-        <v>2</v>
-      </c>
-      <c r="N17" s="36">
-        <v>2</v>
-      </c>
-      <c r="O17" s="36">
-        <v>2</v>
-      </c>
-      <c r="P17" s="36">
-        <v>2</v>
-      </c>
-      <c r="Q17" s="40">
-        <v>3</v>
-      </c>
-      <c r="R17" s="40">
-        <v>3</v>
-      </c>
-      <c r="S17" s="40">
-        <v>3</v>
-      </c>
-      <c r="T17" s="40">
-        <v>3</v>
-      </c>
-      <c r="U17" s="40">
-        <v>3</v>
-      </c>
-      <c r="V17" s="42">
-        <v>4</v>
-      </c>
-      <c r="W17" s="42">
-        <v>4</v>
-      </c>
-      <c r="X17" s="42">
-        <v>4</v>
-      </c>
-      <c r="Y17" s="42">
-        <v>4</v>
-      </c>
-      <c r="Z17" s="42">
-        <v>4</v>
-      </c>
-      <c r="AA17" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB17" s="79">
+      <c r="E17" s="75">
+        <v>13</v>
+      </c>
+      <c r="F17" s="65">
+        <v>13</v>
+      </c>
+      <c r="G17" s="37">
+        <v>1</v>
+      </c>
+      <c r="H17" s="37">
+        <v>1</v>
+      </c>
+      <c r="I17" s="37">
+        <v>1</v>
+      </c>
+      <c r="J17" s="37">
+        <v>1</v>
+      </c>
+      <c r="K17" s="37">
+        <v>1</v>
+      </c>
+      <c r="L17" s="35">
+        <v>2</v>
+      </c>
+      <c r="M17" s="35">
+        <v>2</v>
+      </c>
+      <c r="N17" s="35">
+        <v>2</v>
+      </c>
+      <c r="O17" s="35">
+        <v>2</v>
+      </c>
+      <c r="P17" s="35">
+        <v>2</v>
+      </c>
+      <c r="Q17" s="39">
+        <v>3</v>
+      </c>
+      <c r="R17" s="39">
+        <v>3</v>
+      </c>
+      <c r="S17" s="39">
+        <v>3</v>
+      </c>
+      <c r="T17" s="39">
+        <v>3</v>
+      </c>
+      <c r="U17" s="39">
+        <v>3</v>
+      </c>
+      <c r="V17" s="41">
+        <v>4</v>
+      </c>
+      <c r="W17" s="41">
+        <v>4</v>
+      </c>
+      <c r="X17" s="41">
+        <v>4</v>
+      </c>
+      <c r="Y17" s="41">
+        <v>4</v>
+      </c>
+      <c r="Z17" s="41">
+        <v>4</v>
+      </c>
+      <c r="AA17" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB17" s="78">
         <v>14</v>
       </c>
       <c r="AD17" s="11">
         <v>16</v>
       </c>
       <c r="AE17" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF17" s="74" t="s">
-        <v>47</v>
+        <v>46</v>
+      </c>
+      <c r="AF17" s="73" t="s">
+        <v>46</v>
       </c>
       <c r="AG17" s="26">
         <v>1</v>
       </c>
-      <c r="AJ17" s="31"/>
-      <c r="AK17" s="31"/>
+      <c r="AJ17" s="30"/>
+      <c r="AK17" s="30"/>
       <c r="AL17" s="9"/>
       <c r="AM17" s="9"/>
       <c r="AN17" s="9"/>
-      <c r="AO17" s="28"/>
+      <c r="AO17" s="27"/>
     </row>
     <row r="18" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D18" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="76">
-        <v>13</v>
-      </c>
-      <c r="F18" s="66">
-        <v>13</v>
-      </c>
-      <c r="G18" s="38">
-        <v>1</v>
-      </c>
-      <c r="H18" s="38">
-        <v>1</v>
-      </c>
-      <c r="I18" s="38">
-        <v>1</v>
-      </c>
-      <c r="J18" s="38">
-        <v>1</v>
-      </c>
-      <c r="K18" s="38">
-        <v>1</v>
-      </c>
-      <c r="L18" s="36">
-        <v>2</v>
-      </c>
-      <c r="M18" s="36">
-        <v>2</v>
-      </c>
-      <c r="N18" s="36">
-        <v>2</v>
-      </c>
-      <c r="O18" s="36">
-        <v>2</v>
-      </c>
-      <c r="P18" s="36">
-        <v>2</v>
-      </c>
-      <c r="Q18" s="40">
-        <v>3</v>
-      </c>
-      <c r="R18" s="40">
-        <v>3</v>
-      </c>
-      <c r="S18" s="40">
-        <v>3</v>
-      </c>
-      <c r="T18" s="40">
-        <v>3</v>
-      </c>
-      <c r="U18" s="40">
-        <v>3</v>
-      </c>
-      <c r="V18" s="42">
-        <v>4</v>
-      </c>
-      <c r="W18" s="42">
-        <v>4</v>
-      </c>
-      <c r="X18" s="42">
-        <v>4</v>
-      </c>
-      <c r="Y18" s="42">
-        <v>4</v>
-      </c>
-      <c r="Z18" s="42">
-        <v>4</v>
-      </c>
-      <c r="AA18" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB18" s="79">
+      <c r="E18" s="75">
+        <v>13</v>
+      </c>
+      <c r="F18" s="65">
+        <v>13</v>
+      </c>
+      <c r="G18" s="37">
+        <v>1</v>
+      </c>
+      <c r="H18" s="37">
+        <v>1</v>
+      </c>
+      <c r="I18" s="37">
+        <v>1</v>
+      </c>
+      <c r="J18" s="37">
+        <v>1</v>
+      </c>
+      <c r="K18" s="37">
+        <v>1</v>
+      </c>
+      <c r="L18" s="35">
+        <v>2</v>
+      </c>
+      <c r="M18" s="35">
+        <v>2</v>
+      </c>
+      <c r="N18" s="35">
+        <v>2</v>
+      </c>
+      <c r="O18" s="35">
+        <v>2</v>
+      </c>
+      <c r="P18" s="35">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="39">
+        <v>3</v>
+      </c>
+      <c r="R18" s="39">
+        <v>3</v>
+      </c>
+      <c r="S18" s="39">
+        <v>3</v>
+      </c>
+      <c r="T18" s="39">
+        <v>3</v>
+      </c>
+      <c r="U18" s="39">
+        <v>3</v>
+      </c>
+      <c r="V18" s="41">
+        <v>4</v>
+      </c>
+      <c r="W18" s="41">
+        <v>4</v>
+      </c>
+      <c r="X18" s="41">
+        <v>4</v>
+      </c>
+      <c r="Y18" s="41">
+        <v>4</v>
+      </c>
+      <c r="Z18" s="41">
+        <v>4</v>
+      </c>
+      <c r="AA18" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB18" s="78">
         <v>14</v>
       </c>
       <c r="AD18" s="11">
@@ -2762,87 +2892,87 @@
       <c r="AE18" s="8"/>
       <c r="AF18" s="7"/>
       <c r="AG18" s="26"/>
-      <c r="AJ18" s="31"/>
-      <c r="AK18" s="31"/>
+      <c r="AJ18" s="30"/>
+      <c r="AK18" s="30"/>
       <c r="AL18" s="9"/>
       <c r="AM18" s="9"/>
       <c r="AN18" s="9"/>
-      <c r="AO18" s="28"/>
+      <c r="AO18" s="27"/>
     </row>
     <row r="19" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D19" t="s">
         <v>26</v>
       </c>
-      <c r="E19" s="76">
-        <v>13</v>
-      </c>
-      <c r="F19" s="66">
-        <v>13</v>
-      </c>
-      <c r="G19" s="38">
-        <v>1</v>
-      </c>
-      <c r="H19" s="38">
-        <v>1</v>
-      </c>
-      <c r="I19" s="38">
-        <v>1</v>
-      </c>
-      <c r="J19" s="38">
-        <v>1</v>
-      </c>
-      <c r="K19" s="38">
-        <v>1</v>
-      </c>
-      <c r="L19" s="36">
-        <v>2</v>
-      </c>
-      <c r="M19" s="36">
-        <v>2</v>
-      </c>
-      <c r="N19" s="36">
-        <v>2</v>
-      </c>
-      <c r="O19" s="36">
-        <v>2</v>
-      </c>
-      <c r="P19" s="36">
-        <v>2</v>
-      </c>
-      <c r="Q19" s="40">
-        <v>3</v>
-      </c>
-      <c r="R19" s="40">
-        <v>3</v>
-      </c>
-      <c r="S19" s="40">
-        <v>3</v>
-      </c>
-      <c r="T19" s="40">
-        <v>3</v>
-      </c>
-      <c r="U19" s="40">
-        <v>3</v>
-      </c>
-      <c r="V19" s="42">
-        <v>4</v>
-      </c>
-      <c r="W19" s="42">
-        <v>4</v>
-      </c>
-      <c r="X19" s="42">
-        <v>4</v>
-      </c>
-      <c r="Y19" s="42">
-        <v>4</v>
-      </c>
-      <c r="Z19" s="42">
-        <v>4</v>
-      </c>
-      <c r="AA19" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB19" s="79">
+      <c r="E19" s="75">
+        <v>13</v>
+      </c>
+      <c r="F19" s="65">
+        <v>13</v>
+      </c>
+      <c r="G19" s="37">
+        <v>1</v>
+      </c>
+      <c r="H19" s="37">
+        <v>1</v>
+      </c>
+      <c r="I19" s="37">
+        <v>1</v>
+      </c>
+      <c r="J19" s="37">
+        <v>1</v>
+      </c>
+      <c r="K19" s="37">
+        <v>1</v>
+      </c>
+      <c r="L19" s="35">
+        <v>2</v>
+      </c>
+      <c r="M19" s="35">
+        <v>2</v>
+      </c>
+      <c r="N19" s="35">
+        <v>2</v>
+      </c>
+      <c r="O19" s="35">
+        <v>2</v>
+      </c>
+      <c r="P19" s="35">
+        <v>2</v>
+      </c>
+      <c r="Q19" s="39">
+        <v>3</v>
+      </c>
+      <c r="R19" s="39">
+        <v>3</v>
+      </c>
+      <c r="S19" s="39">
+        <v>3</v>
+      </c>
+      <c r="T19" s="39">
+        <v>3</v>
+      </c>
+      <c r="U19" s="39">
+        <v>3</v>
+      </c>
+      <c r="V19" s="41">
+        <v>4</v>
+      </c>
+      <c r="W19" s="41">
+        <v>4</v>
+      </c>
+      <c r="X19" s="41">
+        <v>4</v>
+      </c>
+      <c r="Y19" s="41">
+        <v>4</v>
+      </c>
+      <c r="Z19" s="41">
+        <v>4</v>
+      </c>
+      <c r="AA19" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB19" s="78">
         <v>14</v>
       </c>
       <c r="AD19" s="11">
@@ -2853,82 +2983,82 @@
       <c r="AG19" s="26"/>
       <c r="AM19" s="9"/>
       <c r="AN19" s="9"/>
-      <c r="AO19" s="28"/>
+      <c r="AO19" s="27"/>
     </row>
     <row r="20" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D20" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="76">
-        <v>13</v>
-      </c>
-      <c r="F20" s="66">
-        <v>13</v>
-      </c>
-      <c r="G20" s="38">
-        <v>1</v>
-      </c>
-      <c r="H20" s="38">
-        <v>1</v>
-      </c>
-      <c r="I20" s="38">
-        <v>1</v>
-      </c>
-      <c r="J20" s="38">
-        <v>1</v>
-      </c>
-      <c r="K20" s="38">
-        <v>1</v>
-      </c>
-      <c r="L20" s="36">
-        <v>2</v>
-      </c>
-      <c r="M20" s="36">
-        <v>2</v>
-      </c>
-      <c r="N20" s="36">
-        <v>2</v>
-      </c>
-      <c r="O20" s="36">
-        <v>2</v>
-      </c>
-      <c r="P20" s="36">
-        <v>2</v>
-      </c>
-      <c r="Q20" s="40">
-        <v>3</v>
-      </c>
-      <c r="R20" s="40">
-        <v>3</v>
-      </c>
-      <c r="S20" s="40">
-        <v>3</v>
-      </c>
-      <c r="T20" s="40">
-        <v>3</v>
-      </c>
-      <c r="U20" s="40">
-        <v>3</v>
-      </c>
-      <c r="V20" s="42">
-        <v>4</v>
-      </c>
-      <c r="W20" s="42">
-        <v>4</v>
-      </c>
-      <c r="X20" s="42">
-        <v>4</v>
-      </c>
-      <c r="Y20" s="42">
-        <v>4</v>
-      </c>
-      <c r="Z20" s="42">
-        <v>4</v>
-      </c>
-      <c r="AA20" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB20" s="79">
+      <c r="E20" s="75">
+        <v>13</v>
+      </c>
+      <c r="F20" s="65">
+        <v>13</v>
+      </c>
+      <c r="G20" s="37">
+        <v>1</v>
+      </c>
+      <c r="H20" s="37">
+        <v>1</v>
+      </c>
+      <c r="I20" s="37">
+        <v>1</v>
+      </c>
+      <c r="J20" s="37">
+        <v>1</v>
+      </c>
+      <c r="K20" s="37">
+        <v>1</v>
+      </c>
+      <c r="L20" s="35">
+        <v>2</v>
+      </c>
+      <c r="M20" s="35">
+        <v>2</v>
+      </c>
+      <c r="N20" s="35">
+        <v>2</v>
+      </c>
+      <c r="O20" s="35">
+        <v>2</v>
+      </c>
+      <c r="P20" s="35">
+        <v>2</v>
+      </c>
+      <c r="Q20" s="39">
+        <v>3</v>
+      </c>
+      <c r="R20" s="39">
+        <v>3</v>
+      </c>
+      <c r="S20" s="39">
+        <v>3</v>
+      </c>
+      <c r="T20" s="39">
+        <v>3</v>
+      </c>
+      <c r="U20" s="39">
+        <v>3</v>
+      </c>
+      <c r="V20" s="41">
+        <v>4</v>
+      </c>
+      <c r="W20" s="41">
+        <v>4</v>
+      </c>
+      <c r="X20" s="41">
+        <v>4</v>
+      </c>
+      <c r="Y20" s="41">
+        <v>4</v>
+      </c>
+      <c r="Z20" s="41">
+        <v>4</v>
+      </c>
+      <c r="AA20" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB20" s="78">
         <v>14</v>
       </c>
       <c r="AD20" s="11">
@@ -2939,82 +3069,82 @@
       <c r="AG20" s="26"/>
       <c r="AM20" s="9"/>
       <c r="AN20" s="9"/>
-      <c r="AO20" s="28"/>
+      <c r="AO20" s="27"/>
     </row>
     <row r="21" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D21" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="77">
+      <c r="E21" s="76">
         <v>16</v>
       </c>
-      <c r="F21" s="67">
+      <c r="F21" s="66">
         <v>16</v>
       </c>
-      <c r="G21" s="38">
-        <v>1</v>
-      </c>
-      <c r="H21" s="38">
-        <v>1</v>
-      </c>
-      <c r="I21" s="38">
-        <v>1</v>
-      </c>
-      <c r="J21" s="38">
-        <v>1</v>
-      </c>
-      <c r="K21" s="38">
-        <v>1</v>
-      </c>
-      <c r="L21" s="36">
-        <v>2</v>
-      </c>
-      <c r="M21" s="36">
-        <v>2</v>
-      </c>
-      <c r="N21" s="36">
-        <v>2</v>
-      </c>
-      <c r="O21" s="36">
-        <v>2</v>
-      </c>
-      <c r="P21" s="36">
-        <v>2</v>
-      </c>
-      <c r="Q21" s="40">
-        <v>3</v>
-      </c>
-      <c r="R21" s="40">
-        <v>3</v>
-      </c>
-      <c r="S21" s="40">
-        <v>3</v>
-      </c>
-      <c r="T21" s="40">
-        <v>3</v>
-      </c>
-      <c r="U21" s="40">
-        <v>3</v>
-      </c>
-      <c r="V21" s="42">
-        <v>4</v>
-      </c>
-      <c r="W21" s="42">
-        <v>4</v>
-      </c>
-      <c r="X21" s="42">
-        <v>4</v>
-      </c>
-      <c r="Y21" s="42">
-        <v>4</v>
-      </c>
-      <c r="Z21" s="42">
-        <v>4</v>
-      </c>
-      <c r="AA21" s="67">
+      <c r="G21" s="37">
+        <v>1</v>
+      </c>
+      <c r="H21" s="37">
+        <v>1</v>
+      </c>
+      <c r="I21" s="37">
+        <v>1</v>
+      </c>
+      <c r="J21" s="37">
+        <v>1</v>
+      </c>
+      <c r="K21" s="37">
+        <v>1</v>
+      </c>
+      <c r="L21" s="35">
+        <v>2</v>
+      </c>
+      <c r="M21" s="35">
+        <v>2</v>
+      </c>
+      <c r="N21" s="35">
+        <v>2</v>
+      </c>
+      <c r="O21" s="35">
+        <v>2</v>
+      </c>
+      <c r="P21" s="35">
+        <v>2</v>
+      </c>
+      <c r="Q21" s="39">
+        <v>3</v>
+      </c>
+      <c r="R21" s="39">
+        <v>3</v>
+      </c>
+      <c r="S21" s="39">
+        <v>3</v>
+      </c>
+      <c r="T21" s="39">
+        <v>3</v>
+      </c>
+      <c r="U21" s="39">
+        <v>3</v>
+      </c>
+      <c r="V21" s="41">
+        <v>4</v>
+      </c>
+      <c r="W21" s="41">
+        <v>4</v>
+      </c>
+      <c r="X21" s="41">
+        <v>4</v>
+      </c>
+      <c r="Y21" s="41">
+        <v>4</v>
+      </c>
+      <c r="Z21" s="41">
+        <v>4</v>
+      </c>
+      <c r="AA21" s="66">
         <v>16</v>
       </c>
-      <c r="AB21" s="67">
+      <c r="AB21" s="66">
         <v>16</v>
       </c>
       <c r="AD21" s="11">
@@ -3025,7 +3155,7 @@
       <c r="AG21" s="26"/>
       <c r="AM21" s="9"/>
       <c r="AN21" s="9"/>
-      <c r="AO21" s="28"/>
+      <c r="AO21" s="27"/>
     </row>
     <row r="22" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A22" s="3"/>
@@ -3063,13 +3193,13 @@
       <c r="AG22" s="26"/>
       <c r="AM22" s="9"/>
       <c r="AN22" s="9"/>
-      <c r="AO22" s="28"/>
+      <c r="AO22" s="27"/>
     </row>
     <row r="23" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A23" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" s="4" t="s">
+      <c r="A23" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="83" t="s">
         <v>10</v>
       </c>
       <c r="D23" t="s">
@@ -3153,20 +3283,20 @@
       <c r="AE23" s="8"/>
       <c r="AF23" s="7"/>
       <c r="AG23" s="26"/>
-      <c r="AI23" s="31"/>
-      <c r="AJ23" s="31"/>
-      <c r="AK23" s="31"/>
+      <c r="AI23" s="30"/>
+      <c r="AJ23" s="30"/>
+      <c r="AK23" s="30"/>
       <c r="AL23" s="9"/>
       <c r="AM23" s="9"/>
       <c r="AN23" s="9"/>
-      <c r="AO23" s="28"/>
+      <c r="AO23" s="27"/>
     </row>
     <row r="24" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A24" s="93" t="s">
+      <c r="A24" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="12" t="s">
-        <v>65</v>
+      <c r="B24" s="85" t="s">
+        <v>62</v>
       </c>
       <c r="D24" t="s">
         <v>13</v>
@@ -3177,64 +3307,64 @@
       <c r="F24" s="14">
         <v>15</v>
       </c>
-      <c r="G24" s="68">
-        <v>5</v>
-      </c>
-      <c r="H24" s="68">
-        <v>5</v>
-      </c>
-      <c r="I24" s="68">
-        <v>5</v>
-      </c>
-      <c r="J24" s="68">
-        <v>5</v>
-      </c>
-      <c r="K24" s="68">
-        <v>5</v>
-      </c>
-      <c r="L24" s="70">
-        <v>6</v>
-      </c>
-      <c r="M24" s="70">
-        <v>6</v>
-      </c>
-      <c r="N24" s="70">
-        <v>6</v>
-      </c>
-      <c r="O24" s="70">
-        <v>6</v>
-      </c>
-      <c r="P24" s="70">
-        <v>6</v>
-      </c>
-      <c r="Q24" s="63">
+      <c r="G24" s="67">
+        <v>5</v>
+      </c>
+      <c r="H24" s="67">
+        <v>5</v>
+      </c>
+      <c r="I24" s="67">
+        <v>5</v>
+      </c>
+      <c r="J24" s="67">
+        <v>5</v>
+      </c>
+      <c r="K24" s="67">
+        <v>5</v>
+      </c>
+      <c r="L24" s="69">
+        <v>6</v>
+      </c>
+      <c r="M24" s="69">
+        <v>6</v>
+      </c>
+      <c r="N24" s="69">
+        <v>6</v>
+      </c>
+      <c r="O24" s="69">
+        <v>6</v>
+      </c>
+      <c r="P24" s="69">
+        <v>6</v>
+      </c>
+      <c r="Q24" s="62">
         <v>7</v>
       </c>
-      <c r="R24" s="63">
+      <c r="R24" s="62">
         <v>7</v>
       </c>
-      <c r="S24" s="63">
+      <c r="S24" s="62">
         <v>7</v>
       </c>
-      <c r="T24" s="63">
+      <c r="T24" s="62">
         <v>7</v>
       </c>
-      <c r="U24" s="63">
+      <c r="U24" s="62">
         <v>7</v>
       </c>
-      <c r="V24" s="61">
+      <c r="V24" s="60">
         <v>8</v>
       </c>
-      <c r="W24" s="61">
+      <c r="W24" s="60">
         <v>8</v>
       </c>
-      <c r="X24" s="61">
+      <c r="X24" s="60">
         <v>8</v>
       </c>
-      <c r="Y24" s="61">
+      <c r="Y24" s="60">
         <v>8</v>
       </c>
-      <c r="Z24" s="61">
+      <c r="Z24" s="60">
         <v>8</v>
       </c>
       <c r="AA24" s="14">
@@ -3249,88 +3379,90 @@
       <c r="AE24" s="8"/>
       <c r="AF24" s="7"/>
       <c r="AG24" s="26"/>
-      <c r="AI24" s="31"/>
-      <c r="AJ24" s="31"/>
-      <c r="AK24" s="31"/>
+      <c r="AI24" s="30"/>
+      <c r="AJ24" s="30"/>
+      <c r="AK24" s="30"/>
       <c r="AL24" s="9"/>
       <c r="AM24" s="9"/>
       <c r="AN24" s="9"/>
-      <c r="AO24" s="28"/>
+      <c r="AO24" s="27"/>
     </row>
     <row r="25" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A25" s="27"/>
+      <c r="B25" s="27"/>
       <c r="D25" t="s">
         <v>14</v>
       </c>
-      <c r="E25" s="76">
-        <v>13</v>
-      </c>
-      <c r="F25" s="66">
-        <v>13</v>
-      </c>
-      <c r="G25" s="69">
-        <v>5</v>
-      </c>
-      <c r="H25" s="69">
-        <v>5</v>
-      </c>
-      <c r="I25" s="69">
-        <v>5</v>
-      </c>
-      <c r="J25" s="69">
-        <v>5</v>
-      </c>
-      <c r="K25" s="69">
-        <v>5</v>
-      </c>
-      <c r="L25" s="71">
-        <v>6</v>
-      </c>
-      <c r="M25" s="71">
-        <v>6</v>
-      </c>
-      <c r="N25" s="71">
-        <v>6</v>
-      </c>
-      <c r="O25" s="71">
-        <v>6</v>
-      </c>
-      <c r="P25" s="71">
-        <v>6</v>
-      </c>
-      <c r="Q25" s="64">
+      <c r="E25" s="75">
+        <v>13</v>
+      </c>
+      <c r="F25" s="65">
+        <v>13</v>
+      </c>
+      <c r="G25" s="68">
+        <v>5</v>
+      </c>
+      <c r="H25" s="68">
+        <v>5</v>
+      </c>
+      <c r="I25" s="68">
+        <v>5</v>
+      </c>
+      <c r="J25" s="68">
+        <v>5</v>
+      </c>
+      <c r="K25" s="68">
+        <v>5</v>
+      </c>
+      <c r="L25" s="70">
+        <v>6</v>
+      </c>
+      <c r="M25" s="70">
+        <v>6</v>
+      </c>
+      <c r="N25" s="70">
+        <v>6</v>
+      </c>
+      <c r="O25" s="70">
+        <v>6</v>
+      </c>
+      <c r="P25" s="70">
+        <v>6</v>
+      </c>
+      <c r="Q25" s="63">
         <v>7</v>
       </c>
-      <c r="R25" s="64">
+      <c r="R25" s="63">
         <v>7</v>
       </c>
-      <c r="S25" s="64">
+      <c r="S25" s="63">
         <v>7</v>
       </c>
-      <c r="T25" s="64">
+      <c r="T25" s="63">
         <v>7</v>
       </c>
-      <c r="U25" s="64">
+      <c r="U25" s="63">
         <v>7</v>
       </c>
-      <c r="V25" s="62">
+      <c r="V25" s="61">
         <v>8</v>
       </c>
-      <c r="W25" s="62">
+      <c r="W25" s="61">
         <v>8</v>
       </c>
-      <c r="X25" s="62">
+      <c r="X25" s="61">
         <v>8</v>
       </c>
-      <c r="Y25" s="62">
+      <c r="Y25" s="61">
         <v>8</v>
       </c>
-      <c r="Z25" s="62">
+      <c r="Z25" s="61">
         <v>8</v>
       </c>
-      <c r="AA25" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB25" s="80">
+      <c r="AA25" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB25" s="79">
         <v>14</v>
       </c>
       <c r="AD25" s="11">
@@ -3339,88 +3471,90 @@
       <c r="AE25" s="8"/>
       <c r="AF25" s="7"/>
       <c r="AG25" s="26"/>
-      <c r="AI25" s="31"/>
-      <c r="AJ25" s="31"/>
-      <c r="AK25" s="31"/>
+      <c r="AI25" s="30"/>
+      <c r="AJ25" s="30"/>
+      <c r="AK25" s="30"/>
       <c r="AL25" s="9"/>
       <c r="AM25" s="9"/>
       <c r="AN25" s="9"/>
-      <c r="AO25" s="28"/>
+      <c r="AO25" s="27"/>
     </row>
     <row r="26" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A26" s="27"/>
+      <c r="B26" s="27"/>
       <c r="D26" t="s">
         <v>15</v>
       </c>
-      <c r="E26" s="76">
-        <v>13</v>
-      </c>
-      <c r="F26" s="66">
-        <v>13</v>
-      </c>
-      <c r="G26" s="69">
-        <v>5</v>
-      </c>
-      <c r="H26" s="69">
-        <v>5</v>
-      </c>
-      <c r="I26" s="69">
-        <v>5</v>
-      </c>
-      <c r="J26" s="69">
-        <v>5</v>
-      </c>
-      <c r="K26" s="69">
-        <v>5</v>
-      </c>
-      <c r="L26" s="71">
-        <v>6</v>
-      </c>
-      <c r="M26" s="71">
-        <v>6</v>
-      </c>
-      <c r="N26" s="71">
-        <v>6</v>
-      </c>
-      <c r="O26" s="71">
-        <v>6</v>
-      </c>
-      <c r="P26" s="71">
-        <v>6</v>
-      </c>
-      <c r="Q26" s="64">
+      <c r="E26" s="75">
+        <v>13</v>
+      </c>
+      <c r="F26" s="65">
+        <v>13</v>
+      </c>
+      <c r="G26" s="68">
+        <v>5</v>
+      </c>
+      <c r="H26" s="68">
+        <v>5</v>
+      </c>
+      <c r="I26" s="68">
+        <v>5</v>
+      </c>
+      <c r="J26" s="68">
+        <v>5</v>
+      </c>
+      <c r="K26" s="68">
+        <v>5</v>
+      </c>
+      <c r="L26" s="70">
+        <v>6</v>
+      </c>
+      <c r="M26" s="70">
+        <v>6</v>
+      </c>
+      <c r="N26" s="70">
+        <v>6</v>
+      </c>
+      <c r="O26" s="70">
+        <v>6</v>
+      </c>
+      <c r="P26" s="70">
+        <v>6</v>
+      </c>
+      <c r="Q26" s="63">
         <v>7</v>
       </c>
-      <c r="R26" s="64">
+      <c r="R26" s="63">
         <v>7</v>
       </c>
-      <c r="S26" s="64">
+      <c r="S26" s="63">
         <v>7</v>
       </c>
-      <c r="T26" s="64">
+      <c r="T26" s="63">
         <v>7</v>
       </c>
-      <c r="U26" s="64">
+      <c r="U26" s="63">
         <v>7</v>
       </c>
-      <c r="V26" s="62">
+      <c r="V26" s="61">
         <v>8</v>
       </c>
-      <c r="W26" s="62">
+      <c r="W26" s="61">
         <v>8</v>
       </c>
-      <c r="X26" s="62">
+      <c r="X26" s="61">
         <v>8</v>
       </c>
-      <c r="Y26" s="62">
+      <c r="Y26" s="61">
         <v>8</v>
       </c>
-      <c r="Z26" s="62">
+      <c r="Z26" s="61">
         <v>8</v>
       </c>
-      <c r="AA26" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB26" s="80">
+      <c r="AA26" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB26" s="79">
         <v>14</v>
       </c>
       <c r="AD26" s="11">
@@ -3429,88 +3563,92 @@
       <c r="AE26" s="8"/>
       <c r="AF26" s="7"/>
       <c r="AG26" s="26"/>
-      <c r="AI26" s="31"/>
-      <c r="AJ26" s="31"/>
-      <c r="AK26" s="31"/>
+      <c r="AI26" s="30"/>
+      <c r="AJ26" s="30"/>
+      <c r="AK26" s="30"/>
       <c r="AL26" s="9"/>
       <c r="AM26" s="9"/>
       <c r="AN26" s="9"/>
-      <c r="AO26" s="28"/>
+      <c r="AO26" s="27"/>
     </row>
     <row r="27" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A27" s="27"/>
+      <c r="B27" s="86" t="s">
+        <v>99</v>
+      </c>
       <c r="D27" t="s">
         <v>16</v>
       </c>
-      <c r="E27" s="76">
-        <v>13</v>
-      </c>
-      <c r="F27" s="66">
-        <v>13</v>
-      </c>
-      <c r="G27" s="69">
-        <v>5</v>
-      </c>
-      <c r="H27" s="69">
-        <v>5</v>
-      </c>
-      <c r="I27" s="69">
-        <v>5</v>
-      </c>
-      <c r="J27" s="69">
-        <v>5</v>
-      </c>
-      <c r="K27" s="69">
-        <v>5</v>
-      </c>
-      <c r="L27" s="71">
-        <v>6</v>
-      </c>
-      <c r="M27" s="71">
-        <v>6</v>
-      </c>
-      <c r="N27" s="71">
-        <v>6</v>
-      </c>
-      <c r="O27" s="71">
-        <v>6</v>
-      </c>
-      <c r="P27" s="71">
-        <v>6</v>
-      </c>
-      <c r="Q27" s="64">
+      <c r="E27" s="75">
+        <v>13</v>
+      </c>
+      <c r="F27" s="65">
+        <v>13</v>
+      </c>
+      <c r="G27" s="68">
+        <v>5</v>
+      </c>
+      <c r="H27" s="68">
+        <v>5</v>
+      </c>
+      <c r="I27" s="68">
+        <v>5</v>
+      </c>
+      <c r="J27" s="68">
+        <v>5</v>
+      </c>
+      <c r="K27" s="68">
+        <v>5</v>
+      </c>
+      <c r="L27" s="70">
+        <v>6</v>
+      </c>
+      <c r="M27" s="70">
+        <v>6</v>
+      </c>
+      <c r="N27" s="70">
+        <v>6</v>
+      </c>
+      <c r="O27" s="70">
+        <v>6</v>
+      </c>
+      <c r="P27" s="70">
+        <v>6</v>
+      </c>
+      <c r="Q27" s="63">
         <v>7</v>
       </c>
-      <c r="R27" s="64">
+      <c r="R27" s="63">
         <v>7</v>
       </c>
-      <c r="S27" s="64">
+      <c r="S27" s="63">
         <v>7</v>
       </c>
-      <c r="T27" s="64">
+      <c r="T27" s="63">
         <v>7</v>
       </c>
-      <c r="U27" s="64">
+      <c r="U27" s="63">
         <v>7</v>
       </c>
-      <c r="V27" s="62">
+      <c r="V27" s="61">
         <v>8</v>
       </c>
-      <c r="W27" s="62">
+      <c r="W27" s="61">
         <v>8</v>
       </c>
-      <c r="X27" s="62">
+      <c r="X27" s="61">
         <v>8</v>
       </c>
-      <c r="Y27" s="62">
+      <c r="Y27" s="61">
         <v>8</v>
       </c>
-      <c r="Z27" s="62">
+      <c r="Z27" s="61">
         <v>8</v>
       </c>
-      <c r="AA27" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB27" s="80">
+      <c r="AA27" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB27" s="79">
         <v>14</v>
       </c>
       <c r="AD27" s="11">
@@ -3519,88 +3657,92 @@
       <c r="AE27" s="8"/>
       <c r="AF27" s="7"/>
       <c r="AG27" s="26"/>
-      <c r="AI27" s="31"/>
-      <c r="AJ27" s="31"/>
-      <c r="AK27" s="31"/>
+      <c r="AI27" s="30"/>
+      <c r="AJ27" s="30"/>
+      <c r="AK27" s="30"/>
       <c r="AL27" s="9"/>
       <c r="AM27" s="9"/>
       <c r="AN27" s="9"/>
-      <c r="AO27" s="28"/>
+      <c r="AO27" s="27"/>
     </row>
     <row r="28" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A28" s="27">
+        <v>1</v>
+      </c>
+      <c r="B28" s="26"/>
       <c r="D28" t="s">
         <v>17</v>
       </c>
-      <c r="E28" s="76">
-        <v>13</v>
-      </c>
-      <c r="F28" s="66">
-        <v>13</v>
-      </c>
-      <c r="G28" s="69">
-        <v>5</v>
-      </c>
-      <c r="H28" s="69">
-        <v>5</v>
-      </c>
-      <c r="I28" s="69">
-        <v>5</v>
-      </c>
-      <c r="J28" s="69">
-        <v>5</v>
-      </c>
-      <c r="K28" s="69">
-        <v>5</v>
-      </c>
-      <c r="L28" s="71">
-        <v>6</v>
-      </c>
-      <c r="M28" s="71">
-        <v>6</v>
-      </c>
-      <c r="N28" s="71">
-        <v>6</v>
-      </c>
-      <c r="O28" s="71">
-        <v>6</v>
-      </c>
-      <c r="P28" s="71">
-        <v>6</v>
-      </c>
-      <c r="Q28" s="64">
+      <c r="E28" s="75">
+        <v>13</v>
+      </c>
+      <c r="F28" s="65">
+        <v>13</v>
+      </c>
+      <c r="G28" s="68">
+        <v>5</v>
+      </c>
+      <c r="H28" s="68">
+        <v>5</v>
+      </c>
+      <c r="I28" s="68">
+        <v>5</v>
+      </c>
+      <c r="J28" s="68">
+        <v>5</v>
+      </c>
+      <c r="K28" s="68">
+        <v>5</v>
+      </c>
+      <c r="L28" s="70">
+        <v>6</v>
+      </c>
+      <c r="M28" s="70">
+        <v>6</v>
+      </c>
+      <c r="N28" s="70">
+        <v>6</v>
+      </c>
+      <c r="O28" s="70">
+        <v>6</v>
+      </c>
+      <c r="P28" s="70">
+        <v>6</v>
+      </c>
+      <c r="Q28" s="63">
         <v>7</v>
       </c>
-      <c r="R28" s="64">
+      <c r="R28" s="63">
         <v>7</v>
       </c>
-      <c r="S28" s="64">
+      <c r="S28" s="63">
         <v>7</v>
       </c>
-      <c r="T28" s="64">
+      <c r="T28" s="63">
         <v>7</v>
       </c>
-      <c r="U28" s="64">
+      <c r="U28" s="63">
         <v>7</v>
       </c>
-      <c r="V28" s="62">
+      <c r="V28" s="61">
         <v>8</v>
       </c>
-      <c r="W28" s="62">
+      <c r="W28" s="61">
         <v>8</v>
       </c>
-      <c r="X28" s="62">
+      <c r="X28" s="61">
         <v>8</v>
       </c>
-      <c r="Y28" s="62">
+      <c r="Y28" s="61">
         <v>8</v>
       </c>
-      <c r="Z28" s="62">
+      <c r="Z28" s="61">
         <v>8</v>
       </c>
-      <c r="AA28" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB28" s="80">
+      <c r="AA28" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB28" s="79">
         <v>14</v>
       </c>
       <c r="AD28" s="11">
@@ -3609,88 +3751,92 @@
       <c r="AE28" s="8"/>
       <c r="AF28" s="7"/>
       <c r="AG28" s="26"/>
-      <c r="AI28" s="31"/>
-      <c r="AJ28" s="31"/>
-      <c r="AK28" s="31"/>
+      <c r="AI28" s="30"/>
+      <c r="AJ28" s="30"/>
+      <c r="AK28" s="30"/>
       <c r="AL28" s="9"/>
       <c r="AM28" s="9"/>
       <c r="AN28" s="9"/>
-      <c r="AO28" s="28"/>
+      <c r="AO28" s="27"/>
     </row>
     <row r="29" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A29" s="27">
+        <v>2</v>
+      </c>
+      <c r="B29" s="26"/>
       <c r="D29" t="s">
         <v>18</v>
       </c>
-      <c r="E29" s="76">
-        <v>13</v>
-      </c>
-      <c r="F29" s="66">
-        <v>13</v>
-      </c>
-      <c r="G29" s="69">
-        <v>5</v>
-      </c>
-      <c r="H29" s="69">
-        <v>5</v>
-      </c>
-      <c r="I29" s="69">
-        <v>5</v>
-      </c>
-      <c r="J29" s="69">
-        <v>5</v>
-      </c>
-      <c r="K29" s="69">
-        <v>5</v>
-      </c>
-      <c r="L29" s="71">
-        <v>6</v>
-      </c>
-      <c r="M29" s="71">
-        <v>6</v>
-      </c>
-      <c r="N29" s="71">
-        <v>6</v>
-      </c>
-      <c r="O29" s="71">
-        <v>6</v>
-      </c>
-      <c r="P29" s="71">
-        <v>6</v>
-      </c>
-      <c r="Q29" s="64">
+      <c r="E29" s="75">
+        <v>13</v>
+      </c>
+      <c r="F29" s="65">
+        <v>13</v>
+      </c>
+      <c r="G29" s="68">
+        <v>5</v>
+      </c>
+      <c r="H29" s="68">
+        <v>5</v>
+      </c>
+      <c r="I29" s="68">
+        <v>5</v>
+      </c>
+      <c r="J29" s="68">
+        <v>5</v>
+      </c>
+      <c r="K29" s="68">
+        <v>5</v>
+      </c>
+      <c r="L29" s="70">
+        <v>6</v>
+      </c>
+      <c r="M29" s="70">
+        <v>6</v>
+      </c>
+      <c r="N29" s="70">
+        <v>6</v>
+      </c>
+      <c r="O29" s="70">
+        <v>6</v>
+      </c>
+      <c r="P29" s="70">
+        <v>6</v>
+      </c>
+      <c r="Q29" s="63">
         <v>7</v>
       </c>
-      <c r="R29" s="64">
+      <c r="R29" s="63">
         <v>7</v>
       </c>
-      <c r="S29" s="64">
+      <c r="S29" s="63">
         <v>7</v>
       </c>
-      <c r="T29" s="64">
+      <c r="T29" s="63">
         <v>7</v>
       </c>
-      <c r="U29" s="64">
+      <c r="U29" s="63">
         <v>7</v>
       </c>
-      <c r="V29" s="62">
+      <c r="V29" s="61">
         <v>8</v>
       </c>
-      <c r="W29" s="62">
+      <c r="W29" s="61">
         <v>8</v>
       </c>
-      <c r="X29" s="62">
+      <c r="X29" s="61">
         <v>8</v>
       </c>
-      <c r="Y29" s="62">
+      <c r="Y29" s="61">
         <v>8</v>
       </c>
-      <c r="Z29" s="62">
+      <c r="Z29" s="61">
         <v>8</v>
       </c>
-      <c r="AA29" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB29" s="80">
+      <c r="AA29" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB29" s="79">
         <v>14</v>
       </c>
       <c r="AD29" s="11">
@@ -3699,88 +3845,92 @@
       <c r="AE29" s="8"/>
       <c r="AF29" s="7"/>
       <c r="AG29" s="26"/>
-      <c r="AI29" s="31"/>
-      <c r="AJ29" s="31"/>
-      <c r="AK29" s="31"/>
+      <c r="AI29" s="30"/>
+      <c r="AJ29" s="30"/>
+      <c r="AK29" s="30"/>
       <c r="AL29" s="9"/>
       <c r="AM29" s="9"/>
       <c r="AN29" s="9"/>
-      <c r="AO29" s="28"/>
+      <c r="AO29" s="27"/>
     </row>
     <row r="30" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A30" s="27">
+        <v>3</v>
+      </c>
+      <c r="B30" s="26"/>
       <c r="D30" t="s">
         <v>19</v>
       </c>
-      <c r="E30" s="76">
-        <v>13</v>
-      </c>
-      <c r="F30" s="66">
-        <v>13</v>
-      </c>
-      <c r="G30" s="69">
-        <v>5</v>
-      </c>
-      <c r="H30" s="69">
-        <v>5</v>
-      </c>
-      <c r="I30" s="69">
-        <v>5</v>
-      </c>
-      <c r="J30" s="69">
-        <v>5</v>
-      </c>
-      <c r="K30" s="69">
-        <v>5</v>
-      </c>
-      <c r="L30" s="71">
-        <v>6</v>
-      </c>
-      <c r="M30" s="71">
-        <v>6</v>
-      </c>
-      <c r="N30" s="71">
-        <v>6</v>
-      </c>
-      <c r="O30" s="71">
-        <v>6</v>
-      </c>
-      <c r="P30" s="71">
-        <v>6</v>
-      </c>
-      <c r="Q30" s="64">
+      <c r="E30" s="75">
+        <v>13</v>
+      </c>
+      <c r="F30" s="65">
+        <v>13</v>
+      </c>
+      <c r="G30" s="68">
+        <v>5</v>
+      </c>
+      <c r="H30" s="68">
+        <v>5</v>
+      </c>
+      <c r="I30" s="68">
+        <v>5</v>
+      </c>
+      <c r="J30" s="68">
+        <v>5</v>
+      </c>
+      <c r="K30" s="68">
+        <v>5</v>
+      </c>
+      <c r="L30" s="70">
+        <v>6</v>
+      </c>
+      <c r="M30" s="70">
+        <v>6</v>
+      </c>
+      <c r="N30" s="70">
+        <v>6</v>
+      </c>
+      <c r="O30" s="70">
+        <v>6</v>
+      </c>
+      <c r="P30" s="70">
+        <v>6</v>
+      </c>
+      <c r="Q30" s="63">
         <v>7</v>
       </c>
-      <c r="R30" s="64">
+      <c r="R30" s="63">
         <v>7</v>
       </c>
-      <c r="S30" s="64">
+      <c r="S30" s="63">
         <v>7</v>
       </c>
-      <c r="T30" s="64">
+      <c r="T30" s="63">
         <v>7</v>
       </c>
-      <c r="U30" s="64">
+      <c r="U30" s="63">
         <v>7</v>
       </c>
-      <c r="V30" s="62">
+      <c r="V30" s="61">
         <v>8</v>
       </c>
-      <c r="W30" s="62">
+      <c r="W30" s="61">
         <v>8</v>
       </c>
-      <c r="X30" s="62">
+      <c r="X30" s="61">
         <v>8</v>
       </c>
-      <c r="Y30" s="62">
+      <c r="Y30" s="61">
         <v>8</v>
       </c>
-      <c r="Z30" s="62">
+      <c r="Z30" s="61">
         <v>8</v>
       </c>
-      <c r="AA30" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB30" s="80">
+      <c r="AA30" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB30" s="79">
         <v>14</v>
       </c>
       <c r="AD30" s="11">
@@ -3789,88 +3939,92 @@
       <c r="AE30" s="8"/>
       <c r="AF30" s="7"/>
       <c r="AG30" s="26"/>
-      <c r="AI30" s="31"/>
-      <c r="AJ30" s="31"/>
-      <c r="AK30" s="31"/>
+      <c r="AI30" s="30"/>
+      <c r="AJ30" s="30"/>
+      <c r="AK30" s="30"/>
       <c r="AL30" s="9"/>
       <c r="AM30" s="9"/>
       <c r="AN30" s="9"/>
-      <c r="AO30" s="28"/>
+      <c r="AO30" s="27"/>
     </row>
     <row r="31" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A31" s="27">
+        <v>4</v>
+      </c>
+      <c r="B31" s="26"/>
       <c r="D31" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="76">
-        <v>13</v>
-      </c>
-      <c r="F31" s="66">
-        <v>13</v>
-      </c>
-      <c r="G31" s="69">
-        <v>5</v>
-      </c>
-      <c r="H31" s="69">
-        <v>5</v>
-      </c>
-      <c r="I31" s="69">
-        <v>5</v>
-      </c>
-      <c r="J31" s="69">
-        <v>5</v>
-      </c>
-      <c r="K31" s="69">
-        <v>5</v>
-      </c>
-      <c r="L31" s="71">
-        <v>6</v>
-      </c>
-      <c r="M31" s="71">
-        <v>6</v>
-      </c>
-      <c r="N31" s="71">
-        <v>6</v>
-      </c>
-      <c r="O31" s="71">
-        <v>6</v>
-      </c>
-      <c r="P31" s="71">
-        <v>6</v>
-      </c>
-      <c r="Q31" s="64">
+      <c r="E31" s="75">
+        <v>13</v>
+      </c>
+      <c r="F31" s="65">
+        <v>13</v>
+      </c>
+      <c r="G31" s="68">
+        <v>5</v>
+      </c>
+      <c r="H31" s="68">
+        <v>5</v>
+      </c>
+      <c r="I31" s="68">
+        <v>5</v>
+      </c>
+      <c r="J31" s="68">
+        <v>5</v>
+      </c>
+      <c r="K31" s="68">
+        <v>5</v>
+      </c>
+      <c r="L31" s="70">
+        <v>6</v>
+      </c>
+      <c r="M31" s="70">
+        <v>6</v>
+      </c>
+      <c r="N31" s="70">
+        <v>6</v>
+      </c>
+      <c r="O31" s="70">
+        <v>6</v>
+      </c>
+      <c r="P31" s="70">
+        <v>6</v>
+      </c>
+      <c r="Q31" s="63">
         <v>7</v>
       </c>
-      <c r="R31" s="64">
+      <c r="R31" s="63">
         <v>7</v>
       </c>
-      <c r="S31" s="64">
+      <c r="S31" s="63">
         <v>7</v>
       </c>
-      <c r="T31" s="64">
+      <c r="T31" s="63">
         <v>7</v>
       </c>
-      <c r="U31" s="64">
+      <c r="U31" s="63">
         <v>7</v>
       </c>
-      <c r="V31" s="62">
+      <c r="V31" s="61">
         <v>8</v>
       </c>
-      <c r="W31" s="62">
+      <c r="W31" s="61">
         <v>8</v>
       </c>
-      <c r="X31" s="62">
+      <c r="X31" s="61">
         <v>8</v>
       </c>
-      <c r="Y31" s="62">
+      <c r="Y31" s="61">
         <v>8</v>
       </c>
-      <c r="Z31" s="62">
+      <c r="Z31" s="61">
         <v>8</v>
       </c>
-      <c r="AA31" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB31" s="80">
+      <c r="AA31" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB31" s="79">
         <v>14</v>
       </c>
       <c r="AD31" s="11">
@@ -3879,88 +4033,92 @@
       <c r="AE31" s="8"/>
       <c r="AF31" s="7"/>
       <c r="AG31" s="26"/>
-      <c r="AI31" s="31"/>
-      <c r="AJ31" s="31"/>
-      <c r="AK31" s="31"/>
+      <c r="AI31" s="30"/>
+      <c r="AJ31" s="30"/>
+      <c r="AK31" s="30"/>
       <c r="AL31" s="9"/>
       <c r="AM31" s="9"/>
       <c r="AN31" s="9"/>
-      <c r="AO31" s="28"/>
+      <c r="AO31" s="27"/>
     </row>
     <row r="32" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A32" s="27">
+        <v>5</v>
+      </c>
+      <c r="B32" s="33"/>
       <c r="D32" t="s">
         <v>21</v>
       </c>
-      <c r="E32" s="76">
-        <v>13</v>
-      </c>
-      <c r="F32" s="66">
-        <v>13</v>
-      </c>
-      <c r="G32" s="69">
-        <v>5</v>
-      </c>
-      <c r="H32" s="69">
-        <v>5</v>
-      </c>
-      <c r="I32" s="69">
-        <v>5</v>
-      </c>
-      <c r="J32" s="69">
-        <v>5</v>
-      </c>
-      <c r="K32" s="69">
-        <v>5</v>
-      </c>
-      <c r="L32" s="71">
-        <v>6</v>
-      </c>
-      <c r="M32" s="71">
-        <v>6</v>
-      </c>
-      <c r="N32" s="71">
-        <v>6</v>
-      </c>
-      <c r="O32" s="71">
-        <v>6</v>
-      </c>
-      <c r="P32" s="71">
-        <v>6</v>
-      </c>
-      <c r="Q32" s="64">
+      <c r="E32" s="75">
+        <v>13</v>
+      </c>
+      <c r="F32" s="65">
+        <v>13</v>
+      </c>
+      <c r="G32" s="68">
+        <v>5</v>
+      </c>
+      <c r="H32" s="68">
+        <v>5</v>
+      </c>
+      <c r="I32" s="68">
+        <v>5</v>
+      </c>
+      <c r="J32" s="68">
+        <v>5</v>
+      </c>
+      <c r="K32" s="68">
+        <v>5</v>
+      </c>
+      <c r="L32" s="70">
+        <v>6</v>
+      </c>
+      <c r="M32" s="70">
+        <v>6</v>
+      </c>
+      <c r="N32" s="70">
+        <v>6</v>
+      </c>
+      <c r="O32" s="70">
+        <v>6</v>
+      </c>
+      <c r="P32" s="70">
+        <v>6</v>
+      </c>
+      <c r="Q32" s="63">
         <v>7</v>
       </c>
-      <c r="R32" s="64">
+      <c r="R32" s="63">
         <v>7</v>
       </c>
-      <c r="S32" s="64">
+      <c r="S32" s="63">
         <v>7</v>
       </c>
-      <c r="T32" s="64">
+      <c r="T32" s="63">
         <v>7</v>
       </c>
-      <c r="U32" s="64">
+      <c r="U32" s="63">
         <v>7</v>
       </c>
-      <c r="V32" s="62">
+      <c r="V32" s="61">
         <v>8</v>
       </c>
-      <c r="W32" s="62">
+      <c r="W32" s="61">
         <v>8</v>
       </c>
-      <c r="X32" s="62">
+      <c r="X32" s="61">
         <v>8</v>
       </c>
-      <c r="Y32" s="62">
+      <c r="Y32" s="61">
         <v>8</v>
       </c>
-      <c r="Z32" s="62">
+      <c r="Z32" s="61">
         <v>8</v>
       </c>
-      <c r="AA32" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB32" s="80">
+      <c r="AA32" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB32" s="79">
         <v>14</v>
       </c>
       <c r="AD32" s="11">
@@ -3975,82 +4133,84 @@
       <c r="AL32" s="9"/>
       <c r="AM32" s="9"/>
       <c r="AN32" s="9"/>
-      <c r="AO32" s="28"/>
+      <c r="AO32" s="27"/>
     </row>
     <row r="33" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="27"/>
+      <c r="B33" s="27"/>
       <c r="D33" t="s">
         <v>22</v>
       </c>
-      <c r="E33" s="76">
-        <v>13</v>
-      </c>
-      <c r="F33" s="66">
-        <v>13</v>
-      </c>
-      <c r="G33" s="69">
-        <v>5</v>
-      </c>
-      <c r="H33" s="69">
-        <v>5</v>
-      </c>
-      <c r="I33" s="69">
-        <v>5</v>
-      </c>
-      <c r="J33" s="69">
-        <v>5</v>
-      </c>
-      <c r="K33" s="69">
-        <v>5</v>
-      </c>
-      <c r="L33" s="71">
-        <v>6</v>
-      </c>
-      <c r="M33" s="71">
-        <v>6</v>
-      </c>
-      <c r="N33" s="71">
-        <v>6</v>
-      </c>
-      <c r="O33" s="71">
-        <v>6</v>
-      </c>
-      <c r="P33" s="71">
-        <v>6</v>
-      </c>
-      <c r="Q33" s="64">
+      <c r="E33" s="75">
+        <v>13</v>
+      </c>
+      <c r="F33" s="65">
+        <v>13</v>
+      </c>
+      <c r="G33" s="68">
+        <v>5</v>
+      </c>
+      <c r="H33" s="68">
+        <v>5</v>
+      </c>
+      <c r="I33" s="68">
+        <v>5</v>
+      </c>
+      <c r="J33" s="68">
+        <v>5</v>
+      </c>
+      <c r="K33" s="68">
+        <v>5</v>
+      </c>
+      <c r="L33" s="70">
+        <v>6</v>
+      </c>
+      <c r="M33" s="70">
+        <v>6</v>
+      </c>
+      <c r="N33" s="70">
+        <v>6</v>
+      </c>
+      <c r="O33" s="70">
+        <v>6</v>
+      </c>
+      <c r="P33" s="70">
+        <v>6</v>
+      </c>
+      <c r="Q33" s="63">
         <v>7</v>
       </c>
-      <c r="R33" s="64">
+      <c r="R33" s="63">
         <v>7</v>
       </c>
-      <c r="S33" s="64">
+      <c r="S33" s="63">
         <v>7</v>
       </c>
-      <c r="T33" s="64">
+      <c r="T33" s="63">
         <v>7</v>
       </c>
-      <c r="U33" s="64">
+      <c r="U33" s="63">
         <v>7</v>
       </c>
-      <c r="V33" s="62">
+      <c r="V33" s="61">
         <v>8</v>
       </c>
-      <c r="W33" s="62">
+      <c r="W33" s="61">
         <v>8</v>
       </c>
-      <c r="X33" s="62">
+      <c r="X33" s="61">
         <v>8</v>
       </c>
-      <c r="Y33" s="62">
+      <c r="Y33" s="61">
         <v>8</v>
       </c>
-      <c r="Z33" s="62">
+      <c r="Z33" s="61">
         <v>8</v>
       </c>
-      <c r="AA33" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB33" s="80">
+      <c r="AA33" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB33" s="79">
         <v>14</v>
       </c>
       <c r="AD33" s="11">
@@ -4061,82 +4221,82 @@
       <c r="AG33" s="26"/>
       <c r="AM33" s="9"/>
       <c r="AN33" s="9"/>
-      <c r="AO33" s="28"/>
+      <c r="AO33" s="27"/>
     </row>
     <row r="34" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D34" t="s">
         <v>23</v>
       </c>
-      <c r="E34" s="76">
-        <v>13</v>
-      </c>
-      <c r="F34" s="66">
-        <v>13</v>
-      </c>
-      <c r="G34" s="69">
-        <v>5</v>
-      </c>
-      <c r="H34" s="69">
-        <v>5</v>
-      </c>
-      <c r="I34" s="69">
-        <v>5</v>
-      </c>
-      <c r="J34" s="69">
-        <v>5</v>
-      </c>
-      <c r="K34" s="69">
-        <v>5</v>
-      </c>
-      <c r="L34" s="71">
-        <v>6</v>
-      </c>
-      <c r="M34" s="71">
-        <v>6</v>
-      </c>
-      <c r="N34" s="71">
-        <v>6</v>
-      </c>
-      <c r="O34" s="71">
-        <v>6</v>
-      </c>
-      <c r="P34" s="71">
-        <v>6</v>
-      </c>
-      <c r="Q34" s="64">
+      <c r="E34" s="75">
+        <v>13</v>
+      </c>
+      <c r="F34" s="65">
+        <v>13</v>
+      </c>
+      <c r="G34" s="68">
+        <v>5</v>
+      </c>
+      <c r="H34" s="68">
+        <v>5</v>
+      </c>
+      <c r="I34" s="68">
+        <v>5</v>
+      </c>
+      <c r="J34" s="68">
+        <v>5</v>
+      </c>
+      <c r="K34" s="68">
+        <v>5</v>
+      </c>
+      <c r="L34" s="70">
+        <v>6</v>
+      </c>
+      <c r="M34" s="70">
+        <v>6</v>
+      </c>
+      <c r="N34" s="70">
+        <v>6</v>
+      </c>
+      <c r="O34" s="70">
+        <v>6</v>
+      </c>
+      <c r="P34" s="70">
+        <v>6</v>
+      </c>
+      <c r="Q34" s="63">
         <v>7</v>
       </c>
-      <c r="R34" s="64">
+      <c r="R34" s="63">
         <v>7</v>
       </c>
-      <c r="S34" s="64">
+      <c r="S34" s="63">
         <v>7</v>
       </c>
-      <c r="T34" s="64">
+      <c r="T34" s="63">
         <v>7</v>
       </c>
-      <c r="U34" s="64">
+      <c r="U34" s="63">
         <v>7</v>
       </c>
-      <c r="V34" s="62">
+      <c r="V34" s="61">
         <v>8</v>
       </c>
-      <c r="W34" s="62">
+      <c r="W34" s="61">
         <v>8</v>
       </c>
-      <c r="X34" s="62">
+      <c r="X34" s="61">
         <v>8</v>
       </c>
-      <c r="Y34" s="62">
+      <c r="Y34" s="61">
         <v>8</v>
       </c>
-      <c r="Z34" s="62">
+      <c r="Z34" s="61">
         <v>8</v>
       </c>
-      <c r="AA34" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB34" s="80">
+      <c r="AA34" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB34" s="79">
         <v>14</v>
       </c>
       <c r="AD34" s="11">
@@ -4150,76 +4310,76 @@
       <c r="D35" t="s">
         <v>24</v>
       </c>
-      <c r="E35" s="76">
-        <v>13</v>
-      </c>
-      <c r="F35" s="66">
-        <v>13</v>
-      </c>
-      <c r="G35" s="69">
-        <v>5</v>
-      </c>
-      <c r="H35" s="69">
-        <v>5</v>
-      </c>
-      <c r="I35" s="69">
-        <v>5</v>
-      </c>
-      <c r="J35" s="69">
-        <v>5</v>
-      </c>
-      <c r="K35" s="69">
-        <v>5</v>
-      </c>
-      <c r="L35" s="71">
-        <v>6</v>
-      </c>
-      <c r="M35" s="71">
-        <v>6</v>
-      </c>
-      <c r="N35" s="71">
-        <v>6</v>
-      </c>
-      <c r="O35" s="71">
-        <v>6</v>
-      </c>
-      <c r="P35" s="71">
-        <v>6</v>
-      </c>
-      <c r="Q35" s="64">
+      <c r="E35" s="75">
+        <v>13</v>
+      </c>
+      <c r="F35" s="65">
+        <v>13</v>
+      </c>
+      <c r="G35" s="68">
+        <v>5</v>
+      </c>
+      <c r="H35" s="68">
+        <v>5</v>
+      </c>
+      <c r="I35" s="68">
+        <v>5</v>
+      </c>
+      <c r="J35" s="68">
+        <v>5</v>
+      </c>
+      <c r="K35" s="68">
+        <v>5</v>
+      </c>
+      <c r="L35" s="70">
+        <v>6</v>
+      </c>
+      <c r="M35" s="70">
+        <v>6</v>
+      </c>
+      <c r="N35" s="70">
+        <v>6</v>
+      </c>
+      <c r="O35" s="70">
+        <v>6</v>
+      </c>
+      <c r="P35" s="70">
+        <v>6</v>
+      </c>
+      <c r="Q35" s="63">
         <v>7</v>
       </c>
-      <c r="R35" s="64">
+      <c r="R35" s="63">
         <v>7</v>
       </c>
-      <c r="S35" s="64">
+      <c r="S35" s="63">
         <v>7</v>
       </c>
-      <c r="T35" s="64">
+      <c r="T35" s="63">
         <v>7</v>
       </c>
-      <c r="U35" s="64">
+      <c r="U35" s="63">
         <v>7</v>
       </c>
-      <c r="V35" s="62">
+      <c r="V35" s="61">
         <v>8</v>
       </c>
-      <c r="W35" s="62">
+      <c r="W35" s="61">
         <v>8</v>
       </c>
-      <c r="X35" s="62">
+      <c r="X35" s="61">
         <v>8</v>
       </c>
-      <c r="Y35" s="62">
+      <c r="Y35" s="61">
         <v>8</v>
       </c>
-      <c r="Z35" s="62">
+      <c r="Z35" s="61">
         <v>8</v>
       </c>
-      <c r="AA35" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB35" s="80">
+      <c r="AA35" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB35" s="79">
         <v>14</v>
       </c>
       <c r="AD35" s="11">
@@ -4233,76 +4393,76 @@
       <c r="D36" t="s">
         <v>25</v>
       </c>
-      <c r="E36" s="76">
-        <v>13</v>
-      </c>
-      <c r="F36" s="66">
-        <v>13</v>
-      </c>
-      <c r="G36" s="69">
-        <v>5</v>
-      </c>
-      <c r="H36" s="69">
-        <v>5</v>
-      </c>
-      <c r="I36" s="69">
-        <v>5</v>
-      </c>
-      <c r="J36" s="69">
-        <v>5</v>
-      </c>
-      <c r="K36" s="69">
-        <v>5</v>
-      </c>
-      <c r="L36" s="71">
-        <v>6</v>
-      </c>
-      <c r="M36" s="71">
-        <v>6</v>
-      </c>
-      <c r="N36" s="71">
-        <v>6</v>
-      </c>
-      <c r="O36" s="71">
-        <v>6</v>
-      </c>
-      <c r="P36" s="71">
-        <v>6</v>
-      </c>
-      <c r="Q36" s="64">
+      <c r="E36" s="75">
+        <v>13</v>
+      </c>
+      <c r="F36" s="65">
+        <v>13</v>
+      </c>
+      <c r="G36" s="68">
+        <v>5</v>
+      </c>
+      <c r="H36" s="68">
+        <v>5</v>
+      </c>
+      <c r="I36" s="68">
+        <v>5</v>
+      </c>
+      <c r="J36" s="68">
+        <v>5</v>
+      </c>
+      <c r="K36" s="68">
+        <v>5</v>
+      </c>
+      <c r="L36" s="70">
+        <v>6</v>
+      </c>
+      <c r="M36" s="70">
+        <v>6</v>
+      </c>
+      <c r="N36" s="70">
+        <v>6</v>
+      </c>
+      <c r="O36" s="70">
+        <v>6</v>
+      </c>
+      <c r="P36" s="70">
+        <v>6</v>
+      </c>
+      <c r="Q36" s="63">
         <v>7</v>
       </c>
-      <c r="R36" s="64">
+      <c r="R36" s="63">
         <v>7</v>
       </c>
-      <c r="S36" s="64">
+      <c r="S36" s="63">
         <v>7</v>
       </c>
-      <c r="T36" s="64">
+      <c r="T36" s="63">
         <v>7</v>
       </c>
-      <c r="U36" s="64">
+      <c r="U36" s="63">
         <v>7</v>
       </c>
-      <c r="V36" s="62">
+      <c r="V36" s="61">
         <v>8</v>
       </c>
-      <c r="W36" s="62">
+      <c r="W36" s="61">
         <v>8</v>
       </c>
-      <c r="X36" s="62">
+      <c r="X36" s="61">
         <v>8</v>
       </c>
-      <c r="Y36" s="62">
+      <c r="Y36" s="61">
         <v>8</v>
       </c>
-      <c r="Z36" s="62">
+      <c r="Z36" s="61">
         <v>8</v>
       </c>
-      <c r="AA36" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB36" s="80">
+      <c r="AA36" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB36" s="79">
         <v>14</v>
       </c>
       <c r="AD36" s="11">
@@ -4316,76 +4476,76 @@
       <c r="D37" t="s">
         <v>26</v>
       </c>
-      <c r="E37" s="76">
-        <v>13</v>
-      </c>
-      <c r="F37" s="66">
-        <v>13</v>
-      </c>
-      <c r="G37" s="69">
-        <v>5</v>
-      </c>
-      <c r="H37" s="69">
-        <v>5</v>
-      </c>
-      <c r="I37" s="69">
-        <v>5</v>
-      </c>
-      <c r="J37" s="69">
-        <v>5</v>
-      </c>
-      <c r="K37" s="69">
-        <v>5</v>
-      </c>
-      <c r="L37" s="71">
-        <v>6</v>
-      </c>
-      <c r="M37" s="71">
-        <v>6</v>
-      </c>
-      <c r="N37" s="71">
-        <v>6</v>
-      </c>
-      <c r="O37" s="71">
-        <v>6</v>
-      </c>
-      <c r="P37" s="71">
-        <v>6</v>
-      </c>
-      <c r="Q37" s="64">
+      <c r="E37" s="75">
+        <v>13</v>
+      </c>
+      <c r="F37" s="65">
+        <v>13</v>
+      </c>
+      <c r="G37" s="68">
+        <v>5</v>
+      </c>
+      <c r="H37" s="68">
+        <v>5</v>
+      </c>
+      <c r="I37" s="68">
+        <v>5</v>
+      </c>
+      <c r="J37" s="68">
+        <v>5</v>
+      </c>
+      <c r="K37" s="68">
+        <v>5</v>
+      </c>
+      <c r="L37" s="70">
+        <v>6</v>
+      </c>
+      <c r="M37" s="70">
+        <v>6</v>
+      </c>
+      <c r="N37" s="70">
+        <v>6</v>
+      </c>
+      <c r="O37" s="70">
+        <v>6</v>
+      </c>
+      <c r="P37" s="70">
+        <v>6</v>
+      </c>
+      <c r="Q37" s="63">
         <v>7</v>
       </c>
-      <c r="R37" s="64">
+      <c r="R37" s="63">
         <v>7</v>
       </c>
-      <c r="S37" s="64">
+      <c r="S37" s="63">
         <v>7</v>
       </c>
-      <c r="T37" s="64">
+      <c r="T37" s="63">
         <v>7</v>
       </c>
-      <c r="U37" s="64">
+      <c r="U37" s="63">
         <v>7</v>
       </c>
-      <c r="V37" s="62">
+      <c r="V37" s="61">
         <v>8</v>
       </c>
-      <c r="W37" s="62">
+      <c r="W37" s="61">
         <v>8</v>
       </c>
-      <c r="X37" s="62">
+      <c r="X37" s="61">
         <v>8</v>
       </c>
-      <c r="Y37" s="62">
+      <c r="Y37" s="61">
         <v>8</v>
       </c>
-      <c r="Z37" s="62">
+      <c r="Z37" s="61">
         <v>8</v>
       </c>
-      <c r="AA37" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB37" s="80">
+      <c r="AA37" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB37" s="79">
         <v>14</v>
       </c>
       <c r="AD37" s="11">
@@ -4399,76 +4559,76 @@
       <c r="D38" t="s">
         <v>27</v>
       </c>
-      <c r="E38" s="76">
-        <v>13</v>
-      </c>
-      <c r="F38" s="66">
-        <v>13</v>
-      </c>
-      <c r="G38" s="69">
-        <v>5</v>
-      </c>
-      <c r="H38" s="69">
-        <v>5</v>
-      </c>
-      <c r="I38" s="69">
-        <v>5</v>
-      </c>
-      <c r="J38" s="69">
-        <v>5</v>
-      </c>
-      <c r="K38" s="69">
-        <v>5</v>
-      </c>
-      <c r="L38" s="71">
-        <v>6</v>
-      </c>
-      <c r="M38" s="71">
-        <v>6</v>
-      </c>
-      <c r="N38" s="71">
-        <v>6</v>
-      </c>
-      <c r="O38" s="71">
-        <v>6</v>
-      </c>
-      <c r="P38" s="71">
-        <v>6</v>
-      </c>
-      <c r="Q38" s="64">
+      <c r="E38" s="75">
+        <v>13</v>
+      </c>
+      <c r="F38" s="65">
+        <v>13</v>
+      </c>
+      <c r="G38" s="68">
+        <v>5</v>
+      </c>
+      <c r="H38" s="68">
+        <v>5</v>
+      </c>
+      <c r="I38" s="68">
+        <v>5</v>
+      </c>
+      <c r="J38" s="68">
+        <v>5</v>
+      </c>
+      <c r="K38" s="68">
+        <v>5</v>
+      </c>
+      <c r="L38" s="70">
+        <v>6</v>
+      </c>
+      <c r="M38" s="70">
+        <v>6</v>
+      </c>
+      <c r="N38" s="70">
+        <v>6</v>
+      </c>
+      <c r="O38" s="70">
+        <v>6</v>
+      </c>
+      <c r="P38" s="70">
+        <v>6</v>
+      </c>
+      <c r="Q38" s="63">
         <v>7</v>
       </c>
-      <c r="R38" s="64">
+      <c r="R38" s="63">
         <v>7</v>
       </c>
-      <c r="S38" s="64">
+      <c r="S38" s="63">
         <v>7</v>
       </c>
-      <c r="T38" s="64">
+      <c r="T38" s="63">
         <v>7</v>
       </c>
-      <c r="U38" s="64">
+      <c r="U38" s="63">
         <v>7</v>
       </c>
-      <c r="V38" s="62">
+      <c r="V38" s="61">
         <v>8</v>
       </c>
-      <c r="W38" s="62">
+      <c r="W38" s="61">
         <v>8</v>
       </c>
-      <c r="X38" s="62">
+      <c r="X38" s="61">
         <v>8</v>
       </c>
-      <c r="Y38" s="62">
+      <c r="Y38" s="61">
         <v>8</v>
       </c>
-      <c r="Z38" s="62">
+      <c r="Z38" s="61">
         <v>8</v>
       </c>
-      <c r="AA38" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB38" s="80">
+      <c r="AA38" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB38" s="79">
         <v>14</v>
       </c>
       <c r="AD38" s="11">
@@ -4482,76 +4642,76 @@
       <c r="D39" t="s">
         <v>28</v>
       </c>
-      <c r="E39" s="77">
+      <c r="E39" s="76">
         <v>16</v>
       </c>
-      <c r="F39" s="67">
+      <c r="F39" s="66">
         <v>16</v>
       </c>
-      <c r="G39" s="69">
-        <v>5</v>
-      </c>
-      <c r="H39" s="69">
-        <v>5</v>
-      </c>
-      <c r="I39" s="69">
-        <v>5</v>
-      </c>
-      <c r="J39" s="69">
-        <v>5</v>
-      </c>
-      <c r="K39" s="69">
-        <v>5</v>
-      </c>
-      <c r="L39" s="71">
-        <v>6</v>
-      </c>
-      <c r="M39" s="71">
-        <v>6</v>
-      </c>
-      <c r="N39" s="71">
-        <v>6</v>
-      </c>
-      <c r="O39" s="71">
-        <v>6</v>
-      </c>
-      <c r="P39" s="71">
-        <v>6</v>
-      </c>
-      <c r="Q39" s="64">
+      <c r="G39" s="68">
+        <v>5</v>
+      </c>
+      <c r="H39" s="68">
+        <v>5</v>
+      </c>
+      <c r="I39" s="68">
+        <v>5</v>
+      </c>
+      <c r="J39" s="68">
+        <v>5</v>
+      </c>
+      <c r="K39" s="68">
+        <v>5</v>
+      </c>
+      <c r="L39" s="70">
+        <v>6</v>
+      </c>
+      <c r="M39" s="70">
+        <v>6</v>
+      </c>
+      <c r="N39" s="70">
+        <v>6</v>
+      </c>
+      <c r="O39" s="70">
+        <v>6</v>
+      </c>
+      <c r="P39" s="70">
+        <v>6</v>
+      </c>
+      <c r="Q39" s="63">
         <v>7</v>
       </c>
-      <c r="R39" s="64">
+      <c r="R39" s="63">
         <v>7</v>
       </c>
-      <c r="S39" s="64">
+      <c r="S39" s="63">
         <v>7</v>
       </c>
-      <c r="T39" s="64">
+      <c r="T39" s="63">
         <v>7</v>
       </c>
-      <c r="U39" s="64">
+      <c r="U39" s="63">
         <v>7</v>
       </c>
-      <c r="V39" s="62">
+      <c r="V39" s="61">
         <v>8</v>
       </c>
-      <c r="W39" s="62">
+      <c r="W39" s="61">
         <v>8</v>
       </c>
-      <c r="X39" s="62">
+      <c r="X39" s="61">
         <v>8</v>
       </c>
-      <c r="Y39" s="62">
+      <c r="Y39" s="61">
         <v>8</v>
       </c>
-      <c r="Z39" s="62">
+      <c r="Z39" s="61">
         <v>8</v>
       </c>
-      <c r="AA39" s="67">
+      <c r="AA39" s="66">
         <v>16</v>
       </c>
-      <c r="AB39" s="78">
+      <c r="AB39" s="77">
         <v>16</v>
       </c>
       <c r="AD39" s="11">
@@ -4595,14 +4755,14 @@
       <c r="AE40" s="8"/>
       <c r="AF40" s="10"/>
       <c r="AG40" s="10"/>
-      <c r="AJ40" s="30"/>
-      <c r="AK40" s="30"/>
+      <c r="AJ40" s="29"/>
+      <c r="AK40" s="29"/>
     </row>
     <row r="41" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A41" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B41" s="4" t="s">
+      <c r="A41" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" s="83" t="s">
         <v>10</v>
       </c>
       <c r="D41" t="s">
@@ -4686,15 +4846,15 @@
       <c r="AE41" s="8"/>
       <c r="AF41" s="10"/>
       <c r="AG41" s="10"/>
-      <c r="AJ41" s="30"/>
-      <c r="AK41" s="30"/>
+      <c r="AJ41" s="29"/>
+      <c r="AK41" s="29"/>
     </row>
     <row r="42" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A42" s="93" t="s">
-        <v>14</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>66</v>
+      <c r="A42" s="84" t="s">
+        <v>14</v>
+      </c>
+      <c r="B42" s="85" t="s">
+        <v>63</v>
       </c>
       <c r="D42" t="s">
         <v>13</v>
@@ -4705,64 +4865,64 @@
       <c r="F42" s="14">
         <v>15</v>
       </c>
-      <c r="G42" s="43">
-        <v>9</v>
-      </c>
-      <c r="H42" s="43">
-        <v>9</v>
-      </c>
-      <c r="I42" s="43">
-        <v>9</v>
-      </c>
-      <c r="J42" s="43">
-        <v>9</v>
-      </c>
-      <c r="K42" s="43">
-        <v>9</v>
-      </c>
-      <c r="L42" s="45">
-        <v>10</v>
-      </c>
-      <c r="M42" s="45">
-        <v>10</v>
-      </c>
-      <c r="N42" s="45">
-        <v>10</v>
-      </c>
-      <c r="O42" s="45">
-        <v>10</v>
-      </c>
-      <c r="P42" s="45">
-        <v>10</v>
-      </c>
-      <c r="Q42" s="47">
+      <c r="G42" s="42">
+        <v>9</v>
+      </c>
+      <c r="H42" s="42">
+        <v>9</v>
+      </c>
+      <c r="I42" s="42">
+        <v>9</v>
+      </c>
+      <c r="J42" s="42">
+        <v>9</v>
+      </c>
+      <c r="K42" s="42">
+        <v>9</v>
+      </c>
+      <c r="L42" s="44">
+        <v>10</v>
+      </c>
+      <c r="M42" s="44">
+        <v>10</v>
+      </c>
+      <c r="N42" s="44">
+        <v>10</v>
+      </c>
+      <c r="O42" s="44">
+        <v>10</v>
+      </c>
+      <c r="P42" s="44">
+        <v>10</v>
+      </c>
+      <c r="Q42" s="46">
         <v>11</v>
       </c>
-      <c r="R42" s="47">
+      <c r="R42" s="46">
         <v>11</v>
       </c>
-      <c r="S42" s="47">
+      <c r="S42" s="46">
         <v>11</v>
       </c>
-      <c r="T42" s="47">
+      <c r="T42" s="46">
         <v>11</v>
       </c>
-      <c r="U42" s="47">
+      <c r="U42" s="46">
         <v>11</v>
       </c>
-      <c r="V42" s="49">
+      <c r="V42" s="48">
         <v>12</v>
       </c>
-      <c r="W42" s="49">
+      <c r="W42" s="48">
         <v>12</v>
       </c>
-      <c r="X42" s="49">
+      <c r="X42" s="48">
         <v>12</v>
       </c>
-      <c r="Y42" s="49">
+      <c r="Y42" s="48">
         <v>12</v>
       </c>
-      <c r="Z42" s="49">
+      <c r="Z42" s="48">
         <v>12</v>
       </c>
       <c r="AA42" s="14">
@@ -4779,79 +4939,81 @@
       <c r="AG42" s="10"/>
     </row>
     <row r="43" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A43" s="27"/>
+      <c r="B43" s="27"/>
       <c r="D43" t="s">
         <v>14</v>
       </c>
-      <c r="E43" s="76">
-        <v>13</v>
-      </c>
-      <c r="F43" s="66">
-        <v>13</v>
-      </c>
-      <c r="G43" s="44">
-        <v>9</v>
-      </c>
-      <c r="H43" s="44">
-        <v>9</v>
-      </c>
-      <c r="I43" s="44">
-        <v>9</v>
-      </c>
-      <c r="J43" s="44">
-        <v>9</v>
-      </c>
-      <c r="K43" s="44">
-        <v>9</v>
-      </c>
-      <c r="L43" s="46">
-        <v>10</v>
-      </c>
-      <c r="M43" s="46">
-        <v>10</v>
-      </c>
-      <c r="N43" s="46">
-        <v>10</v>
-      </c>
-      <c r="O43" s="46">
-        <v>10</v>
-      </c>
-      <c r="P43" s="46">
-        <v>10</v>
-      </c>
-      <c r="Q43" s="48">
+      <c r="E43" s="75">
+        <v>13</v>
+      </c>
+      <c r="F43" s="65">
+        <v>13</v>
+      </c>
+      <c r="G43" s="43">
+        <v>9</v>
+      </c>
+      <c r="H43" s="43">
+        <v>9</v>
+      </c>
+      <c r="I43" s="43">
+        <v>9</v>
+      </c>
+      <c r="J43" s="43">
+        <v>9</v>
+      </c>
+      <c r="K43" s="43">
+        <v>9</v>
+      </c>
+      <c r="L43" s="45">
+        <v>10</v>
+      </c>
+      <c r="M43" s="45">
+        <v>10</v>
+      </c>
+      <c r="N43" s="45">
+        <v>10</v>
+      </c>
+      <c r="O43" s="45">
+        <v>10</v>
+      </c>
+      <c r="P43" s="45">
+        <v>10</v>
+      </c>
+      <c r="Q43" s="47">
         <v>11</v>
       </c>
-      <c r="R43" s="48">
+      <c r="R43" s="47">
         <v>11</v>
       </c>
-      <c r="S43" s="48">
+      <c r="S43" s="47">
         <v>11</v>
       </c>
-      <c r="T43" s="48">
+      <c r="T43" s="47">
         <v>11</v>
       </c>
-      <c r="U43" s="48">
+      <c r="U43" s="47">
         <v>11</v>
       </c>
-      <c r="V43" s="50">
+      <c r="V43" s="49">
         <v>12</v>
       </c>
-      <c r="W43" s="50">
+      <c r="W43" s="49">
         <v>12</v>
       </c>
-      <c r="X43" s="50">
+      <c r="X43" s="49">
         <v>12</v>
       </c>
-      <c r="Y43" s="50">
+      <c r="Y43" s="49">
         <v>12</v>
       </c>
-      <c r="Z43" s="50">
+      <c r="Z43" s="49">
         <v>12</v>
       </c>
-      <c r="AA43" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB43" s="79">
+      <c r="AA43" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB43" s="78">
         <v>14</v>
       </c>
       <c r="AD43" s="11">
@@ -4862,79 +5024,81 @@
       <c r="AG43" s="10"/>
     </row>
     <row r="44" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A44" s="27"/>
+      <c r="B44" s="27"/>
       <c r="D44" t="s">
         <v>15</v>
       </c>
-      <c r="E44" s="76">
-        <v>13</v>
-      </c>
-      <c r="F44" s="66">
-        <v>13</v>
-      </c>
-      <c r="G44" s="44">
-        <v>9</v>
-      </c>
-      <c r="H44" s="44">
-        <v>9</v>
-      </c>
-      <c r="I44" s="44">
-        <v>9</v>
-      </c>
-      <c r="J44" s="44">
-        <v>9</v>
-      </c>
-      <c r="K44" s="44">
-        <v>9</v>
-      </c>
-      <c r="L44" s="46">
-        <v>10</v>
-      </c>
-      <c r="M44" s="46">
-        <v>10</v>
-      </c>
-      <c r="N44" s="46">
-        <v>10</v>
-      </c>
-      <c r="O44" s="46">
-        <v>10</v>
-      </c>
-      <c r="P44" s="46">
-        <v>10</v>
-      </c>
-      <c r="Q44" s="48">
+      <c r="E44" s="75">
+        <v>13</v>
+      </c>
+      <c r="F44" s="65">
+        <v>13</v>
+      </c>
+      <c r="G44" s="43">
+        <v>9</v>
+      </c>
+      <c r="H44" s="43">
+        <v>9</v>
+      </c>
+      <c r="I44" s="43">
+        <v>9</v>
+      </c>
+      <c r="J44" s="43">
+        <v>9</v>
+      </c>
+      <c r="K44" s="43">
+        <v>9</v>
+      </c>
+      <c r="L44" s="45">
+        <v>10</v>
+      </c>
+      <c r="M44" s="45">
+        <v>10</v>
+      </c>
+      <c r="N44" s="45">
+        <v>10</v>
+      </c>
+      <c r="O44" s="45">
+        <v>10</v>
+      </c>
+      <c r="P44" s="45">
+        <v>10</v>
+      </c>
+      <c r="Q44" s="47">
         <v>11</v>
       </c>
-      <c r="R44" s="48">
+      <c r="R44" s="47">
         <v>11</v>
       </c>
-      <c r="S44" s="48">
+      <c r="S44" s="47">
         <v>11</v>
       </c>
-      <c r="T44" s="48">
+      <c r="T44" s="47">
         <v>11</v>
       </c>
-      <c r="U44" s="48">
+      <c r="U44" s="47">
         <v>11</v>
       </c>
-      <c r="V44" s="50">
+      <c r="V44" s="49">
         <v>12</v>
       </c>
-      <c r="W44" s="50">
+      <c r="W44" s="49">
         <v>12</v>
       </c>
-      <c r="X44" s="50">
+      <c r="X44" s="49">
         <v>12</v>
       </c>
-      <c r="Y44" s="50">
+      <c r="Y44" s="49">
         <v>12</v>
       </c>
-      <c r="Z44" s="50">
+      <c r="Z44" s="49">
         <v>12</v>
       </c>
-      <c r="AA44" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB44" s="79">
+      <c r="AA44" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB44" s="78">
         <v>14</v>
       </c>
       <c r="AD44" s="11">
@@ -4945,79 +5109,83 @@
       <c r="AG44" s="10"/>
     </row>
     <row r="45" spans="1:41" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="27"/>
+      <c r="B45" s="86" t="s">
+        <v>99</v>
+      </c>
       <c r="D45" t="s">
         <v>16</v>
       </c>
-      <c r="E45" s="76">
-        <v>13</v>
-      </c>
-      <c r="F45" s="66">
-        <v>13</v>
-      </c>
-      <c r="G45" s="44">
-        <v>9</v>
-      </c>
-      <c r="H45" s="44">
-        <v>9</v>
-      </c>
-      <c r="I45" s="44">
-        <v>9</v>
-      </c>
-      <c r="J45" s="44">
-        <v>9</v>
-      </c>
-      <c r="K45" s="44">
-        <v>9</v>
-      </c>
-      <c r="L45" s="46">
-        <v>10</v>
-      </c>
-      <c r="M45" s="46">
-        <v>10</v>
-      </c>
-      <c r="N45" s="46">
-        <v>10</v>
-      </c>
-      <c r="O45" s="46">
-        <v>10</v>
-      </c>
-      <c r="P45" s="46">
-        <v>10</v>
-      </c>
-      <c r="Q45" s="48">
+      <c r="E45" s="75">
+        <v>13</v>
+      </c>
+      <c r="F45" s="65">
+        <v>13</v>
+      </c>
+      <c r="G45" s="43">
+        <v>9</v>
+      </c>
+      <c r="H45" s="43">
+        <v>9</v>
+      </c>
+      <c r="I45" s="43">
+        <v>9</v>
+      </c>
+      <c r="J45" s="43">
+        <v>9</v>
+      </c>
+      <c r="K45" s="43">
+        <v>9</v>
+      </c>
+      <c r="L45" s="45">
+        <v>10</v>
+      </c>
+      <c r="M45" s="45">
+        <v>10</v>
+      </c>
+      <c r="N45" s="45">
+        <v>10</v>
+      </c>
+      <c r="O45" s="45">
+        <v>10</v>
+      </c>
+      <c r="P45" s="45">
+        <v>10</v>
+      </c>
+      <c r="Q45" s="47">
         <v>11</v>
       </c>
-      <c r="R45" s="48">
+      <c r="R45" s="47">
         <v>11</v>
       </c>
-      <c r="S45" s="48">
+      <c r="S45" s="47">
         <v>11</v>
       </c>
-      <c r="T45" s="48">
+      <c r="T45" s="47">
         <v>11</v>
       </c>
-      <c r="U45" s="48">
+      <c r="U45" s="47">
         <v>11</v>
       </c>
-      <c r="V45" s="50">
+      <c r="V45" s="49">
         <v>12</v>
       </c>
-      <c r="W45" s="50">
+      <c r="W45" s="49">
         <v>12</v>
       </c>
-      <c r="X45" s="50">
+      <c r="X45" s="49">
         <v>12</v>
       </c>
-      <c r="Y45" s="50">
+      <c r="Y45" s="49">
         <v>12</v>
       </c>
-      <c r="Z45" s="50">
+      <c r="Z45" s="49">
         <v>12</v>
       </c>
-      <c r="AA45" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB45" s="79">
+      <c r="AA45" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB45" s="78">
         <v>14</v>
       </c>
       <c r="AD45" s="11">
@@ -5028,79 +5196,83 @@
       <c r="AG45" s="10"/>
     </row>
     <row r="46" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A46" s="27">
+        <v>1</v>
+      </c>
+      <c r="B46" s="26"/>
       <c r="D46" t="s">
         <v>17</v>
       </c>
-      <c r="E46" s="76">
-        <v>13</v>
-      </c>
-      <c r="F46" s="66">
-        <v>13</v>
-      </c>
-      <c r="G46" s="44">
-        <v>9</v>
-      </c>
-      <c r="H46" s="44">
-        <v>9</v>
-      </c>
-      <c r="I46" s="44">
-        <v>9</v>
-      </c>
-      <c r="J46" s="44">
-        <v>9</v>
-      </c>
-      <c r="K46" s="44">
-        <v>9</v>
-      </c>
-      <c r="L46" s="46">
-        <v>10</v>
-      </c>
-      <c r="M46" s="46">
-        <v>10</v>
-      </c>
-      <c r="N46" s="46">
-        <v>10</v>
-      </c>
-      <c r="O46" s="46">
-        <v>10</v>
-      </c>
-      <c r="P46" s="46">
-        <v>10</v>
-      </c>
-      <c r="Q46" s="48">
+      <c r="E46" s="75">
+        <v>13</v>
+      </c>
+      <c r="F46" s="65">
+        <v>13</v>
+      </c>
+      <c r="G46" s="43">
+        <v>9</v>
+      </c>
+      <c r="H46" s="43">
+        <v>9</v>
+      </c>
+      <c r="I46" s="43">
+        <v>9</v>
+      </c>
+      <c r="J46" s="43">
+        <v>9</v>
+      </c>
+      <c r="K46" s="43">
+        <v>9</v>
+      </c>
+      <c r="L46" s="45">
+        <v>10</v>
+      </c>
+      <c r="M46" s="45">
+        <v>10</v>
+      </c>
+      <c r="N46" s="45">
+        <v>10</v>
+      </c>
+      <c r="O46" s="45">
+        <v>10</v>
+      </c>
+      <c r="P46" s="45">
+        <v>10</v>
+      </c>
+      <c r="Q46" s="47">
         <v>11</v>
       </c>
-      <c r="R46" s="48">
+      <c r="R46" s="47">
         <v>11</v>
       </c>
-      <c r="S46" s="48">
+      <c r="S46" s="47">
         <v>11</v>
       </c>
-      <c r="T46" s="48">
+      <c r="T46" s="47">
         <v>11</v>
       </c>
-      <c r="U46" s="48">
+      <c r="U46" s="47">
         <v>11</v>
       </c>
-      <c r="V46" s="50">
+      <c r="V46" s="49">
         <v>12</v>
       </c>
-      <c r="W46" s="50">
+      <c r="W46" s="49">
         <v>12</v>
       </c>
-      <c r="X46" s="50">
+      <c r="X46" s="49">
         <v>12</v>
       </c>
-      <c r="Y46" s="50">
+      <c r="Y46" s="49">
         <v>12</v>
       </c>
-      <c r="Z46" s="50">
+      <c r="Z46" s="49">
         <v>12</v>
       </c>
-      <c r="AA46" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB46" s="79">
+      <c r="AA46" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB46" s="78">
         <v>14</v>
       </c>
       <c r="AD46" s="11">
@@ -5111,79 +5283,83 @@
       <c r="AG46" s="10"/>
     </row>
     <row r="47" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A47" s="27">
+        <v>2</v>
+      </c>
+      <c r="B47" s="26"/>
       <c r="D47" t="s">
         <v>18</v>
       </c>
-      <c r="E47" s="76">
-        <v>13</v>
-      </c>
-      <c r="F47" s="66">
-        <v>13</v>
-      </c>
-      <c r="G47" s="44">
-        <v>9</v>
-      </c>
-      <c r="H47" s="44">
-        <v>9</v>
-      </c>
-      <c r="I47" s="44">
-        <v>9</v>
-      </c>
-      <c r="J47" s="44">
-        <v>9</v>
-      </c>
-      <c r="K47" s="44">
-        <v>9</v>
-      </c>
-      <c r="L47" s="46">
-        <v>10</v>
-      </c>
-      <c r="M47" s="46">
-        <v>10</v>
-      </c>
-      <c r="N47" s="46">
-        <v>10</v>
-      </c>
-      <c r="O47" s="46">
-        <v>10</v>
-      </c>
-      <c r="P47" s="46">
-        <v>10</v>
-      </c>
-      <c r="Q47" s="48">
+      <c r="E47" s="75">
+        <v>13</v>
+      </c>
+      <c r="F47" s="65">
+        <v>13</v>
+      </c>
+      <c r="G47" s="43">
+        <v>9</v>
+      </c>
+      <c r="H47" s="43">
+        <v>9</v>
+      </c>
+      <c r="I47" s="43">
+        <v>9</v>
+      </c>
+      <c r="J47" s="43">
+        <v>9</v>
+      </c>
+      <c r="K47" s="43">
+        <v>9</v>
+      </c>
+      <c r="L47" s="45">
+        <v>10</v>
+      </c>
+      <c r="M47" s="45">
+        <v>10</v>
+      </c>
+      <c r="N47" s="45">
+        <v>10</v>
+      </c>
+      <c r="O47" s="45">
+        <v>10</v>
+      </c>
+      <c r="P47" s="45">
+        <v>10</v>
+      </c>
+      <c r="Q47" s="47">
         <v>11</v>
       </c>
-      <c r="R47" s="48">
+      <c r="R47" s="47">
         <v>11</v>
       </c>
-      <c r="S47" s="48">
+      <c r="S47" s="47">
         <v>11</v>
       </c>
-      <c r="T47" s="48">
+      <c r="T47" s="47">
         <v>11</v>
       </c>
-      <c r="U47" s="48">
+      <c r="U47" s="47">
         <v>11</v>
       </c>
-      <c r="V47" s="50">
+      <c r="V47" s="49">
         <v>12</v>
       </c>
-      <c r="W47" s="50">
+      <c r="W47" s="49">
         <v>12</v>
       </c>
-      <c r="X47" s="50">
+      <c r="X47" s="49">
         <v>12</v>
       </c>
-      <c r="Y47" s="50">
+      <c r="Y47" s="49">
         <v>12</v>
       </c>
-      <c r="Z47" s="50">
+      <c r="Z47" s="49">
         <v>12</v>
       </c>
-      <c r="AA47" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB47" s="79">
+      <c r="AA47" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB47" s="78">
         <v>14</v>
       </c>
       <c r="AD47" s="11">
@@ -5194,79 +5370,83 @@
       <c r="AG47" s="10"/>
     </row>
     <row r="48" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A48" s="27">
+        <v>3</v>
+      </c>
+      <c r="B48" s="26"/>
       <c r="D48" t="s">
         <v>19</v>
       </c>
-      <c r="E48" s="76">
-        <v>13</v>
-      </c>
-      <c r="F48" s="66">
-        <v>13</v>
-      </c>
-      <c r="G48" s="44">
-        <v>9</v>
-      </c>
-      <c r="H48" s="44">
-        <v>9</v>
-      </c>
-      <c r="I48" s="44">
-        <v>9</v>
-      </c>
-      <c r="J48" s="44">
-        <v>9</v>
-      </c>
-      <c r="K48" s="44">
-        <v>9</v>
-      </c>
-      <c r="L48" s="46">
-        <v>10</v>
-      </c>
-      <c r="M48" s="46">
-        <v>10</v>
-      </c>
-      <c r="N48" s="46">
-        <v>10</v>
-      </c>
-      <c r="O48" s="46">
-        <v>10</v>
-      </c>
-      <c r="P48" s="46">
-        <v>10</v>
-      </c>
-      <c r="Q48" s="48">
+      <c r="E48" s="75">
+        <v>13</v>
+      </c>
+      <c r="F48" s="65">
+        <v>13</v>
+      </c>
+      <c r="G48" s="43">
+        <v>9</v>
+      </c>
+      <c r="H48" s="43">
+        <v>9</v>
+      </c>
+      <c r="I48" s="43">
+        <v>9</v>
+      </c>
+      <c r="J48" s="43">
+        <v>9</v>
+      </c>
+      <c r="K48" s="43">
+        <v>9</v>
+      </c>
+      <c r="L48" s="45">
+        <v>10</v>
+      </c>
+      <c r="M48" s="45">
+        <v>10</v>
+      </c>
+      <c r="N48" s="45">
+        <v>10</v>
+      </c>
+      <c r="O48" s="45">
+        <v>10</v>
+      </c>
+      <c r="P48" s="45">
+        <v>10</v>
+      </c>
+      <c r="Q48" s="47">
         <v>11</v>
       </c>
-      <c r="R48" s="48">
+      <c r="R48" s="47">
         <v>11</v>
       </c>
-      <c r="S48" s="48">
+      <c r="S48" s="47">
         <v>11</v>
       </c>
-      <c r="T48" s="48">
+      <c r="T48" s="47">
         <v>11</v>
       </c>
-      <c r="U48" s="48">
+      <c r="U48" s="47">
         <v>11</v>
       </c>
-      <c r="V48" s="50">
+      <c r="V48" s="49">
         <v>12</v>
       </c>
-      <c r="W48" s="50">
+      <c r="W48" s="49">
         <v>12</v>
       </c>
-      <c r="X48" s="50">
+      <c r="X48" s="49">
         <v>12</v>
       </c>
-      <c r="Y48" s="50">
+      <c r="Y48" s="49">
         <v>12</v>
       </c>
-      <c r="Z48" s="50">
+      <c r="Z48" s="49">
         <v>12</v>
       </c>
-      <c r="AA48" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB48" s="79">
+      <c r="AA48" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB48" s="78">
         <v>14</v>
       </c>
       <c r="AD48" s="11">
@@ -5277,79 +5457,83 @@
       <c r="AG48" s="10"/>
     </row>
     <row r="49" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A49" s="27">
+        <v>4</v>
+      </c>
+      <c r="B49" s="26"/>
       <c r="D49" t="s">
         <v>20</v>
       </c>
-      <c r="E49" s="76">
-        <v>13</v>
-      </c>
-      <c r="F49" s="66">
-        <v>13</v>
-      </c>
-      <c r="G49" s="44">
-        <v>9</v>
-      </c>
-      <c r="H49" s="44">
-        <v>9</v>
-      </c>
-      <c r="I49" s="44">
-        <v>9</v>
-      </c>
-      <c r="J49" s="44">
-        <v>9</v>
-      </c>
-      <c r="K49" s="44">
-        <v>9</v>
-      </c>
-      <c r="L49" s="46">
-        <v>10</v>
-      </c>
-      <c r="M49" s="46">
-        <v>10</v>
-      </c>
-      <c r="N49" s="46">
-        <v>10</v>
-      </c>
-      <c r="O49" s="46">
-        <v>10</v>
-      </c>
-      <c r="P49" s="46">
-        <v>10</v>
-      </c>
-      <c r="Q49" s="48">
+      <c r="E49" s="75">
+        <v>13</v>
+      </c>
+      <c r="F49" s="65">
+        <v>13</v>
+      </c>
+      <c r="G49" s="43">
+        <v>9</v>
+      </c>
+      <c r="H49" s="43">
+        <v>9</v>
+      </c>
+      <c r="I49" s="43">
+        <v>9</v>
+      </c>
+      <c r="J49" s="43">
+        <v>9</v>
+      </c>
+      <c r="K49" s="43">
+        <v>9</v>
+      </c>
+      <c r="L49" s="45">
+        <v>10</v>
+      </c>
+      <c r="M49" s="45">
+        <v>10</v>
+      </c>
+      <c r="N49" s="45">
+        <v>10</v>
+      </c>
+      <c r="O49" s="45">
+        <v>10</v>
+      </c>
+      <c r="P49" s="45">
+        <v>10</v>
+      </c>
+      <c r="Q49" s="47">
         <v>11</v>
       </c>
-      <c r="R49" s="48">
+      <c r="R49" s="47">
         <v>11</v>
       </c>
-      <c r="S49" s="48">
+      <c r="S49" s="47">
         <v>11</v>
       </c>
-      <c r="T49" s="48">
+      <c r="T49" s="47">
         <v>11</v>
       </c>
-      <c r="U49" s="48">
+      <c r="U49" s="47">
         <v>11</v>
       </c>
-      <c r="V49" s="50">
+      <c r="V49" s="49">
         <v>12</v>
       </c>
-      <c r="W49" s="50">
+      <c r="W49" s="49">
         <v>12</v>
       </c>
-      <c r="X49" s="50">
+      <c r="X49" s="49">
         <v>12</v>
       </c>
-      <c r="Y49" s="50">
+      <c r="Y49" s="49">
         <v>12</v>
       </c>
-      <c r="Z49" s="50">
+      <c r="Z49" s="49">
         <v>12</v>
       </c>
-      <c r="AA49" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB49" s="79">
+      <c r="AA49" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB49" s="78">
         <v>14</v>
       </c>
       <c r="AD49" s="11">
@@ -5360,79 +5544,83 @@
       <c r="AG49" s="10"/>
     </row>
     <row r="50" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A50" s="27">
+        <v>5</v>
+      </c>
+      <c r="B50" s="33"/>
       <c r="D50" t="s">
         <v>21</v>
       </c>
-      <c r="E50" s="76">
-        <v>13</v>
-      </c>
-      <c r="F50" s="66">
-        <v>13</v>
-      </c>
-      <c r="G50" s="44">
-        <v>9</v>
-      </c>
-      <c r="H50" s="44">
-        <v>9</v>
-      </c>
-      <c r="I50" s="44">
-        <v>9</v>
-      </c>
-      <c r="J50" s="44">
-        <v>9</v>
-      </c>
-      <c r="K50" s="44">
-        <v>9</v>
-      </c>
-      <c r="L50" s="46">
-        <v>10</v>
-      </c>
-      <c r="M50" s="46">
-        <v>10</v>
-      </c>
-      <c r="N50" s="46">
-        <v>10</v>
-      </c>
-      <c r="O50" s="46">
-        <v>10</v>
-      </c>
-      <c r="P50" s="46">
-        <v>10</v>
-      </c>
-      <c r="Q50" s="48">
+      <c r="E50" s="75">
+        <v>13</v>
+      </c>
+      <c r="F50" s="65">
+        <v>13</v>
+      </c>
+      <c r="G50" s="43">
+        <v>9</v>
+      </c>
+      <c r="H50" s="43">
+        <v>9</v>
+      </c>
+      <c r="I50" s="43">
+        <v>9</v>
+      </c>
+      <c r="J50" s="43">
+        <v>9</v>
+      </c>
+      <c r="K50" s="43">
+        <v>9</v>
+      </c>
+      <c r="L50" s="45">
+        <v>10</v>
+      </c>
+      <c r="M50" s="45">
+        <v>10</v>
+      </c>
+      <c r="N50" s="45">
+        <v>10</v>
+      </c>
+      <c r="O50" s="45">
+        <v>10</v>
+      </c>
+      <c r="P50" s="45">
+        <v>10</v>
+      </c>
+      <c r="Q50" s="47">
         <v>11</v>
       </c>
-      <c r="R50" s="48">
+      <c r="R50" s="47">
         <v>11</v>
       </c>
-      <c r="S50" s="48">
+      <c r="S50" s="47">
         <v>11</v>
       </c>
-      <c r="T50" s="48">
+      <c r="T50" s="47">
         <v>11</v>
       </c>
-      <c r="U50" s="48">
+      <c r="U50" s="47">
         <v>11</v>
       </c>
-      <c r="V50" s="50">
+      <c r="V50" s="49">
         <v>12</v>
       </c>
-      <c r="W50" s="50">
+      <c r="W50" s="49">
         <v>12</v>
       </c>
-      <c r="X50" s="50">
+      <c r="X50" s="49">
         <v>12</v>
       </c>
-      <c r="Y50" s="50">
+      <c r="Y50" s="49">
         <v>12</v>
       </c>
-      <c r="Z50" s="50">
+      <c r="Z50" s="49">
         <v>12</v>
       </c>
-      <c r="AA50" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB50" s="79">
+      <c r="AA50" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB50" s="78">
         <v>14</v>
       </c>
       <c r="AD50" s="11">
@@ -5443,79 +5631,81 @@
       <c r="AG50" s="10"/>
     </row>
     <row r="51" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A51" s="27"/>
+      <c r="B51" s="27"/>
       <c r="D51" t="s">
         <v>22</v>
       </c>
-      <c r="E51" s="76">
-        <v>13</v>
-      </c>
-      <c r="F51" s="66">
-        <v>13</v>
-      </c>
-      <c r="G51" s="44">
-        <v>9</v>
-      </c>
-      <c r="H51" s="44">
-        <v>9</v>
-      </c>
-      <c r="I51" s="44">
-        <v>9</v>
-      </c>
-      <c r="J51" s="44">
-        <v>9</v>
-      </c>
-      <c r="K51" s="44">
-        <v>9</v>
-      </c>
-      <c r="L51" s="46">
-        <v>10</v>
-      </c>
-      <c r="M51" s="46">
-        <v>10</v>
-      </c>
-      <c r="N51" s="46">
-        <v>10</v>
-      </c>
-      <c r="O51" s="46">
-        <v>10</v>
-      </c>
-      <c r="P51" s="46">
-        <v>10</v>
-      </c>
-      <c r="Q51" s="48">
+      <c r="E51" s="75">
+        <v>13</v>
+      </c>
+      <c r="F51" s="65">
+        <v>13</v>
+      </c>
+      <c r="G51" s="43">
+        <v>9</v>
+      </c>
+      <c r="H51" s="43">
+        <v>9</v>
+      </c>
+      <c r="I51" s="43">
+        <v>9</v>
+      </c>
+      <c r="J51" s="43">
+        <v>9</v>
+      </c>
+      <c r="K51" s="43">
+        <v>9</v>
+      </c>
+      <c r="L51" s="45">
+        <v>10</v>
+      </c>
+      <c r="M51" s="45">
+        <v>10</v>
+      </c>
+      <c r="N51" s="45">
+        <v>10</v>
+      </c>
+      <c r="O51" s="45">
+        <v>10</v>
+      </c>
+      <c r="P51" s="45">
+        <v>10</v>
+      </c>
+      <c r="Q51" s="47">
         <v>11</v>
       </c>
-      <c r="R51" s="48">
+      <c r="R51" s="47">
         <v>11</v>
       </c>
-      <c r="S51" s="48">
+      <c r="S51" s="47">
         <v>11</v>
       </c>
-      <c r="T51" s="48">
+      <c r="T51" s="47">
         <v>11</v>
       </c>
-      <c r="U51" s="48">
+      <c r="U51" s="47">
         <v>11</v>
       </c>
-      <c r="V51" s="50">
+      <c r="V51" s="49">
         <v>12</v>
       </c>
-      <c r="W51" s="50">
+      <c r="W51" s="49">
         <v>12</v>
       </c>
-      <c r="X51" s="50">
+      <c r="X51" s="49">
         <v>12</v>
       </c>
-      <c r="Y51" s="50">
+      <c r="Y51" s="49">
         <v>12</v>
       </c>
-      <c r="Z51" s="50">
+      <c r="Z51" s="49">
         <v>12</v>
       </c>
-      <c r="AA51" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB51" s="79">
+      <c r="AA51" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB51" s="78">
         <v>14</v>
       </c>
       <c r="AD51" s="17">
@@ -5529,76 +5719,76 @@
       <c r="D52" t="s">
         <v>23</v>
       </c>
-      <c r="E52" s="76">
-        <v>13</v>
-      </c>
-      <c r="F52" s="66">
-        <v>13</v>
-      </c>
-      <c r="G52" s="44">
-        <v>9</v>
-      </c>
-      <c r="H52" s="44">
-        <v>9</v>
-      </c>
-      <c r="I52" s="44">
-        <v>9</v>
-      </c>
-      <c r="J52" s="44">
-        <v>9</v>
-      </c>
-      <c r="K52" s="44">
-        <v>9</v>
-      </c>
-      <c r="L52" s="46">
-        <v>10</v>
-      </c>
-      <c r="M52" s="46">
-        <v>10</v>
-      </c>
-      <c r="N52" s="46">
-        <v>10</v>
-      </c>
-      <c r="O52" s="46">
-        <v>10</v>
-      </c>
-      <c r="P52" s="46">
-        <v>10</v>
-      </c>
-      <c r="Q52" s="48">
+      <c r="E52" s="75">
+        <v>13</v>
+      </c>
+      <c r="F52" s="65">
+        <v>13</v>
+      </c>
+      <c r="G52" s="43">
+        <v>9</v>
+      </c>
+      <c r="H52" s="43">
+        <v>9</v>
+      </c>
+      <c r="I52" s="43">
+        <v>9</v>
+      </c>
+      <c r="J52" s="43">
+        <v>9</v>
+      </c>
+      <c r="K52" s="43">
+        <v>9</v>
+      </c>
+      <c r="L52" s="45">
+        <v>10</v>
+      </c>
+      <c r="M52" s="45">
+        <v>10</v>
+      </c>
+      <c r="N52" s="45">
+        <v>10</v>
+      </c>
+      <c r="O52" s="45">
+        <v>10</v>
+      </c>
+      <c r="P52" s="45">
+        <v>10</v>
+      </c>
+      <c r="Q52" s="47">
         <v>11</v>
       </c>
-      <c r="R52" s="48">
+      <c r="R52" s="47">
         <v>11</v>
       </c>
-      <c r="S52" s="48">
+      <c r="S52" s="47">
         <v>11</v>
       </c>
-      <c r="T52" s="48">
+      <c r="T52" s="47">
         <v>11</v>
       </c>
-      <c r="U52" s="48">
+      <c r="U52" s="47">
         <v>11</v>
       </c>
-      <c r="V52" s="50">
+      <c r="V52" s="49">
         <v>12</v>
       </c>
-      <c r="W52" s="50">
+      <c r="W52" s="49">
         <v>12</v>
       </c>
-      <c r="X52" s="50">
+      <c r="X52" s="49">
         <v>12</v>
       </c>
-      <c r="Y52" s="50">
+      <c r="Y52" s="49">
         <v>12</v>
       </c>
-      <c r="Z52" s="50">
+      <c r="Z52" s="49">
         <v>12</v>
       </c>
-      <c r="AA52" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB52" s="79">
+      <c r="AA52" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB52" s="78">
         <v>14</v>
       </c>
     </row>
@@ -5606,76 +5796,76 @@
       <c r="D53" t="s">
         <v>24</v>
       </c>
-      <c r="E53" s="76">
-        <v>13</v>
-      </c>
-      <c r="F53" s="66">
-        <v>13</v>
-      </c>
-      <c r="G53" s="44">
-        <v>9</v>
-      </c>
-      <c r="H53" s="44">
-        <v>9</v>
-      </c>
-      <c r="I53" s="44">
-        <v>9</v>
-      </c>
-      <c r="J53" s="44">
-        <v>9</v>
-      </c>
-      <c r="K53" s="44">
-        <v>9</v>
-      </c>
-      <c r="L53" s="46">
-        <v>10</v>
-      </c>
-      <c r="M53" s="46">
-        <v>10</v>
-      </c>
-      <c r="N53" s="46">
-        <v>10</v>
-      </c>
-      <c r="O53" s="46">
-        <v>10</v>
-      </c>
-      <c r="P53" s="46">
-        <v>10</v>
-      </c>
-      <c r="Q53" s="48">
+      <c r="E53" s="75">
+        <v>13</v>
+      </c>
+      <c r="F53" s="65">
+        <v>13</v>
+      </c>
+      <c r="G53" s="43">
+        <v>9</v>
+      </c>
+      <c r="H53" s="43">
+        <v>9</v>
+      </c>
+      <c r="I53" s="43">
+        <v>9</v>
+      </c>
+      <c r="J53" s="43">
+        <v>9</v>
+      </c>
+      <c r="K53" s="43">
+        <v>9</v>
+      </c>
+      <c r="L53" s="45">
+        <v>10</v>
+      </c>
+      <c r="M53" s="45">
+        <v>10</v>
+      </c>
+      <c r="N53" s="45">
+        <v>10</v>
+      </c>
+      <c r="O53" s="45">
+        <v>10</v>
+      </c>
+      <c r="P53" s="45">
+        <v>10</v>
+      </c>
+      <c r="Q53" s="47">
         <v>11</v>
       </c>
-      <c r="R53" s="48">
+      <c r="R53" s="47">
         <v>11</v>
       </c>
-      <c r="S53" s="48">
+      <c r="S53" s="47">
         <v>11</v>
       </c>
-      <c r="T53" s="48">
+      <c r="T53" s="47">
         <v>11</v>
       </c>
-      <c r="U53" s="48">
+      <c r="U53" s="47">
         <v>11</v>
       </c>
-      <c r="V53" s="50">
+      <c r="V53" s="49">
         <v>12</v>
       </c>
-      <c r="W53" s="50">
+      <c r="W53" s="49">
         <v>12</v>
       </c>
-      <c r="X53" s="50">
+      <c r="X53" s="49">
         <v>12</v>
       </c>
-      <c r="Y53" s="50">
+      <c r="Y53" s="49">
         <v>12</v>
       </c>
-      <c r="Z53" s="50">
+      <c r="Z53" s="49">
         <v>12</v>
       </c>
-      <c r="AA53" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB53" s="79">
+      <c r="AA53" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB53" s="78">
         <v>14</v>
       </c>
       <c r="AE53" s="20"/>
@@ -5687,76 +5877,76 @@
       <c r="D54" t="s">
         <v>25</v>
       </c>
-      <c r="E54" s="76">
-        <v>13</v>
-      </c>
-      <c r="F54" s="66">
-        <v>13</v>
-      </c>
-      <c r="G54" s="44">
-        <v>9</v>
-      </c>
-      <c r="H54" s="44">
-        <v>9</v>
-      </c>
-      <c r="I54" s="44">
-        <v>9</v>
-      </c>
-      <c r="J54" s="44">
-        <v>9</v>
-      </c>
-      <c r="K54" s="44">
-        <v>9</v>
-      </c>
-      <c r="L54" s="46">
-        <v>10</v>
-      </c>
-      <c r="M54" s="46">
-        <v>10</v>
-      </c>
-      <c r="N54" s="46">
-        <v>10</v>
-      </c>
-      <c r="O54" s="46">
-        <v>10</v>
-      </c>
-      <c r="P54" s="46">
-        <v>10</v>
-      </c>
-      <c r="Q54" s="48">
+      <c r="E54" s="75">
+        <v>13</v>
+      </c>
+      <c r="F54" s="65">
+        <v>13</v>
+      </c>
+      <c r="G54" s="43">
+        <v>9</v>
+      </c>
+      <c r="H54" s="43">
+        <v>9</v>
+      </c>
+      <c r="I54" s="43">
+        <v>9</v>
+      </c>
+      <c r="J54" s="43">
+        <v>9</v>
+      </c>
+      <c r="K54" s="43">
+        <v>9</v>
+      </c>
+      <c r="L54" s="45">
+        <v>10</v>
+      </c>
+      <c r="M54" s="45">
+        <v>10</v>
+      </c>
+      <c r="N54" s="45">
+        <v>10</v>
+      </c>
+      <c r="O54" s="45">
+        <v>10</v>
+      </c>
+      <c r="P54" s="45">
+        <v>10</v>
+      </c>
+      <c r="Q54" s="47">
         <v>11</v>
       </c>
-      <c r="R54" s="48">
+      <c r="R54" s="47">
         <v>11</v>
       </c>
-      <c r="S54" s="48">
+      <c r="S54" s="47">
         <v>11</v>
       </c>
-      <c r="T54" s="48">
+      <c r="T54" s="47">
         <v>11</v>
       </c>
-      <c r="U54" s="48">
+      <c r="U54" s="47">
         <v>11</v>
       </c>
-      <c r="V54" s="50">
+      <c r="V54" s="49">
         <v>12</v>
       </c>
-      <c r="W54" s="50">
+      <c r="W54" s="49">
         <v>12</v>
       </c>
-      <c r="X54" s="50">
+      <c r="X54" s="49">
         <v>12</v>
       </c>
-      <c r="Y54" s="50">
+      <c r="Y54" s="49">
         <v>12</v>
       </c>
-      <c r="Z54" s="50">
+      <c r="Z54" s="49">
         <v>12</v>
       </c>
-      <c r="AA54" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB54" s="79">
+      <c r="AA54" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB54" s="78">
         <v>14</v>
       </c>
       <c r="AE54" s="20"/>
@@ -5768,76 +5958,76 @@
       <c r="D55" t="s">
         <v>26</v>
       </c>
-      <c r="E55" s="76">
-        <v>13</v>
-      </c>
-      <c r="F55" s="66">
-        <v>13</v>
-      </c>
-      <c r="G55" s="44">
-        <v>9</v>
-      </c>
-      <c r="H55" s="44">
-        <v>9</v>
-      </c>
-      <c r="I55" s="44">
-        <v>9</v>
-      </c>
-      <c r="J55" s="44">
-        <v>9</v>
-      </c>
-      <c r="K55" s="44">
-        <v>9</v>
-      </c>
-      <c r="L55" s="46">
-        <v>10</v>
-      </c>
-      <c r="M55" s="46">
-        <v>10</v>
-      </c>
-      <c r="N55" s="46">
-        <v>10</v>
-      </c>
-      <c r="O55" s="46">
-        <v>10</v>
-      </c>
-      <c r="P55" s="46">
-        <v>10</v>
-      </c>
-      <c r="Q55" s="48">
+      <c r="E55" s="75">
+        <v>13</v>
+      </c>
+      <c r="F55" s="65">
+        <v>13</v>
+      </c>
+      <c r="G55" s="43">
+        <v>9</v>
+      </c>
+      <c r="H55" s="43">
+        <v>9</v>
+      </c>
+      <c r="I55" s="43">
+        <v>9</v>
+      </c>
+      <c r="J55" s="43">
+        <v>9</v>
+      </c>
+      <c r="K55" s="43">
+        <v>9</v>
+      </c>
+      <c r="L55" s="45">
+        <v>10</v>
+      </c>
+      <c r="M55" s="45">
+        <v>10</v>
+      </c>
+      <c r="N55" s="45">
+        <v>10</v>
+      </c>
+      <c r="O55" s="45">
+        <v>10</v>
+      </c>
+      <c r="P55" s="45">
+        <v>10</v>
+      </c>
+      <c r="Q55" s="47">
         <v>11</v>
       </c>
-      <c r="R55" s="48">
+      <c r="R55" s="47">
         <v>11</v>
       </c>
-      <c r="S55" s="48">
+      <c r="S55" s="47">
         <v>11</v>
       </c>
-      <c r="T55" s="48">
+      <c r="T55" s="47">
         <v>11</v>
       </c>
-      <c r="U55" s="48">
+      <c r="U55" s="47">
         <v>11</v>
       </c>
-      <c r="V55" s="50">
+      <c r="V55" s="49">
         <v>12</v>
       </c>
-      <c r="W55" s="50">
+      <c r="W55" s="49">
         <v>12</v>
       </c>
-      <c r="X55" s="50">
+      <c r="X55" s="49">
         <v>12</v>
       </c>
-      <c r="Y55" s="50">
+      <c r="Y55" s="49">
         <v>12</v>
       </c>
-      <c r="Z55" s="50">
+      <c r="Z55" s="49">
         <v>12</v>
       </c>
-      <c r="AA55" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB55" s="79">
+      <c r="AA55" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB55" s="78">
         <v>14</v>
       </c>
       <c r="AE55" s="20"/>
@@ -5849,76 +6039,76 @@
       <c r="D56" t="s">
         <v>27</v>
       </c>
-      <c r="E56" s="76">
-        <v>13</v>
-      </c>
-      <c r="F56" s="66">
-        <v>13</v>
-      </c>
-      <c r="G56" s="44">
-        <v>9</v>
-      </c>
-      <c r="H56" s="44">
-        <v>9</v>
-      </c>
-      <c r="I56" s="44">
-        <v>9</v>
-      </c>
-      <c r="J56" s="44">
-        <v>9</v>
-      </c>
-      <c r="K56" s="44">
-        <v>9</v>
-      </c>
-      <c r="L56" s="46">
-        <v>10</v>
-      </c>
-      <c r="M56" s="46">
-        <v>10</v>
-      </c>
-      <c r="N56" s="46">
-        <v>10</v>
-      </c>
-      <c r="O56" s="46">
-        <v>10</v>
-      </c>
-      <c r="P56" s="46">
-        <v>10</v>
-      </c>
-      <c r="Q56" s="48">
+      <c r="E56" s="75">
+        <v>13</v>
+      </c>
+      <c r="F56" s="65">
+        <v>13</v>
+      </c>
+      <c r="G56" s="43">
+        <v>9</v>
+      </c>
+      <c r="H56" s="43">
+        <v>9</v>
+      </c>
+      <c r="I56" s="43">
+        <v>9</v>
+      </c>
+      <c r="J56" s="43">
+        <v>9</v>
+      </c>
+      <c r="K56" s="43">
+        <v>9</v>
+      </c>
+      <c r="L56" s="45">
+        <v>10</v>
+      </c>
+      <c r="M56" s="45">
+        <v>10</v>
+      </c>
+      <c r="N56" s="45">
+        <v>10</v>
+      </c>
+      <c r="O56" s="45">
+        <v>10</v>
+      </c>
+      <c r="P56" s="45">
+        <v>10</v>
+      </c>
+      <c r="Q56" s="47">
         <v>11</v>
       </c>
-      <c r="R56" s="48">
+      <c r="R56" s="47">
         <v>11</v>
       </c>
-      <c r="S56" s="48">
+      <c r="S56" s="47">
         <v>11</v>
       </c>
-      <c r="T56" s="48">
+      <c r="T56" s="47">
         <v>11</v>
       </c>
-      <c r="U56" s="48">
+      <c r="U56" s="47">
         <v>11</v>
       </c>
-      <c r="V56" s="50">
+      <c r="V56" s="49">
         <v>12</v>
       </c>
-      <c r="W56" s="50">
+      <c r="W56" s="49">
         <v>12</v>
       </c>
-      <c r="X56" s="50">
+      <c r="X56" s="49">
         <v>12</v>
       </c>
-      <c r="Y56" s="50">
+      <c r="Y56" s="49">
         <v>12</v>
       </c>
-      <c r="Z56" s="50">
+      <c r="Z56" s="49">
         <v>12</v>
       </c>
-      <c r="AA56" s="79">
-        <v>14</v>
-      </c>
-      <c r="AB56" s="79">
+      <c r="AA56" s="78">
+        <v>14</v>
+      </c>
+      <c r="AB56" s="78">
         <v>14</v>
       </c>
       <c r="AE56" s="9"/>
@@ -5927,76 +6117,76 @@
       <c r="D57" t="s">
         <v>28</v>
       </c>
-      <c r="E57" s="77">
+      <c r="E57" s="76">
         <v>16</v>
       </c>
-      <c r="F57" s="67">
+      <c r="F57" s="66">
         <v>16</v>
       </c>
-      <c r="G57" s="44">
-        <v>9</v>
-      </c>
-      <c r="H57" s="44">
-        <v>9</v>
-      </c>
-      <c r="I57" s="44">
-        <v>9</v>
-      </c>
-      <c r="J57" s="44">
-        <v>9</v>
-      </c>
-      <c r="K57" s="44">
-        <v>9</v>
-      </c>
-      <c r="L57" s="46">
-        <v>10</v>
-      </c>
-      <c r="M57" s="46">
-        <v>10</v>
-      </c>
-      <c r="N57" s="46">
-        <v>10</v>
-      </c>
-      <c r="O57" s="46">
-        <v>10</v>
-      </c>
-      <c r="P57" s="46">
-        <v>10</v>
-      </c>
-      <c r="Q57" s="48">
+      <c r="G57" s="43">
+        <v>9</v>
+      </c>
+      <c r="H57" s="43">
+        <v>9</v>
+      </c>
+      <c r="I57" s="43">
+        <v>9</v>
+      </c>
+      <c r="J57" s="43">
+        <v>9</v>
+      </c>
+      <c r="K57" s="43">
+        <v>9</v>
+      </c>
+      <c r="L57" s="45">
+        <v>10</v>
+      </c>
+      <c r="M57" s="45">
+        <v>10</v>
+      </c>
+      <c r="N57" s="45">
+        <v>10</v>
+      </c>
+      <c r="O57" s="45">
+        <v>10</v>
+      </c>
+      <c r="P57" s="45">
+        <v>10</v>
+      </c>
+      <c r="Q57" s="47">
         <v>11</v>
       </c>
-      <c r="R57" s="48">
+      <c r="R57" s="47">
         <v>11</v>
       </c>
-      <c r="S57" s="48">
+      <c r="S57" s="47">
         <v>11</v>
       </c>
-      <c r="T57" s="48">
+      <c r="T57" s="47">
         <v>11</v>
       </c>
-      <c r="U57" s="48">
+      <c r="U57" s="47">
         <v>11</v>
       </c>
-      <c r="V57" s="50">
+      <c r="V57" s="49">
         <v>12</v>
       </c>
-      <c r="W57" s="50">
+      <c r="W57" s="49">
         <v>12</v>
       </c>
-      <c r="X57" s="50">
+      <c r="X57" s="49">
         <v>12</v>
       </c>
-      <c r="Y57" s="50">
+      <c r="Y57" s="49">
         <v>12</v>
       </c>
-      <c r="Z57" s="50">
+      <c r="Z57" s="49">
         <v>12</v>
       </c>
-      <c r="AA57" s="67">
+      <c r="AA57" s="66">
         <v>16</v>
       </c>
-      <c r="AB57" s="67">
+      <c r="AB57" s="66">
         <v>16</v>
       </c>
       <c r="AE57" s="9"/>
@@ -6040,6 +6230,89 @@
       <c r="AN58" s="20"/>
     </row>
     <row r="59" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A59" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B59" s="83" t="s">
+        <v>10</v>
+      </c>
+      <c r="C59" s="87"/>
+      <c r="D59" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E59" s="27">
+        <v>1</v>
+      </c>
+      <c r="F59" s="27">
+        <v>2</v>
+      </c>
+      <c r="G59" s="27">
+        <v>3</v>
+      </c>
+      <c r="H59" s="27">
+        <v>4</v>
+      </c>
+      <c r="I59" s="27">
+        <v>5</v>
+      </c>
+      <c r="J59" s="27">
+        <v>6</v>
+      </c>
+      <c r="K59" s="27">
+        <v>7</v>
+      </c>
+      <c r="L59" s="27">
+        <v>8</v>
+      </c>
+      <c r="M59" s="27">
+        <v>9</v>
+      </c>
+      <c r="N59" s="27">
+        <v>10</v>
+      </c>
+      <c r="O59" s="27">
+        <v>11</v>
+      </c>
+      <c r="P59" s="27">
+        <v>12</v>
+      </c>
+      <c r="Q59" s="27">
+        <v>13</v>
+      </c>
+      <c r="R59" s="27">
+        <v>14</v>
+      </c>
+      <c r="S59" s="27">
+        <v>15</v>
+      </c>
+      <c r="T59" s="27">
+        <v>16</v>
+      </c>
+      <c r="U59" s="27">
+        <v>17</v>
+      </c>
+      <c r="V59" s="27">
+        <v>18</v>
+      </c>
+      <c r="W59" s="27">
+        <v>19</v>
+      </c>
+      <c r="X59" s="27">
+        <v>20</v>
+      </c>
+      <c r="Y59" s="27">
+        <v>21</v>
+      </c>
+      <c r="Z59" s="27">
+        <v>22</v>
+      </c>
+      <c r="AA59" s="27">
+        <v>23</v>
+      </c>
+      <c r="AB59" s="27">
+        <v>24</v>
+      </c>
+      <c r="AC59" s="87"/>
       <c r="AE59" s="9"/>
       <c r="AK59" s="20"/>
       <c r="AL59" s="21"/>
@@ -6047,16 +6320,581 @@
       <c r="AN59" s="20"/>
     </row>
     <row r="60" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A60" s="84" t="s">
+        <v>101</v>
+      </c>
+      <c r="B60" s="85"/>
+      <c r="C60" s="87"/>
+      <c r="D60" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" s="88"/>
+      <c r="F60" s="89"/>
+      <c r="G60" s="89"/>
+      <c r="H60" s="89"/>
+      <c r="I60" s="89"/>
+      <c r="J60" s="89"/>
+      <c r="K60" s="89"/>
+      <c r="L60" s="89"/>
+      <c r="M60" s="89"/>
+      <c r="N60" s="89"/>
+      <c r="O60" s="89"/>
+      <c r="P60" s="89"/>
+      <c r="Q60" s="89"/>
+      <c r="R60" s="89"/>
+      <c r="S60" s="89"/>
+      <c r="T60" s="89"/>
+      <c r="U60" s="89"/>
+      <c r="V60" s="89"/>
+      <c r="W60" s="89"/>
+      <c r="X60" s="89"/>
+      <c r="Y60" s="89"/>
+      <c r="Z60" s="89"/>
+      <c r="AA60" s="89"/>
+      <c r="AB60" s="90"/>
+      <c r="AC60" s="87"/>
       <c r="AE60" s="9"/>
     </row>
     <row r="61" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A61" s="27"/>
+      <c r="B61" s="27"/>
+      <c r="C61" s="87"/>
+      <c r="D61" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" s="91"/>
+      <c r="F61" s="92"/>
+      <c r="G61" s="92"/>
+      <c r="H61" s="92"/>
+      <c r="I61" s="92"/>
+      <c r="J61" s="92"/>
+      <c r="K61" s="92"/>
+      <c r="L61" s="92"/>
+      <c r="M61" s="92"/>
+      <c r="N61" s="92"/>
+      <c r="O61" s="92"/>
+      <c r="P61" s="92"/>
+      <c r="Q61" s="92"/>
+      <c r="R61" s="92"/>
+      <c r="S61" s="92"/>
+      <c r="T61" s="92"/>
+      <c r="U61" s="92"/>
+      <c r="V61" s="92"/>
+      <c r="W61" s="92"/>
+      <c r="X61" s="92"/>
+      <c r="Y61" s="92"/>
+      <c r="Z61" s="92"/>
+      <c r="AA61" s="92"/>
+      <c r="AB61" s="93"/>
+      <c r="AC61" s="87"/>
       <c r="AE61" s="9"/>
     </row>
     <row r="62" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A62" s="27"/>
+      <c r="B62" s="27"/>
+      <c r="C62" s="87"/>
+      <c r="D62" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E62" s="91"/>
+      <c r="F62" s="92"/>
+      <c r="G62" s="92"/>
+      <c r="H62" s="92"/>
+      <c r="I62" s="92"/>
+      <c r="J62" s="92"/>
+      <c r="K62" s="92"/>
+      <c r="L62" s="92"/>
+      <c r="M62" s="92"/>
+      <c r="N62" s="92"/>
+      <c r="O62" s="92"/>
+      <c r="P62" s="92"/>
+      <c r="Q62" s="92"/>
+      <c r="R62" s="92"/>
+      <c r="S62" s="92"/>
+      <c r="T62" s="92"/>
+      <c r="U62" s="92"/>
+      <c r="V62" s="92"/>
+      <c r="W62" s="92"/>
+      <c r="X62" s="92"/>
+      <c r="Y62" s="92"/>
+      <c r="Z62" s="92"/>
+      <c r="AA62" s="92"/>
+      <c r="AB62" s="93"/>
+      <c r="AC62" s="87"/>
       <c r="AE62" s="9"/>
     </row>
     <row r="63" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A63" s="27"/>
+      <c r="B63" s="86" t="s">
+        <v>99</v>
+      </c>
+      <c r="C63" s="87"/>
+      <c r="D63" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="E63" s="91"/>
+      <c r="F63" s="92"/>
+      <c r="G63" s="92"/>
+      <c r="H63" s="92"/>
+      <c r="I63" s="92"/>
+      <c r="J63" s="92"/>
+      <c r="K63" s="92"/>
+      <c r="L63" s="92"/>
+      <c r="M63" s="92"/>
+      <c r="N63" s="92"/>
+      <c r="O63" s="92"/>
+      <c r="P63" s="92"/>
+      <c r="Q63" s="92"/>
+      <c r="R63" s="92"/>
+      <c r="S63" s="92"/>
+      <c r="T63" s="92"/>
+      <c r="U63" s="92"/>
+      <c r="V63" s="92"/>
+      <c r="W63" s="92"/>
+      <c r="X63" s="92"/>
+      <c r="Y63" s="92"/>
+      <c r="Z63" s="92"/>
+      <c r="AA63" s="92"/>
+      <c r="AB63" s="93"/>
+      <c r="AC63" s="87"/>
       <c r="AE63" s="9"/>
+    </row>
+    <row r="64" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A64" s="27">
+        <v>1</v>
+      </c>
+      <c r="B64" s="26"/>
+      <c r="C64" s="87"/>
+      <c r="D64" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="E64" s="91"/>
+      <c r="F64" s="92"/>
+      <c r="G64" s="92"/>
+      <c r="H64" s="92"/>
+      <c r="I64" s="92"/>
+      <c r="J64" s="92"/>
+      <c r="K64" s="92"/>
+      <c r="L64" s="92"/>
+      <c r="M64" s="92"/>
+      <c r="N64" s="92"/>
+      <c r="O64" s="92"/>
+      <c r="P64" s="92"/>
+      <c r="Q64" s="92"/>
+      <c r="R64" s="92"/>
+      <c r="S64" s="92"/>
+      <c r="T64" s="92"/>
+      <c r="U64" s="92"/>
+      <c r="V64" s="92"/>
+      <c r="W64" s="92"/>
+      <c r="X64" s="92"/>
+      <c r="Y64" s="92"/>
+      <c r="Z64" s="92"/>
+      <c r="AA64" s="92"/>
+      <c r="AB64" s="93"/>
+      <c r="AC64" s="87"/>
+    </row>
+    <row r="65" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A65" s="27">
+        <v>2</v>
+      </c>
+      <c r="B65" s="26"/>
+      <c r="C65" s="87"/>
+      <c r="D65" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E65" s="91"/>
+      <c r="F65" s="92"/>
+      <c r="G65" s="92"/>
+      <c r="H65" s="92"/>
+      <c r="I65" s="92"/>
+      <c r="J65" s="92"/>
+      <c r="K65" s="92"/>
+      <c r="L65" s="92"/>
+      <c r="M65" s="92"/>
+      <c r="N65" s="92"/>
+      <c r="O65" s="92"/>
+      <c r="P65" s="92"/>
+      <c r="Q65" s="92"/>
+      <c r="R65" s="92"/>
+      <c r="S65" s="92"/>
+      <c r="T65" s="92"/>
+      <c r="U65" s="92"/>
+      <c r="V65" s="92"/>
+      <c r="W65" s="92"/>
+      <c r="X65" s="92"/>
+      <c r="Y65" s="92"/>
+      <c r="Z65" s="92"/>
+      <c r="AA65" s="92"/>
+      <c r="AB65" s="93"/>
+      <c r="AC65" s="87"/>
+    </row>
+    <row r="66" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A66" s="27">
+        <v>3</v>
+      </c>
+      <c r="B66" s="26"/>
+      <c r="C66" s="87"/>
+      <c r="D66" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="E66" s="91"/>
+      <c r="F66" s="92"/>
+      <c r="G66" s="92"/>
+      <c r="H66" s="92"/>
+      <c r="I66" s="92"/>
+      <c r="J66" s="92"/>
+      <c r="K66" s="92"/>
+      <c r="L66" s="92"/>
+      <c r="M66" s="92"/>
+      <c r="N66" s="92"/>
+      <c r="O66" s="92"/>
+      <c r="P66" s="92"/>
+      <c r="Q66" s="92"/>
+      <c r="R66" s="92"/>
+      <c r="S66" s="92"/>
+      <c r="T66" s="92"/>
+      <c r="U66" s="92"/>
+      <c r="V66" s="92"/>
+      <c r="W66" s="92"/>
+      <c r="X66" s="92"/>
+      <c r="Y66" s="92"/>
+      <c r="Z66" s="92"/>
+      <c r="AA66" s="92"/>
+      <c r="AB66" s="93"/>
+      <c r="AC66" s="87"/>
+    </row>
+    <row r="67" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A67" s="27">
+        <v>4</v>
+      </c>
+      <c r="B67" s="26"/>
+      <c r="C67" s="87"/>
+      <c r="D67" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E67" s="91"/>
+      <c r="F67" s="92"/>
+      <c r="G67" s="92"/>
+      <c r="H67" s="92"/>
+      <c r="I67" s="92"/>
+      <c r="J67" s="92"/>
+      <c r="K67" s="92"/>
+      <c r="L67" s="92"/>
+      <c r="M67" s="92"/>
+      <c r="N67" s="92"/>
+      <c r="O67" s="92"/>
+      <c r="P67" s="92"/>
+      <c r="Q67" s="92"/>
+      <c r="R67" s="92"/>
+      <c r="S67" s="92"/>
+      <c r="T67" s="92"/>
+      <c r="U67" s="92"/>
+      <c r="V67" s="92"/>
+      <c r="W67" s="92"/>
+      <c r="X67" s="92"/>
+      <c r="Y67" s="92"/>
+      <c r="Z67" s="92"/>
+      <c r="AA67" s="92"/>
+      <c r="AB67" s="93"/>
+      <c r="AC67" s="87"/>
+    </row>
+    <row r="68" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A68" s="27">
+        <v>5</v>
+      </c>
+      <c r="B68" s="33"/>
+      <c r="C68" s="87"/>
+      <c r="D68" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="E68" s="91"/>
+      <c r="F68" s="92"/>
+      <c r="G68" s="92"/>
+      <c r="H68" s="92"/>
+      <c r="I68" s="92"/>
+      <c r="J68" s="92"/>
+      <c r="K68" s="92"/>
+      <c r="L68" s="92"/>
+      <c r="M68" s="92"/>
+      <c r="N68" s="92"/>
+      <c r="O68" s="92"/>
+      <c r="P68" s="92"/>
+      <c r="Q68" s="92"/>
+      <c r="R68" s="92"/>
+      <c r="S68" s="92"/>
+      <c r="T68" s="92"/>
+      <c r="U68" s="92"/>
+      <c r="V68" s="92"/>
+      <c r="W68" s="92"/>
+      <c r="X68" s="92"/>
+      <c r="Y68" s="92"/>
+      <c r="Z68" s="92"/>
+      <c r="AA68" s="92"/>
+      <c r="AB68" s="93"/>
+      <c r="AC68" s="87"/>
+    </row>
+    <row r="69" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A69" s="27"/>
+      <c r="B69" s="27"/>
+      <c r="C69" s="87"/>
+      <c r="D69" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="E69" s="91"/>
+      <c r="F69" s="92"/>
+      <c r="G69" s="92"/>
+      <c r="H69" s="92"/>
+      <c r="I69" s="92"/>
+      <c r="J69" s="92"/>
+      <c r="K69" s="92"/>
+      <c r="L69" s="92"/>
+      <c r="M69" s="92"/>
+      <c r="N69" s="92"/>
+      <c r="O69" s="92"/>
+      <c r="P69" s="92"/>
+      <c r="Q69" s="92"/>
+      <c r="R69" s="92"/>
+      <c r="S69" s="92"/>
+      <c r="T69" s="92"/>
+      <c r="U69" s="92"/>
+      <c r="V69" s="92"/>
+      <c r="W69" s="92"/>
+      <c r="X69" s="92"/>
+      <c r="Y69" s="92"/>
+      <c r="Z69" s="92"/>
+      <c r="AA69" s="92"/>
+      <c r="AB69" s="93"/>
+      <c r="AC69" s="87"/>
+    </row>
+    <row r="70" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A70" s="27"/>
+      <c r="B70" s="27"/>
+      <c r="C70" s="87"/>
+      <c r="D70" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="E70" s="91"/>
+      <c r="F70" s="92"/>
+      <c r="G70" s="92"/>
+      <c r="H70" s="92"/>
+      <c r="I70" s="92"/>
+      <c r="J70" s="92"/>
+      <c r="K70" s="92"/>
+      <c r="L70" s="92"/>
+      <c r="M70" s="92"/>
+      <c r="N70" s="92"/>
+      <c r="O70" s="92"/>
+      <c r="P70" s="92"/>
+      <c r="Q70" s="92"/>
+      <c r="R70" s="92"/>
+      <c r="S70" s="92"/>
+      <c r="T70" s="92"/>
+      <c r="U70" s="92"/>
+      <c r="V70" s="92"/>
+      <c r="W70" s="92"/>
+      <c r="X70" s="92"/>
+      <c r="Y70" s="92"/>
+      <c r="Z70" s="92"/>
+      <c r="AA70" s="92"/>
+      <c r="AB70" s="93"/>
+      <c r="AC70" s="87"/>
+    </row>
+    <row r="71" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A71" s="27"/>
+      <c r="B71" s="27"/>
+      <c r="C71" s="87"/>
+      <c r="D71" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="E71" s="91"/>
+      <c r="F71" s="92"/>
+      <c r="G71" s="92"/>
+      <c r="H71" s="92"/>
+      <c r="I71" s="92"/>
+      <c r="J71" s="92"/>
+      <c r="K71" s="92"/>
+      <c r="L71" s="92"/>
+      <c r="M71" s="92"/>
+      <c r="N71" s="92"/>
+      <c r="O71" s="92"/>
+      <c r="P71" s="92"/>
+      <c r="Q71" s="92"/>
+      <c r="R71" s="92"/>
+      <c r="S71" s="92"/>
+      <c r="T71" s="92"/>
+      <c r="U71" s="92"/>
+      <c r="V71" s="92"/>
+      <c r="W71" s="92"/>
+      <c r="X71" s="92"/>
+      <c r="Y71" s="92"/>
+      <c r="Z71" s="92"/>
+      <c r="AA71" s="92"/>
+      <c r="AB71" s="93"/>
+      <c r="AC71" s="87"/>
+    </row>
+    <row r="72" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A72" s="27"/>
+      <c r="B72" s="27"/>
+      <c r="C72" s="87"/>
+      <c r="D72" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="E72" s="91"/>
+      <c r="F72" s="92"/>
+      <c r="G72" s="92"/>
+      <c r="H72" s="92"/>
+      <c r="I72" s="92"/>
+      <c r="J72" s="92"/>
+      <c r="K72" s="92"/>
+      <c r="L72" s="92"/>
+      <c r="M72" s="92"/>
+      <c r="N72" s="92"/>
+      <c r="O72" s="92"/>
+      <c r="P72" s="92"/>
+      <c r="Q72" s="92"/>
+      <c r="R72" s="92"/>
+      <c r="S72" s="92"/>
+      <c r="T72" s="92"/>
+      <c r="U72" s="92"/>
+      <c r="V72" s="92"/>
+      <c r="W72" s="92"/>
+      <c r="X72" s="92"/>
+      <c r="Y72" s="92"/>
+      <c r="Z72" s="92"/>
+      <c r="AA72" s="92"/>
+      <c r="AB72" s="93"/>
+      <c r="AC72" s="87"/>
+    </row>
+    <row r="73" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A73" s="27"/>
+      <c r="B73" s="27"/>
+      <c r="C73" s="87"/>
+      <c r="D73" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="E73" s="91"/>
+      <c r="F73" s="92"/>
+      <c r="G73" s="92"/>
+      <c r="H73" s="92"/>
+      <c r="I73" s="92"/>
+      <c r="J73" s="92"/>
+      <c r="K73" s="92"/>
+      <c r="L73" s="92"/>
+      <c r="M73" s="92"/>
+      <c r="N73" s="92"/>
+      <c r="O73" s="92"/>
+      <c r="P73" s="92"/>
+      <c r="Q73" s="92"/>
+      <c r="R73" s="92"/>
+      <c r="S73" s="92"/>
+      <c r="T73" s="92"/>
+      <c r="U73" s="92"/>
+      <c r="V73" s="92"/>
+      <c r="W73" s="92"/>
+      <c r="X73" s="92"/>
+      <c r="Y73" s="92"/>
+      <c r="Z73" s="92"/>
+      <c r="AA73" s="92"/>
+      <c r="AB73" s="93"/>
+      <c r="AC73" s="87"/>
+    </row>
+    <row r="74" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A74" s="27"/>
+      <c r="B74" s="27"/>
+      <c r="C74" s="87"/>
+      <c r="D74" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="E74" s="91"/>
+      <c r="F74" s="92"/>
+      <c r="G74" s="92"/>
+      <c r="H74" s="92"/>
+      <c r="I74" s="92"/>
+      <c r="J74" s="92"/>
+      <c r="K74" s="92"/>
+      <c r="L74" s="92"/>
+      <c r="M74" s="92"/>
+      <c r="N74" s="92"/>
+      <c r="O74" s="92"/>
+      <c r="P74" s="92"/>
+      <c r="Q74" s="92"/>
+      <c r="R74" s="92"/>
+      <c r="S74" s="92"/>
+      <c r="T74" s="92"/>
+      <c r="U74" s="92"/>
+      <c r="V74" s="92"/>
+      <c r="W74" s="92"/>
+      <c r="X74" s="92"/>
+      <c r="Y74" s="92"/>
+      <c r="Z74" s="92"/>
+      <c r="AA74" s="92"/>
+      <c r="AB74" s="93"/>
+      <c r="AC74" s="87"/>
+    </row>
+    <row r="75" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A75" s="27"/>
+      <c r="B75" s="27"/>
+      <c r="C75" s="87"/>
+      <c r="D75" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="E75" s="94"/>
+      <c r="F75" s="95"/>
+      <c r="G75" s="95"/>
+      <c r="H75" s="95"/>
+      <c r="I75" s="95"/>
+      <c r="J75" s="95"/>
+      <c r="K75" s="95"/>
+      <c r="L75" s="95"/>
+      <c r="M75" s="95"/>
+      <c r="N75" s="95"/>
+      <c r="O75" s="95"/>
+      <c r="P75" s="95"/>
+      <c r="Q75" s="95"/>
+      <c r="R75" s="95"/>
+      <c r="S75" s="95"/>
+      <c r="T75" s="95"/>
+      <c r="U75" s="95"/>
+      <c r="V75" s="95"/>
+      <c r="W75" s="95"/>
+      <c r="X75" s="95"/>
+      <c r="Y75" s="95"/>
+      <c r="Z75" s="95"/>
+      <c r="AA75" s="95"/>
+      <c r="AB75" s="85"/>
+      <c r="AC75" s="87"/>
+    </row>
+    <row r="76" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A76" s="87"/>
+      <c r="B76" s="87"/>
+      <c r="C76" s="87"/>
+      <c r="D76" s="87"/>
+      <c r="E76" s="87"/>
+      <c r="F76" s="87"/>
+      <c r="G76" s="87"/>
+      <c r="H76" s="87"/>
+      <c r="I76" s="87"/>
+      <c r="J76" s="87"/>
+      <c r="K76" s="87"/>
+      <c r="L76" s="87"/>
+      <c r="M76" s="87"/>
+      <c r="N76" s="87"/>
+      <c r="O76" s="87"/>
+      <c r="P76" s="87"/>
+      <c r="Q76" s="87"/>
+      <c r="R76" s="87"/>
+      <c r="S76" s="87"/>
+      <c r="T76" s="87"/>
+      <c r="U76" s="87"/>
+      <c r="V76" s="87"/>
+      <c r="W76" s="87"/>
+      <c r="X76" s="87"/>
+      <c r="Y76" s="87"/>
+      <c r="Z76" s="87"/>
+      <c r="AA76" s="87"/>
+      <c r="AB76" s="87"/>
+      <c r="AC76" s="87"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6067,14 +6905,14 @@
     <mergeCell ref="AK5:AL5"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A6 A24 A42" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"R,G,B"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ4 AJ10:AJ11" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2:AE51" xr:uid="{3CB4C30D-1E31-874F-8891-21C3C0C672E2}">
       <formula1>"Condition,QC,Blank,TrueBlank,Library,SystemValidation"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A6" xr:uid="{62885FFE-2AB0-084D-AAC7-A781F3A6460F}">
+      <formula1>"R,G,B,Y"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6084,16 +6922,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R51"/>
+  <dimension ref="A1:S51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="14" max="16" width="10.6640625" customWidth="1"/>
-    <col min="17" max="17" width="30.83203125" customWidth="1"/>
-    <col min="18" max="18" width="19.6640625" customWidth="1"/>
-    <col min="19" max="19" width="22.83203125" customWidth="1"/>
+    <col min="15" max="17" width="10.6640625" customWidth="1"/>
+    <col min="18" max="18" width="30.83203125" customWidth="1"/>
+    <col min="19" max="19" width="19.6640625" customWidth="1"/>
+    <col min="20" max="20" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -6136,14 +6974,20 @@
       <c r="N1" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="R1" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="P1" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="11">
         <v>1</v>
       </c>
@@ -6156,45 +7000,48 @@
         <v>H1B</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E2" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="H2" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H2" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="I2" s="7" t="s">
+      <c r="J2" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="K2" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>59</v>
       </c>
       <c r="L2" s="26">
         <f>IF(LEN(User!AG2)=0,"",User!AG2)</f>
         <v>1</v>
       </c>
       <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="10"/>
+      <c r="N2" s="11">
+        <v>1</v>
+      </c>
+      <c r="O2" s="11"/>
       <c r="P2" s="10"/>
-      <c r="Q2" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="R2" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q2" s="10"/>
+      <c r="R2" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="11">
         <v>2</v>
       </c>
@@ -6207,39 +7054,45 @@
         <v>H1T</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E3" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="H3" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I3" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="I3" s="7" t="s">
+      <c r="J3" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="K3" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>59</v>
       </c>
       <c r="L3" s="26">
         <f>IF(LEN(User!AG3)=0,"",User!AG3)</f>
         <v>1</v>
       </c>
       <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="10"/>
+      <c r="N3" s="11">
+        <v>2</v>
+      </c>
+      <c r="O3" s="11"/>
       <c r="P3" s="10"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q3" s="10"/>
+      <c r="R3" s="96" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="11">
         <v>3</v>
       </c>
@@ -6252,41 +7105,44 @@
         <v>D2B</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E4" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="G4" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I4" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H4" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="I4" s="7" t="s">
+      <c r="J4" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="K4" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>59</v>
       </c>
       <c r="L4" s="26">
         <f>IF(LEN(User!AG4)=0,"",User!AG4)</f>
         <v>1</v>
       </c>
       <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="10"/>
+      <c r="N4" s="11">
+        <v>3</v>
+      </c>
+      <c r="O4" s="11"/>
       <c r="P4" s="10"/>
-      <c r="Q4" s="20"/>
-      <c r="R4" s="21"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q4" s="10"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="21"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="11">
         <v>4</v>
       </c>
@@ -6299,45 +7155,48 @@
         <v>D2T</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E5" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="G5" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="H5" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="I5" s="7" t="s">
+      <c r="J5" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="K5" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>59</v>
       </c>
       <c r="L5" s="26">
         <f>IF(LEN(User!AG5)=0,"",User!AG5)</f>
         <v>1</v>
       </c>
       <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="10"/>
+      <c r="N5" s="11">
+        <v>4</v>
+      </c>
+      <c r="O5" s="11"/>
       <c r="P5" s="10"/>
-      <c r="Q5" s="32" t="s">
-        <v>75</v>
-      </c>
-      <c r="R5" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q5" s="10"/>
+      <c r="R5" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="S5" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="11">
         <v>5</v>
       </c>
@@ -6350,39 +7209,46 @@
         <v>H3B</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E6" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="G6" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="H6" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H6" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="I6" s="7" t="s">
+      <c r="J6" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="K6" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>59</v>
       </c>
       <c r="L6" s="26">
         <f>IF(LEN(User!AG6)=0,"",User!AG6)</f>
         <v>1</v>
       </c>
       <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="10"/>
+      <c r="N6" s="11">
+        <v>5</v>
+      </c>
+      <c r="O6" s="11"/>
       <c r="P6" s="10"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q6" s="10"/>
+      <c r="R6" s="101" t="s">
+        <v>107</v>
+      </c>
+      <c r="S6" s="102"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" s="11">
         <v>6</v>
       </c>
@@ -6395,39 +7261,42 @@
         <v>H3T</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E7" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="G7" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="H7" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H7" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="I7" s="7" t="s">
+      <c r="J7" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="K7" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>59</v>
       </c>
       <c r="L7" s="26">
         <f>IF(LEN(User!AG7)=0,"",User!AG7)</f>
         <v>1</v>
       </c>
       <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="10"/>
+      <c r="N7" s="11">
+        <v>6</v>
+      </c>
+      <c r="O7" s="11"/>
       <c r="P7" s="10"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q7" s="10"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="11">
         <v>7</v>
       </c>
@@ -6440,45 +7309,48 @@
         <v>D4B</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E8" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="G8" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="H8" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H8" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="I8" s="7" t="s">
+      <c r="J8" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="K8" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>59</v>
       </c>
       <c r="L8" s="26">
         <f>IF(LEN(User!AG8)=0,"",User!AG8)</f>
         <v>1</v>
       </c>
       <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="10"/>
+      <c r="N8" s="11">
+        <v>7</v>
+      </c>
+      <c r="O8" s="11"/>
       <c r="P8" s="10"/>
-      <c r="Q8" s="33" t="s">
-        <v>73</v>
-      </c>
-      <c r="R8" s="27">
+      <c r="Q8" s="10"/>
+      <c r="R8" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="S8" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
         <v>8</v>
       </c>
@@ -6491,45 +7363,48 @@
         <v>D4T</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E9" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="G9" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="H9" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H9" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="I9" s="7" t="s">
+      <c r="J9" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="K9" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>59</v>
       </c>
       <c r="L9" s="26">
         <f>IF(LEN(User!AG9)=0,"",User!AG9)</f>
         <v>1</v>
       </c>
       <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="10"/>
+      <c r="N9" s="11">
+        <v>8</v>
+      </c>
+      <c r="O9" s="11"/>
       <c r="P9" s="10"/>
-      <c r="Q9" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="R9" s="6">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q9" s="10"/>
+      <c r="R9" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="S9" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="11">
         <v>9</v>
       </c>
@@ -6542,39 +7417,46 @@
         <v>H5B</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E10" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="G10" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="H10" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H10" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="I10" s="7" t="s">
+      <c r="J10" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="K10" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>59</v>
       </c>
       <c r="L10" s="26">
         <f>IF(LEN(User!AG10)=0,"",User!AG10)</f>
         <v>1</v>
       </c>
       <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="10"/>
+      <c r="N10" s="11">
+        <v>9</v>
+      </c>
+      <c r="O10" s="11"/>
       <c r="P10" s="10"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q10" s="10"/>
+      <c r="R10" s="99" t="s">
+        <v>109</v>
+      </c>
+      <c r="S10" s="100"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="11">
         <v>10</v>
       </c>
@@ -6587,39 +7469,42 @@
         <v>H5T</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E11" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="G11" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="H11" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I11" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H11" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="I11" s="7" t="s">
+      <c r="J11" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="K11" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>59</v>
       </c>
       <c r="L11" s="26">
         <f>IF(LEN(User!AG11)=0,"",User!AG11)</f>
         <v>1</v>
       </c>
       <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="10"/>
+      <c r="N11" s="11">
+        <v>10</v>
+      </c>
+      <c r="O11" s="11"/>
       <c r="P11" s="10"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q11" s="10"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="11">
         <v>11</v>
       </c>
@@ -6632,45 +7517,48 @@
         <v>D6B</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E12" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="G12" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="H12" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I12" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H12" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="I12" s="7" t="s">
+      <c r="J12" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="K12" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>59</v>
       </c>
       <c r="L12" s="26">
         <f>IF(LEN(User!AG12)=0,"",User!AG12)</f>
         <v>1</v>
       </c>
       <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="10"/>
+      <c r="N12" s="11">
+        <v>11</v>
+      </c>
+      <c r="O12" s="11"/>
       <c r="P12" s="10"/>
-      <c r="Q12" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="R12" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q12" s="10"/>
+      <c r="R12" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="S12" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="11">
         <v>12</v>
       </c>
@@ -6683,43 +7571,46 @@
         <v>D6T</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E13" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="G13" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="H13" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H13" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="I13" s="7" t="s">
+      <c r="J13" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="K13" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>59</v>
       </c>
       <c r="L13" s="26">
         <f>IF(LEN(User!AG13)=0,"",User!AG13)</f>
         <v>1</v>
       </c>
       <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="10"/>
+      <c r="N13" s="11">
+        <v>12</v>
+      </c>
+      <c r="O13" s="11"/>
       <c r="P13" s="10"/>
-      <c r="Q13" s="82" t="s">
-        <v>91</v>
-      </c>
-      <c r="R13" s="83"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q13" s="10"/>
+      <c r="R13" s="99" t="s">
+        <v>86</v>
+      </c>
+      <c r="S13" s="100"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="11">
         <v>13</v>
       </c>
@@ -6732,39 +7623,48 @@
         <v>hyea</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E14" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="G14" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="H14" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I14" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H14" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>57</v>
-      </c>
       <c r="J14" s="7" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L14" s="26">
         <f>IF(LEN(User!AG14)=0,"",User!AG14)</f>
         <v>2</v>
       </c>
       <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="10"/>
+      <c r="N14" s="11">
+        <v>13</v>
+      </c>
+      <c r="O14" s="11"/>
       <c r="P14" s="10"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q14" s="10"/>
+      <c r="R14" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="S14" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="11">
         <v>14</v>
       </c>
@@ -6777,39 +7677,46 @@
         <v>hyeb</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E15" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="G15" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="H15" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I15" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H15" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>57</v>
-      </c>
       <c r="J15" s="7" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L15" s="26">
         <f>IF(LEN(User!AG15)=0,"",User!AG15)</f>
         <v>2</v>
       </c>
       <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="10"/>
+      <c r="N15" s="11">
+        <v>14</v>
+      </c>
+      <c r="O15" s="11"/>
       <c r="P15" s="10"/>
-    </row>
-    <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q15" s="10"/>
+      <c r="R15" s="97" t="s">
+        <v>111</v>
+      </c>
+      <c r="S15" s="98"/>
+    </row>
+    <row r="16" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="11">
         <v>15</v>
       </c>
@@ -6822,39 +7729,42 @@
         <v>tb</v>
       </c>
       <c r="D16" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="F16" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="G16" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="H16" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I16" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>57</v>
-      </c>
       <c r="J16" s="7" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="L16" s="26">
         <f>IF(LEN(User!AG16)=0,"",User!AG16)</f>
         <v>1</v>
       </c>
       <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="10"/>
+      <c r="N16" s="11">
+        <v>15</v>
+      </c>
+      <c r="O16" s="11"/>
       <c r="P16" s="10"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="10"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="11">
         <v>16</v>
       </c>
@@ -6867,39 +7777,42 @@
         <v>Library</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E17" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="G17" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="H17" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I17" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H17" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="I17" s="7" t="s">
+      <c r="J17" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J17" s="7" t="s">
+      <c r="K17" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>59</v>
       </c>
       <c r="L17" s="26">
         <f>IF(LEN(User!AG17)=0,"",User!AG17)</f>
         <v>1</v>
       </c>
       <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="10"/>
+      <c r="N17" s="11">
+        <v>16</v>
+      </c>
+      <c r="O17" s="11"/>
       <c r="P17" s="10"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="10"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="11">
         <v>17</v>
       </c>
@@ -6922,10 +7835,11 @@
       <c r="L18" s="26"/>
       <c r="M18" s="11"/>
       <c r="N18" s="11"/>
-      <c r="O18" s="10"/>
+      <c r="O18" s="11"/>
       <c r="P18" s="10"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="10"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="11">
         <v>18</v>
       </c>
@@ -6951,10 +7865,11 @@
       </c>
       <c r="M19" s="11"/>
       <c r="N19" s="11"/>
-      <c r="O19" s="10"/>
+      <c r="O19" s="11"/>
       <c r="P19" s="10"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="10"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" s="11">
         <v>19</v>
       </c>
@@ -6980,10 +7895,11 @@
       </c>
       <c r="M20" s="11"/>
       <c r="N20" s="11"/>
-      <c r="O20" s="10"/>
+      <c r="O20" s="11"/>
       <c r="P20" s="10"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="10"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" s="11">
         <v>20</v>
       </c>
@@ -7009,10 +7925,11 @@
       </c>
       <c r="M21" s="11"/>
       <c r="N21" s="11"/>
-      <c r="O21" s="10"/>
+      <c r="O21" s="11"/>
       <c r="P21" s="10"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="10"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" s="11">
         <v>21</v>
       </c>
@@ -7038,10 +7955,11 @@
       </c>
       <c r="M22" s="11"/>
       <c r="N22" s="11"/>
-      <c r="O22" s="10"/>
+      <c r="O22" s="11"/>
       <c r="P22" s="10"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="10"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" s="11">
         <v>22</v>
       </c>
@@ -7067,10 +7985,11 @@
       </c>
       <c r="M23" s="11"/>
       <c r="N23" s="11"/>
-      <c r="O23" s="10"/>
+      <c r="O23" s="11"/>
       <c r="P23" s="10"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="10"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" s="11">
         <v>23</v>
       </c>
@@ -7096,10 +8015,11 @@
       </c>
       <c r="M24" s="11"/>
       <c r="N24" s="11"/>
-      <c r="O24" s="10"/>
+      <c r="O24" s="11"/>
       <c r="P24" s="10"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="10"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" s="11">
         <v>24</v>
       </c>
@@ -7125,10 +8045,11 @@
       </c>
       <c r="M25" s="11"/>
       <c r="N25" s="11"/>
-      <c r="O25" s="10"/>
+      <c r="O25" s="11"/>
       <c r="P25" s="10"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="10"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" s="11">
         <v>25</v>
       </c>
@@ -7154,10 +8075,11 @@
       </c>
       <c r="M26" s="11"/>
       <c r="N26" s="11"/>
-      <c r="O26" s="10"/>
+      <c r="O26" s="11"/>
       <c r="P26" s="10"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="10"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" s="11">
         <v>26</v>
       </c>
@@ -7183,10 +8105,11 @@
       </c>
       <c r="M27" s="11"/>
       <c r="N27" s="11"/>
-      <c r="O27" s="10"/>
+      <c r="O27" s="11"/>
       <c r="P27" s="10"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="10"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" s="11">
         <v>27</v>
       </c>
@@ -7212,10 +8135,11 @@
       </c>
       <c r="M28" s="11"/>
       <c r="N28" s="11"/>
-      <c r="O28" s="10"/>
+      <c r="O28" s="11"/>
       <c r="P28" s="10"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="10"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" s="11">
         <v>28</v>
       </c>
@@ -7241,10 +8165,11 @@
       </c>
       <c r="M29" s="11"/>
       <c r="N29" s="11"/>
-      <c r="O29" s="10"/>
+      <c r="O29" s="11"/>
       <c r="P29" s="10"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="10"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" s="11">
         <v>29</v>
       </c>
@@ -7270,10 +8195,11 @@
       </c>
       <c r="M30" s="11"/>
       <c r="N30" s="11"/>
-      <c r="O30" s="10"/>
+      <c r="O30" s="11"/>
       <c r="P30" s="10"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="10"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" s="11">
         <v>30</v>
       </c>
@@ -7299,10 +8225,11 @@
       </c>
       <c r="M31" s="11"/>
       <c r="N31" s="11"/>
-      <c r="O31" s="10"/>
+      <c r="O31" s="11"/>
       <c r="P31" s="10"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="10"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" s="11">
         <v>31</v>
       </c>
@@ -7328,10 +8255,11 @@
       </c>
       <c r="M32" s="11"/>
       <c r="N32" s="11"/>
-      <c r="O32" s="10"/>
+      <c r="O32" s="11"/>
       <c r="P32" s="10"/>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="10"/>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" s="11">
         <v>32</v>
       </c>
@@ -7357,10 +8285,11 @@
       </c>
       <c r="M33" s="11"/>
       <c r="N33" s="11"/>
-      <c r="O33" s="10"/>
+      <c r="O33" s="11"/>
       <c r="P33" s="10"/>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="10"/>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34" s="11">
         <v>33</v>
       </c>
@@ -7386,10 +8315,11 @@
       </c>
       <c r="M34" s="11"/>
       <c r="N34" s="11"/>
-      <c r="O34" s="10"/>
+      <c r="O34" s="11"/>
       <c r="P34" s="10"/>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="10"/>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A35" s="11">
         <v>34</v>
       </c>
@@ -7415,10 +8345,11 @@
       </c>
       <c r="M35" s="11"/>
       <c r="N35" s="11"/>
-      <c r="O35" s="10"/>
+      <c r="O35" s="11"/>
       <c r="P35" s="10"/>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="10"/>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" s="11">
         <v>35</v>
       </c>
@@ -7442,11 +8373,11 @@
         <f>IF(LEN(User!AG36)=0,"",User!AG36)</f>
         <v/>
       </c>
-      <c r="N36" s="11"/>
-      <c r="O36" s="10"/>
+      <c r="O36" s="11"/>
       <c r="P36" s="10"/>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q36" s="10"/>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37" s="11">
         <v>36</v>
       </c>
@@ -7472,10 +8403,11 @@
       </c>
       <c r="M37" s="11"/>
       <c r="N37" s="11"/>
-      <c r="O37" s="10"/>
+      <c r="O37" s="11"/>
       <c r="P37" s="10"/>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q37" s="10"/>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A38" s="11">
         <v>37</v>
       </c>
@@ -7501,10 +8433,11 @@
       </c>
       <c r="M38" s="11"/>
       <c r="N38" s="11"/>
-      <c r="O38" s="10"/>
+      <c r="O38" s="11"/>
       <c r="P38" s="10"/>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="10"/>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" s="11">
         <v>38</v>
       </c>
@@ -7530,10 +8463,11 @@
       </c>
       <c r="M39" s="11"/>
       <c r="N39" s="11"/>
-      <c r="O39" s="10"/>
+      <c r="O39" s="11"/>
       <c r="P39" s="10"/>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="10"/>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A40" s="11">
         <v>39</v>
       </c>
@@ -7559,10 +8493,11 @@
       </c>
       <c r="M40" s="11"/>
       <c r="N40" s="11"/>
-      <c r="O40" s="10"/>
+      <c r="O40" s="11"/>
       <c r="P40" s="10"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="10"/>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A41" s="11">
         <v>40</v>
       </c>
@@ -7588,10 +8523,11 @@
       </c>
       <c r="M41" s="11"/>
       <c r="N41" s="11"/>
-      <c r="O41" s="10"/>
+      <c r="O41" s="11"/>
       <c r="P41" s="10"/>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="10"/>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42" s="11">
         <v>41</v>
       </c>
@@ -7617,10 +8553,11 @@
       </c>
       <c r="M42" s="11"/>
       <c r="N42" s="11"/>
-      <c r="O42" s="10"/>
+      <c r="O42" s="11"/>
       <c r="P42" s="10"/>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="10"/>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" s="11">
         <v>42</v>
       </c>
@@ -7646,10 +8583,11 @@
       </c>
       <c r="M43" s="11"/>
       <c r="N43" s="11"/>
-      <c r="O43" s="10"/>
+      <c r="O43" s="11"/>
       <c r="P43" s="10"/>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="10"/>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" s="11">
         <v>43</v>
       </c>
@@ -7675,10 +8613,11 @@
       </c>
       <c r="M44" s="11"/>
       <c r="N44" s="11"/>
-      <c r="O44" s="10"/>
+      <c r="O44" s="11"/>
       <c r="P44" s="10"/>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="10"/>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" s="11">
         <v>44</v>
       </c>
@@ -7704,10 +8643,11 @@
       </c>
       <c r="M45" s="11"/>
       <c r="N45" s="11"/>
-      <c r="O45" s="10"/>
+      <c r="O45" s="11"/>
       <c r="P45" s="10"/>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="10"/>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" s="11">
         <v>45</v>
       </c>
@@ -7733,10 +8673,11 @@
       </c>
       <c r="M46" s="11"/>
       <c r="N46" s="11"/>
-      <c r="O46" s="10"/>
+      <c r="O46" s="11"/>
       <c r="P46" s="10"/>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="10"/>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" s="11">
         <v>46</v>
       </c>
@@ -7762,10 +8703,11 @@
       </c>
       <c r="M47" s="11"/>
       <c r="N47" s="11"/>
-      <c r="O47" s="10"/>
+      <c r="O47" s="11"/>
       <c r="P47" s="10"/>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="10"/>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" s="11">
         <v>47</v>
       </c>
@@ -7791,10 +8733,11 @@
       </c>
       <c r="M48" s="11"/>
       <c r="N48" s="11"/>
-      <c r="O48" s="10"/>
+      <c r="O48" s="11"/>
       <c r="P48" s="10"/>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="10"/>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" s="11">
         <v>48</v>
       </c>
@@ -7820,10 +8763,11 @@
       </c>
       <c r="M49" s="11"/>
       <c r="N49" s="11"/>
-      <c r="O49" s="10"/>
+      <c r="O49" s="11"/>
       <c r="P49" s="10"/>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="10"/>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50" s="11">
         <v>49</v>
       </c>
@@ -7849,10 +8793,11 @@
       </c>
       <c r="M50" s="11"/>
       <c r="N50" s="11"/>
-      <c r="O50" s="10"/>
+      <c r="O50" s="11"/>
       <c r="P50" s="10"/>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="10"/>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" s="17">
         <v>50</v>
       </c>
@@ -7872,28 +8817,34 @@
       <c r="I51" s="12"/>
       <c r="J51" s="12"/>
       <c r="K51" s="16"/>
-      <c r="L51" s="34"/>
+      <c r="L51" s="33"/>
       <c r="M51" s="17"/>
       <c r="N51" s="17"/>
-      <c r="O51" s="18"/>
+      <c r="O51" s="17"/>
       <c r="P51" s="18"/>
+      <c r="Q51" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="Q13:R13"/>
+  <mergeCells count="3">
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="R10:S10"/>
   </mergeCells>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:C51" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Condition,QC,Blank,TrueBlank,Lib,SystemValidation,WetQC"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R12" xr:uid="{6AEEFCB2-B044-694B-9F49-3FEEB06C2FFC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S12" xr:uid="{37444466-4092-9F47-B85A-45B248F37EB3}">
       <formula1>"(choose),UltiMate3000,Vanquish Neo"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R5" xr:uid="{B83349D0-A4C7-354E-8FBD-A709474D425E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S5" xr:uid="{EAE169CD-CDD9-4448-AB00-B7A8134C5DC3}">
       <formula1>"(choose),Before,After"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2" xr:uid="{70ABDF96-F658-C64A-B1D3-FB2C11CCB448}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2" xr:uid="{C000D901-F3CF-7E46-91EA-29F5445586C7}">
       <formula1>"(choose),1 column,2 column"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S14" xr:uid="{773FB858-C65F-E745-B583-52578F21D4B5}">
+      <formula1>"(choose),Thermo,Bruker"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
